--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="532" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18A19E2F-A60C-41A0-B4F6-6F40F131EB1F}"/>
+  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8F590C5-92F0-4F23-B500-A5E78789D151}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="290">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1047,10 +1047,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1752,10 +1748,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12">
-        <v>1.452</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1786,10 +1782,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14">
-        <v>1.0649999999999999</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1803,10 +1799,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15">
-        <v>1.1000000000000001</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1820,10 +1816,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16">
-        <v>0.98399999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1837,10 +1833,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E17">
-        <v>1.0589999999999999</v>
+        <v>1.0740000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1871,10 +1867,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1888,10 +1884,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>1.0349999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2024,10 +2020,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E28">
-        <v>1.0209999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2092,10 +2088,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E32">
-        <v>1.0609999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2227,7 +2223,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C327"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2482,10 +2478,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="8">
-        <v>46254</v>
+        <v>46273</v>
       </c>
       <c r="C23" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2493,10 +2489,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="C24" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2504,10 +2500,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46161</v>
+        <v>46022</v>
       </c>
       <c r="C25" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2515,10 +2511,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46086</v>
+        <v>46161</v>
       </c>
       <c r="C26" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2526,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46211</v>
+        <v>46086</v>
       </c>
       <c r="C27" s="9">
         <v>3</v>
@@ -2537,10 +2533,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46020</v>
+        <v>46211</v>
       </c>
       <c r="C28" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2548,10 +2544,10 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C29" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2559,10 +2555,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46136</v>
+        <v>46076</v>
       </c>
       <c r="C30" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2570,10 +2566,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46078</v>
+        <v>46136</v>
       </c>
       <c r="C31" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2581,10 +2577,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46176</v>
+        <v>46078</v>
       </c>
       <c r="C32" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2592,10 +2588,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="C33" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2603,7 +2599,7 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46262</v>
+        <v>46182</v>
       </c>
       <c r="C34" s="6">
         <v>1</v>
@@ -2614,10 +2610,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46098</v>
+        <v>46262</v>
       </c>
       <c r="C35" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2625,7 +2621,7 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46181</v>
+        <v>46098</v>
       </c>
       <c r="C36" s="6">
         <v>3</v>
@@ -2636,10 +2632,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46084</v>
+        <v>46181</v>
       </c>
       <c r="C37" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2647,10 +2643,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C38" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2658,10 +2654,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C39" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2669,7 +2665,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -2680,10 +2676,10 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C41" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2691,10 +2687,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C42" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2702,10 +2698,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C43" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2713,10 +2709,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46246</v>
+        <v>46132</v>
       </c>
       <c r="C44" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2724,7 +2720,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46127</v>
+        <v>46246</v>
       </c>
       <c r="C45" s="9">
         <v>2</v>
@@ -2735,7 +2731,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46258</v>
+        <v>46127</v>
       </c>
       <c r="C46" s="6">
         <v>2</v>
@@ -2746,10 +2742,10 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46225</v>
+        <v>46258</v>
       </c>
       <c r="C47" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2757,10 +2753,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="C48" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2768,10 +2764,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46091</v>
+        <v>46212</v>
       </c>
       <c r="C49" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2779,10 +2775,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C50" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2790,7 +2786,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C51" s="9">
         <v>1</v>
@@ -2801,7 +2797,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2812,7 +2808,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2823,7 +2819,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46184</v>
+        <v>46113</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2834,10 +2830,10 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46090</v>
+        <v>46184</v>
       </c>
       <c r="C55" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2845,10 +2841,10 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46210</v>
+        <v>46090</v>
       </c>
       <c r="C56" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2856,10 +2852,10 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46139</v>
+        <v>46210</v>
       </c>
       <c r="C57" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2867,7 +2863,7 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
@@ -2878,7 +2874,7 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C59" s="9">
         <v>1</v>
@@ -2889,7 +2885,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2900,7 +2896,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2911,10 +2907,10 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C62" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2922,10 +2918,10 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C63" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2933,7 +2929,7 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -2944,7 +2940,7 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C65" s="9">
         <v>1</v>
@@ -2955,7 +2951,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2966,7 +2962,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2977,7 +2973,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2988,7 +2984,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2999,7 +2995,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -3010,7 +3006,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3018,13 +3014,13 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46007</v>
+        <v>46261</v>
       </c>
       <c r="C72" s="6">
-        <v>76</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3032,10 +3028,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C73" s="9">
-        <v>33</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3043,10 +3039,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C74" s="6">
-        <v>78</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3054,10 +3050,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C75" s="9">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3065,10 +3061,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C76" s="6">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3076,10 +3072,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C77" s="9">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3087,10 +3083,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C78" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3098,10 +3094,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C79" s="9">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3109,10 +3105,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C80" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3120,10 +3116,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C81" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3131,10 +3127,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C82" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3142,10 +3138,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46262</v>
+        <v>46013</v>
       </c>
       <c r="C83" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3153,7 +3149,7 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46022</v>
+        <v>46262</v>
       </c>
       <c r="C84" s="6">
         <v>2</v>
@@ -3164,10 +3160,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C85" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3175,10 +3171,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C86" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3186,10 +3182,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C87" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3197,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C88" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3208,7 +3204,7 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C89" s="9">
         <v>2</v>
@@ -3219,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C90" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3230,10 +3226,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C91" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3241,7 +3237,7 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C92" s="6">
         <v>1</v>
@@ -3252,10 +3248,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C93" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3263,10 +3259,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C94" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3274,10 +3270,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C95" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3285,10 +3281,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C96" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3296,10 +3292,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C97" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3307,10 +3303,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46217</v>
+        <v>46078</v>
       </c>
       <c r="C98" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3318,7 +3314,7 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46099</v>
+        <v>46217</v>
       </c>
       <c r="C99" s="9">
         <v>1</v>
@@ -3329,7 +3325,7 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46104</v>
+        <v>46272</v>
       </c>
       <c r="C100" s="6">
         <v>3</v>
@@ -3340,7 +3336,7 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46267</v>
+        <v>46099</v>
       </c>
       <c r="C101" s="9">
         <v>1</v>
@@ -3351,10 +3347,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46248</v>
+        <v>46104</v>
       </c>
       <c r="C102" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3362,7 +3358,7 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46231</v>
+        <v>46267</v>
       </c>
       <c r="C103" s="9">
         <v>1</v>
@@ -3373,7 +3369,7 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46258</v>
+        <v>46273</v>
       </c>
       <c r="C104" s="6">
         <v>3</v>
@@ -3384,7 +3380,7 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46020</v>
+        <v>46248</v>
       </c>
       <c r="C105" s="9">
         <v>2</v>
@@ -3395,10 +3391,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46076</v>
+        <v>46231</v>
       </c>
       <c r="C106" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3406,10 +3402,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46111</v>
+        <v>46258</v>
       </c>
       <c r="C107" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3417,7 +3413,7 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46087</v>
+        <v>46020</v>
       </c>
       <c r="C108" s="6">
         <v>2</v>
@@ -3428,10 +3424,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46140</v>
+        <v>46076</v>
       </c>
       <c r="C109" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3439,10 +3435,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46113</v>
+        <v>46111</v>
       </c>
       <c r="C110" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3450,7 +3446,7 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46119</v>
+        <v>46087</v>
       </c>
       <c r="C111" s="9">
         <v>2</v>
@@ -3461,10 +3457,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46108</v>
+        <v>46140</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3472,10 +3468,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46098</v>
+        <v>46113</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3483,10 +3479,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3494,10 +3490,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46079</v>
+        <v>46108</v>
       </c>
       <c r="C115" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3505,10 +3501,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46139</v>
+        <v>46274</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3516,10 +3512,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46148</v>
+        <v>46098</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3527,7 +3523,7 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46185</v>
+        <v>46141</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -3538,10 +3534,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46174</v>
+        <v>46079</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3549,7 +3545,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46092</v>
+        <v>46139</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3560,7 +3556,7 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46021</v>
+        <v>46148</v>
       </c>
       <c r="C121" s="9">
         <v>2</v>
@@ -3571,7 +3567,7 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -3582,10 +3578,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46252</v>
+        <v>46174</v>
       </c>
       <c r="C123" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3593,10 +3589,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46212</v>
+        <v>46092</v>
       </c>
       <c r="C124" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3604,10 +3600,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="C125" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3615,10 +3611,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46227</v>
+        <v>46177</v>
       </c>
       <c r="C126" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3626,10 +3622,10 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46188</v>
+        <v>46252</v>
       </c>
       <c r="C127" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3637,10 +3633,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46147</v>
+        <v>46212</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3648,10 +3644,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46134</v>
+        <v>46086</v>
       </c>
       <c r="C129" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3659,10 +3655,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46182</v>
+        <v>46227</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3670,7 +3666,7 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3681,7 +3677,7 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46225</v>
+        <v>46147</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3689,46 +3685,46 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46003</v>
+        <v>46134</v>
       </c>
       <c r="C133" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46002</v>
+        <v>46182</v>
       </c>
       <c r="C134" s="6">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46008</v>
+        <v>46190</v>
       </c>
       <c r="C135" s="9">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46000</v>
+        <v>46225</v>
       </c>
       <c r="C136" s="6">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3736,10 +3732,10 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C137" s="9">
-        <v>38</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3747,10 +3743,10 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="C138" s="6">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3758,10 +3754,10 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="C139" s="9">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3769,10 +3765,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C140" s="6">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,10 +3776,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C141" s="9">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3791,10 +3787,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C142" s="6">
-        <v>8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3802,10 +3798,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C143" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3813,10 +3809,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46021</v>
+        <v>46006</v>
       </c>
       <c r="C144" s="6">
-        <v>2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3824,7 +3820,7 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46212</v>
+        <v>46009</v>
       </c>
       <c r="C145" s="9">
         <v>2</v>
@@ -3835,7 +3831,7 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46077</v>
+        <v>46014</v>
       </c>
       <c r="C146" s="6">
         <v>8</v>
@@ -3846,10 +3842,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46167</v>
+        <v>46013</v>
       </c>
       <c r="C147" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3857,10 +3853,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46209</v>
+        <v>46021</v>
       </c>
       <c r="C148" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3868,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46189</v>
+        <v>46212</v>
       </c>
       <c r="C149" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3879,10 +3875,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46245</v>
+        <v>46077</v>
       </c>
       <c r="C150" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3890,7 +3886,7 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="C151" s="9">
         <v>1</v>
@@ -3901,10 +3897,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="C152" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3912,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46093</v>
+        <v>46189</v>
       </c>
       <c r="C153" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3923,10 +3919,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="C154" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3934,10 +3930,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46090</v>
+        <v>46170</v>
       </c>
       <c r="C155" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3945,10 +3941,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46078</v>
+        <v>46210</v>
       </c>
       <c r="C156" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3956,10 +3952,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="C157" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3967,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46134</v>
+        <v>46233</v>
       </c>
       <c r="C158" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3978,7 +3974,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46083</v>
+        <v>46090</v>
       </c>
       <c r="C159" s="9">
         <v>4</v>
@@ -3989,10 +3985,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46262</v>
+        <v>46078</v>
       </c>
       <c r="C160" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4000,10 +3996,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46022</v>
+        <v>46084</v>
       </c>
       <c r="C161" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4011,7 +4007,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46114</v>
+        <v>46134</v>
       </c>
       <c r="C162" s="6">
         <v>2</v>
@@ -4022,10 +4018,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46135</v>
+        <v>46083</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4033,10 +4029,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46127</v>
+        <v>46262</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4044,7 +4040,7 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4055,10 +4051,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4066,7 +4062,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46267</v>
+        <v>46135</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4077,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4088,10 +4084,10 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46168</v>
+        <v>46087</v>
       </c>
       <c r="C169" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4099,7 +4095,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46248</v>
+        <v>46108</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4110,7 +4106,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46252</v>
+        <v>46267</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4121,7 +4117,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4132,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="C173" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4143,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46161</v>
+        <v>46248</v>
       </c>
       <c r="C174" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4154,7 +4150,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46129</v>
+        <v>46252</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4165,7 +4161,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46080</v>
+        <v>46097</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4176,7 +4172,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46120</v>
+        <v>46177</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4187,10 +4183,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46101</v>
+        <v>46161</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4198,7 +4194,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46155</v>
+        <v>46129</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4209,7 +4205,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46150</v>
+        <v>46080</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4220,7 +4216,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46141</v>
+        <v>46120</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4231,7 +4227,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46085</v>
+        <v>46101</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4242,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4253,10 +4249,10 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46126</v>
+        <v>46150</v>
       </c>
       <c r="C184" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4264,10 +4260,10 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46118</v>
+        <v>46141</v>
       </c>
       <c r="C185" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4275,7 +4271,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46258</v>
+        <v>46085</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4286,7 +4282,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46192</v>
+        <v>46148</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4297,54 +4293,54 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46079</v>
+        <v>46126</v>
       </c>
       <c r="C188" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46003</v>
+        <v>46118</v>
       </c>
       <c r="C189" s="9">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46000</v>
+        <v>46258</v>
       </c>
       <c r="C190" s="6">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46006</v>
+        <v>46192</v>
       </c>
       <c r="C191" s="9">
-        <v>167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46001</v>
+        <v>46079</v>
       </c>
       <c r="C192" s="6">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4352,10 +4348,10 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46014</v>
+        <v>46003</v>
       </c>
       <c r="C193" s="9">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4363,10 +4359,10 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C194" s="6">
-        <v>170</v>
+        <v>132</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4374,10 +4370,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C195" s="9">
-        <v>17</v>
+        <v>167</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4385,10 +4381,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C196" s="6">
-        <v>18</v>
+        <v>173</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4396,10 +4392,10 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C197" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4407,10 +4403,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C198" s="6">
-        <v>43</v>
+        <v>170</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4418,10 +4414,10 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C199" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4429,10 +4425,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46258</v>
+        <v>46010</v>
       </c>
       <c r="C200" s="6">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4440,10 +4436,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46080</v>
+        <v>46008</v>
       </c>
       <c r="C201" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4451,10 +4447,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46209</v>
+        <v>46007</v>
       </c>
       <c r="C202" s="6">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4462,10 +4458,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46227</v>
+        <v>46013</v>
       </c>
       <c r="C203" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4473,10 +4469,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46090</v>
+        <v>46258</v>
       </c>
       <c r="C204" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4484,10 +4480,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46192</v>
+        <v>46080</v>
       </c>
       <c r="C205" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4495,10 +4491,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46079</v>
+        <v>46209</v>
       </c>
       <c r="C206" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4506,7 +4502,7 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46015</v>
+        <v>46227</v>
       </c>
       <c r="C207" s="9">
         <v>1</v>
@@ -4517,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C208" s="6">
         <v>5</v>
@@ -4528,10 +4524,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46098</v>
+        <v>46192</v>
       </c>
       <c r="C209" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4539,10 +4535,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46021</v>
+        <v>46079</v>
       </c>
       <c r="C210" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4550,7 +4546,7 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46265</v>
+        <v>46015</v>
       </c>
       <c r="C211" s="9">
         <v>1</v>
@@ -4561,10 +4557,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C212" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4572,10 +4568,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46260</v>
+        <v>46098</v>
       </c>
       <c r="C213" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4583,10 +4579,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46128</v>
+        <v>46021</v>
       </c>
       <c r="C214" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4594,10 +4590,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46083</v>
+        <v>46265</v>
       </c>
       <c r="C215" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4605,10 +4601,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46255</v>
+        <v>46078</v>
       </c>
       <c r="C216" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4616,10 +4612,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46076</v>
+        <v>46260</v>
       </c>
       <c r="C217" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4627,10 +4623,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46262</v>
+        <v>46128</v>
       </c>
       <c r="C218" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4638,10 +4634,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C219" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4649,7 +4645,7 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46099</v>
+        <v>46255</v>
       </c>
       <c r="C220" s="6">
         <v>2</v>
@@ -4660,10 +4656,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C221" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4671,7 +4667,7 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46226</v>
+        <v>46262</v>
       </c>
       <c r="C222" s="6">
         <v>1</v>
@@ -4682,10 +4678,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46092</v>
+        <v>46084</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4693,7 +4689,7 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46022</v>
+        <v>46273</v>
       </c>
       <c r="C224" s="6">
         <v>1</v>
@@ -4704,7 +4700,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46031</v>
+        <v>46099</v>
       </c>
       <c r="C225" s="9">
         <v>2</v>
@@ -4715,10 +4711,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46120</v>
+        <v>46154</v>
       </c>
       <c r="C226" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4726,10 +4722,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="C227" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4737,10 +4733,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46077</v>
+        <v>46092</v>
       </c>
       <c r="C228" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4748,7 +4744,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4759,7 +4755,7 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46216</v>
+        <v>46031</v>
       </c>
       <c r="C230" s="6">
         <v>2</v>
@@ -4770,10 +4766,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46037</v>
+        <v>46120</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4781,7 +4777,7 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46020</v>
+        <v>46237</v>
       </c>
       <c r="C232" s="6">
         <v>3</v>
@@ -4792,10 +4788,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46106</v>
+        <v>46077</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4803,7 +4799,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46211</v>
+        <v>46114</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4814,10 +4810,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46239</v>
+        <v>46216</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4825,7 +4821,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46155</v>
+        <v>46037</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4836,10 +4832,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46210</v>
+        <v>46020</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4847,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -4858,7 +4854,7 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46132</v>
+        <v>46211</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
@@ -4869,7 +4865,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46108</v>
+        <v>46239</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -4880,7 +4876,7 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -4891,10 +4887,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46118</v>
+        <v>46210</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4902,7 +4898,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46035</v>
+        <v>46112</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4913,7 +4909,7 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46181</v>
+        <v>46132</v>
       </c>
       <c r="C244" s="6">
         <v>1</v>
@@ -4924,7 +4920,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4935,10 +4931,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46030</v>
+        <v>46148</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4946,7 +4942,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46204</v>
+        <v>46118</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -4957,7 +4953,7 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46176</v>
+        <v>46035</v>
       </c>
       <c r="C248" s="6">
         <v>1</v>
@@ -4968,7 +4964,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46101</v>
+        <v>46181</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4979,7 +4975,7 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46213</v>
+        <v>46087</v>
       </c>
       <c r="C250" s="6">
         <v>1</v>
@@ -4990,65 +4986,65 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46142</v>
+        <v>46030</v>
       </c>
       <c r="C251" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46001</v>
+        <v>46204</v>
       </c>
       <c r="C252" s="6">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46008</v>
+        <v>46176</v>
       </c>
       <c r="C253" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46003</v>
+        <v>46101</v>
       </c>
       <c r="C254" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46002</v>
+        <v>46213</v>
       </c>
       <c r="C255" s="9">
-        <v>109</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46006</v>
+        <v>46142</v>
       </c>
       <c r="C256" s="6">
-        <v>145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5056,10 +5052,10 @@
         <v>21</v>
       </c>
       <c r="B257" s="8">
-        <v>46007</v>
+        <v>46001</v>
       </c>
       <c r="C257" s="9">
-        <v>45</v>
+        <v>151</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5067,10 +5063,10 @@
         <v>21</v>
       </c>
       <c r="B258" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C258" s="6">
-        <v>127</v>
+        <v>38</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5078,10 +5074,10 @@
         <v>21</v>
       </c>
       <c r="B259" s="8">
-        <v>46084</v>
+        <v>46003</v>
       </c>
       <c r="C259" s="9">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5089,10 +5085,10 @@
         <v>21</v>
       </c>
       <c r="B260" s="5">
-        <v>46013</v>
+        <v>46002</v>
       </c>
       <c r="C260" s="6">
-        <v>26</v>
+        <v>109</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5100,10 +5096,10 @@
         <v>21</v>
       </c>
       <c r="B261" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C261" s="9">
-        <v>19</v>
+        <v>145</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5111,10 +5107,10 @@
         <v>21</v>
       </c>
       <c r="B262" s="5">
-        <v>46021</v>
+        <v>46007</v>
       </c>
       <c r="C262" s="6">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5122,10 +5118,10 @@
         <v>21</v>
       </c>
       <c r="B263" s="8">
-        <v>46009</v>
+        <v>46000</v>
       </c>
       <c r="C263" s="9">
-        <v>24</v>
+        <v>127</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5133,10 +5129,10 @@
         <v>21</v>
       </c>
       <c r="B264" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C264" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5144,10 +5140,10 @@
         <v>21</v>
       </c>
       <c r="B265" s="8">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="C265" s="9">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5155,10 +5151,10 @@
         <v>21</v>
       </c>
       <c r="B266" s="5">
-        <v>46157</v>
+        <v>46010</v>
       </c>
       <c r="C266" s="6">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -5166,10 +5162,10 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46079</v>
+        <v>46021</v>
       </c>
       <c r="C267" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -5177,10 +5173,10 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46167</v>
+        <v>46009</v>
       </c>
       <c r="C268" s="6">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5188,10 +5184,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46035</v>
+        <v>46083</v>
       </c>
       <c r="C269" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5199,10 +5195,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46085</v>
+        <v>46014</v>
       </c>
       <c r="C270" s="6">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5210,7 +5206,7 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46120</v>
+        <v>46157</v>
       </c>
       <c r="C271" s="9">
         <v>2</v>
@@ -5221,10 +5217,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46114</v>
+        <v>46079</v>
       </c>
       <c r="C272" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5232,10 +5228,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46094</v>
+        <v>46167</v>
       </c>
       <c r="C273" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5243,10 +5239,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46192</v>
+        <v>46035</v>
       </c>
       <c r="C274" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5254,10 +5250,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="C275" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5265,7 +5261,7 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C276" s="6">
         <v>2</v>
@@ -5276,10 +5272,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46091</v>
+        <v>46114</v>
       </c>
       <c r="C277" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5287,10 +5283,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="C278" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5298,10 +5294,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46020</v>
+        <v>46192</v>
       </c>
       <c r="C279" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5309,10 +5305,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C280" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5320,10 +5316,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46217</v>
+        <v>46127</v>
       </c>
       <c r="C281" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5331,10 +5327,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46078</v>
+        <v>46091</v>
       </c>
       <c r="C282" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5342,10 +5338,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46209</v>
+        <v>46090</v>
       </c>
       <c r="C283" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5353,10 +5349,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46237</v>
+        <v>46020</v>
       </c>
       <c r="C284" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5364,10 +5360,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46148</v>
+        <v>46015</v>
       </c>
       <c r="C285" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5375,10 +5371,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46105</v>
+        <v>46217</v>
       </c>
       <c r="C286" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5386,10 +5382,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46087</v>
+        <v>46078</v>
       </c>
       <c r="C287" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5397,10 +5393,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46107</v>
+        <v>46209</v>
       </c>
       <c r="C288" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5408,10 +5404,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46086</v>
+        <v>46237</v>
       </c>
       <c r="C289" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5419,10 +5415,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46106</v>
+        <v>46148</v>
       </c>
       <c r="C290" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5430,10 +5426,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46150</v>
+        <v>46105</v>
       </c>
       <c r="C291" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5441,7 +5437,7 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46104</v>
+        <v>46087</v>
       </c>
       <c r="C292" s="6">
         <v>3</v>
@@ -5452,10 +5448,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46118</v>
+        <v>46107</v>
       </c>
       <c r="C293" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5463,10 +5459,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46231</v>
+        <v>46086</v>
       </c>
       <c r="C294" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5474,10 +5470,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46076</v>
+        <v>46106</v>
       </c>
       <c r="C295" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5485,10 +5481,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46182</v>
+        <v>46150</v>
       </c>
       <c r="C296" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5496,10 +5492,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46188</v>
+        <v>46104</v>
       </c>
       <c r="C297" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5507,7 +5503,7 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46154</v>
+        <v>46118</v>
       </c>
       <c r="C298" s="6">
         <v>1</v>
@@ -5518,10 +5514,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46093</v>
+        <v>46231</v>
       </c>
       <c r="C299" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5529,10 +5525,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46122</v>
+        <v>46076</v>
       </c>
       <c r="C300" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5540,10 +5536,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46092</v>
+        <v>46182</v>
       </c>
       <c r="C301" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5551,10 +5547,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46156</v>
+        <v>46188</v>
       </c>
       <c r="C302" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5562,7 +5558,7 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46133</v>
+        <v>46154</v>
       </c>
       <c r="C303" s="9">
         <v>1</v>
@@ -5573,10 +5569,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46189</v>
+        <v>46093</v>
       </c>
       <c r="C304" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5584,7 +5580,7 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46210</v>
+        <v>46122</v>
       </c>
       <c r="C305" s="9">
         <v>1</v>
@@ -5595,10 +5591,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46232</v>
+        <v>46092</v>
       </c>
       <c r="C306" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5606,10 +5602,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="C307" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5617,7 +5613,7 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46022</v>
+        <v>46133</v>
       </c>
       <c r="C308" s="6">
         <v>1</v>
@@ -5628,10 +5624,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46100</v>
+        <v>46189</v>
       </c>
       <c r="C309" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5639,7 +5635,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46101</v>
+        <v>46210</v>
       </c>
       <c r="C310" s="6">
         <v>1</v>
@@ -5650,10 +5646,10 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46097</v>
+        <v>46232</v>
       </c>
       <c r="C311" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -5661,10 +5657,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="C312" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5672,7 +5668,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46108</v>
+        <v>46022</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5683,10 +5679,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46233</v>
+        <v>46100</v>
       </c>
       <c r="C314" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5694,10 +5690,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C315" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5705,10 +5701,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="C316" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5716,10 +5712,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46253</v>
+        <v>46077</v>
       </c>
       <c r="C317" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5727,7 +5723,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C318" s="6">
         <v>1</v>
@@ -5738,7 +5734,7 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46244</v>
+        <v>46233</v>
       </c>
       <c r="C319" s="9">
         <v>1</v>
@@ -5749,10 +5745,10 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="C320" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -5760,7 +5756,7 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46031</v>
+        <v>46113</v>
       </c>
       <c r="C321" s="9">
         <v>1</v>
@@ -5771,9 +5767,64 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
+        <v>46253</v>
+      </c>
+      <c r="C322" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B323" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C323" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B324" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C324" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B325" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C325" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B326" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C326" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B327" s="8">
         <v>46155</v>
       </c>
-      <c r="C322" s="6">
+      <c r="C327" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5996,7 +6047,7 @@
         <v>28</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6030,7 +6081,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6047,7 +6098,7 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -6064,7 +6115,7 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -6081,7 +6132,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -6092,13 +6143,13 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -6115,7 +6166,7 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6132,7 +6183,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -6268,7 +6319,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6333,10 +6384,10 @@
         <v>81</v>
       </c>
       <c r="D32">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E32">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6913,7 +6964,7 @@
         <v>289</v>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -6965,7 +7016,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -6976,7 +7027,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -7009,7 +7060,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -7020,7 +7071,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -7031,7 +7082,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -7042,7 +7093,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -7053,7 +7104,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -7064,7 +7115,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>87</v>
+        <v>49</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -7075,7 +7126,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -7086,7 +7137,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -7097,7 +7148,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -7119,7 +7170,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -7141,7 +7192,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>239</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7163,7 +7214,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -7174,7 +7225,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -7185,10 +7236,10 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -7196,7 +7247,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -7207,7 +7258,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7218,7 +7269,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7229,7 +7280,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7240,7 +7291,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7251,7 +7302,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7262,7 +7313,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7273,7 +7324,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7284,7 +7335,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7295,7 +7346,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7306,7 +7357,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7317,7 +7368,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7328,7 +7379,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7339,7 +7390,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7350,7 +7401,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7361,7 +7412,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -7383,7 +7434,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7394,7 +7445,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7405,7 +7456,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -7416,7 +7467,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7427,7 +7478,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7438,7 +7489,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7449,7 +7500,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -7460,7 +7511,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7471,7 +7522,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7482,7 +7533,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7493,7 +7544,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7504,7 +7555,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7515,7 +7566,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7526,7 +7577,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7537,7 +7588,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7548,7 +7599,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7559,7 +7610,7 @@
         <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7570,7 +7621,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -7578,13 +7629,13 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B101" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C101">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -7592,10 +7643,10 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C102">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -7603,10 +7654,10 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C103">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -7614,10 +7665,10 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C104">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -7625,10 +7676,10 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -7636,7 +7687,7 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C106">
         <v>6</v>
@@ -7647,7 +7698,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C107">
         <v>6</v>
@@ -7658,10 +7709,10 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -7669,10 +7720,10 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C109">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -7680,10 +7731,10 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C110">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -7691,7 +7742,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -7702,7 +7753,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -7713,7 +7764,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -7724,7 +7775,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -7735,7 +7786,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -7746,10 +7797,10 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C116">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -7757,7 +7808,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -7768,7 +7819,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C118">
         <v>3</v>
@@ -7779,10 +7830,10 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -7790,7 +7841,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -7801,7 +7852,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7812,7 +7863,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7823,7 +7874,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7834,7 +7885,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7845,7 +7896,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7856,7 +7907,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7867,7 +7918,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -7878,7 +7929,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -7889,7 +7940,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -7900,7 +7951,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -7911,10 +7962,10 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -7922,7 +7973,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7933,7 +7984,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -7944,7 +7995,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7955,7 +8006,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7966,7 +8017,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7977,7 +8028,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7988,7 +8039,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7999,7 +8050,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8010,7 +8061,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8021,7 +8072,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -8032,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8043,7 +8094,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -8054,7 +8105,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -8065,7 +8116,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -8076,7 +8127,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8087,7 +8138,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8098,7 +8149,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8109,7 +8160,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8120,7 +8171,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8131,7 +8182,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>67</v>
+        <v>157</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8142,7 +8193,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8153,7 +8204,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8164,7 +8215,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8175,7 +8226,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8186,7 +8237,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8197,7 +8248,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -8208,7 +8259,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -8219,7 +8270,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8230,7 +8281,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8241,7 +8292,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8252,7 +8303,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8263,7 +8314,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8274,7 +8325,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>96</v>
+        <v>271</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8285,7 +8336,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8296,7 +8347,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8307,7 +8358,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8318,7 +8369,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8329,7 +8380,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8340,7 +8391,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8351,7 +8402,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8362,7 +8413,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8373,7 +8424,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8384,7 +8435,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8395,7 +8446,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8406,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8417,7 +8468,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>181</v>
+        <v>70</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8428,7 +8479,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8439,7 +8490,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8450,7 +8501,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8461,7 +8512,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8472,7 +8523,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8483,7 +8534,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8494,7 +8545,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8505,7 +8556,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8513,13 +8564,13 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c r="C186">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -8527,10 +8578,10 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C187">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8538,10 +8589,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C188">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8549,10 +8600,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C189">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8560,10 +8611,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="C190">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -8571,10 +8622,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="C191">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -8582,10 +8633,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="C192">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8593,10 +8644,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C193">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8604,10 +8655,10 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="C194">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -8615,7 +8666,7 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C195">
         <v>11</v>
@@ -8626,10 +8677,10 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C196">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -8637,7 +8688,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C197">
         <v>10</v>
@@ -8648,10 +8699,10 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C198">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -8659,7 +8710,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C199">
         <v>9</v>
@@ -8670,10 +8721,10 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="C200">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -8681,7 +8732,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C201">
         <v>8</v>
@@ -8692,10 +8743,10 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="C202">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -8703,7 +8754,7 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="C203">
         <v>7</v>
@@ -8714,10 +8765,10 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C204">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -8725,7 +8776,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>194</v>
+        <v>57</v>
       </c>
       <c r="C205">
         <v>6</v>
@@ -8736,10 +8787,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>47</v>
+        <v>194</v>
       </c>
       <c r="C206">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -8747,7 +8798,7 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -8758,7 +8809,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -8769,7 +8820,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8780,7 +8831,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C210">
         <v>5</v>
@@ -8791,10 +8842,10 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C211">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -8802,7 +8853,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8813,7 +8864,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8824,7 +8875,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -8835,10 +8886,10 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C215">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -8846,7 +8897,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8857,7 +8908,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8868,7 +8919,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8879,7 +8930,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8890,7 +8941,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8901,7 +8952,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8912,7 +8963,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -8923,7 +8974,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>289</v>
+        <v>59</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -8934,7 +8985,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -8945,10 +8996,10 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="C225">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -8956,7 +9007,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8967,7 +9018,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8978,7 +9029,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>64</v>
+        <v>201</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8989,7 +9040,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9000,7 +9051,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9011,7 +9062,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9022,10 +9073,10 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -9033,7 +9084,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -9044,7 +9095,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -9055,7 +9106,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9066,7 +9117,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9077,7 +9128,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9088,7 +9139,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9099,7 +9150,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9110,7 +9161,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9121,7 +9172,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>118</v>
+        <v>239</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9132,7 +9183,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9143,7 +9194,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9154,7 +9205,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9165,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9176,7 +9227,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9187,7 +9238,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9198,7 +9249,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9209,7 +9260,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9220,7 +9271,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9231,7 +9282,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9242,7 +9293,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>215</v>
+        <v>123</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9253,7 +9304,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9264,7 +9315,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9275,7 +9326,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9286,7 +9337,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9297,7 +9348,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9308,7 +9359,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9319,7 +9370,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9330,7 +9381,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9341,7 +9392,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9352,7 +9403,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9363,7 +9414,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9374,7 +9425,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9385,7 +9436,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9396,7 +9447,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9407,7 +9458,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9418,7 +9469,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9429,7 +9480,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9440,7 +9491,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9451,7 +9502,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>116</v>
+        <v>208</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9462,7 +9513,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>231</v>
+        <v>116</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9470,13 +9521,13 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>118</v>
+        <v>231</v>
       </c>
       <c r="C273">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -9484,10 +9535,10 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C274">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -9495,10 +9546,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="C275">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -9506,10 +9557,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="C276">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -9517,7 +9568,7 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>196</v>
+        <v>101</v>
       </c>
       <c r="C277">
         <v>8</v>
@@ -9528,10 +9579,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="C278">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -9539,7 +9590,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="C279">
         <v>6</v>
@@ -9550,10 +9601,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C280">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -9561,7 +9612,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>236</v>
+        <v>138</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -9572,7 +9623,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>125</v>
+        <v>236</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9583,7 +9634,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9594,7 +9645,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9605,7 +9656,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -9616,10 +9667,10 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C286">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -9627,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -9638,10 +9689,10 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C288">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -9649,7 +9700,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>242</v>
+        <v>123</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -9660,7 +9711,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9671,7 +9722,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9682,7 +9733,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>243</v>
+        <v>124</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9693,7 +9744,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9704,7 +9755,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9715,7 +9766,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9726,7 +9777,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>159</v>
+        <v>62</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9737,7 +9788,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9748,7 +9799,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9759,7 +9810,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9770,10 +9821,10 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C300">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -9781,7 +9832,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9792,7 +9843,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9803,7 +9854,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9814,7 +9865,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9825,7 +9876,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9836,7 +9887,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9847,7 +9898,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9858,7 +9909,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9869,7 +9920,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>247</v>
+        <v>54</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9880,7 +9931,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9891,7 +9942,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9902,7 +9953,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>192</v>
+        <v>244</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9913,7 +9964,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9924,7 +9975,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>241</v>
+        <v>70</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9935,7 +9986,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -9946,10 +9997,10 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="C316">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -9957,7 +10008,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>135</v>
+        <v>268</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9968,7 +10019,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9979,7 +10030,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9990,7 +10041,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10001,7 +10052,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10012,7 +10063,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10023,7 +10074,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>134</v>
+        <v>259</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10034,7 +10085,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10045,7 +10096,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10056,7 +10107,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10067,7 +10118,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10078,7 +10129,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>249</v>
+        <v>179</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10089,7 +10140,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>144</v>
+        <v>249</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10100,7 +10151,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10111,7 +10162,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>206</v>
+        <v>254</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10122,7 +10173,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>49</v>
+        <v>206</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10133,7 +10184,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>269</v>
+        <v>49</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10144,7 +10195,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10155,7 +10206,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10166,7 +10217,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>255</v>
+        <v>116</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -10177,7 +10228,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10188,7 +10239,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>251</v>
+        <v>91</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10199,7 +10250,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10210,7 +10261,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10221,7 +10272,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>63</v>
+        <v>266</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10232,7 +10283,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>248</v>
+        <v>63</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10243,7 +10294,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10254,7 +10305,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10265,7 +10316,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10276,7 +10327,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10287,7 +10338,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10298,7 +10349,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10309,7 +10360,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>263</v>
+        <v>161</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10320,14 +10371,22 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
+        <v>263</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B351" t="s">
         <v>264</v>
       </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="12"/>
+      <c r="C351">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10386,7 +10445,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10397,7 +10456,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10408,7 +10467,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10430,7 +10489,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10441,7 +10500,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10579,7 +10638,7 @@
         <v>276</v>
       </c>
       <c r="C9">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10667,7 +10726,7 @@
         <v>282</v>
       </c>
       <c r="C17">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -10755,7 +10814,7 @@
         <v>276</v>
       </c>
       <c r="C25">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="541" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8F590C5-92F0-4F23-B500-A5E78789D151}"/>
+  <xr:revisionPtr revIDLastSave="549" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27685BB5-32D4-4E2A-830D-42211D215256}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="290">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1047,6 +1047,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2105,10 +2109,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E33">
-        <v>1.036</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2223,7 +2227,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C327"/>
+  <dimension ref="A1:C329"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2371,7 +2375,7 @@
         <v>46010</v>
       </c>
       <c r="C13" s="9">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2445,10 +2449,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46021</v>
+        <v>46275</v>
       </c>
       <c r="C20" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2456,10 +2460,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="8">
-        <v>46080</v>
+        <v>46021</v>
       </c>
       <c r="C21" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2467,10 +2471,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="5">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="C22" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2478,7 +2482,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="8">
-        <v>46273</v>
+        <v>46087</v>
       </c>
       <c r="C23" s="9">
         <v>3</v>
@@ -2489,10 +2493,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46254</v>
+        <v>46273</v>
       </c>
       <c r="C24" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2500,10 +2504,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="C25" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2511,10 +2515,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46161</v>
+        <v>46022</v>
       </c>
       <c r="C26" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2522,10 +2526,10 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46086</v>
+        <v>46161</v>
       </c>
       <c r="C27" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2533,7 +2537,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46211</v>
+        <v>46086</v>
       </c>
       <c r="C28" s="6">
         <v>3</v>
@@ -2544,10 +2548,10 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46020</v>
+        <v>46211</v>
       </c>
       <c r="C29" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2555,10 +2559,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C30" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2566,10 +2570,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46136</v>
+        <v>46076</v>
       </c>
       <c r="C31" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2577,10 +2581,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46078</v>
+        <v>46136</v>
       </c>
       <c r="C32" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2588,10 +2592,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46176</v>
+        <v>46078</v>
       </c>
       <c r="C33" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2599,10 +2603,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="C34" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2610,7 +2614,7 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46262</v>
+        <v>46182</v>
       </c>
       <c r="C35" s="9">
         <v>1</v>
@@ -2621,10 +2625,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46098</v>
+        <v>46262</v>
       </c>
       <c r="C36" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2632,7 +2636,7 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46181</v>
+        <v>46098</v>
       </c>
       <c r="C37" s="9">
         <v>3</v>
@@ -2643,10 +2647,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46084</v>
+        <v>46181</v>
       </c>
       <c r="C38" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2654,10 +2658,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C39" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2665,10 +2669,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C40" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2676,7 +2680,7 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C41" s="9">
         <v>2</v>
@@ -2687,10 +2691,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C42" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2698,10 +2702,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C43" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2709,10 +2713,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C44" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2720,10 +2724,10 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46246</v>
+        <v>46132</v>
       </c>
       <c r="C45" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2731,7 +2735,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46127</v>
+        <v>46246</v>
       </c>
       <c r="C46" s="6">
         <v>2</v>
@@ -2742,7 +2746,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46258</v>
+        <v>46127</v>
       </c>
       <c r="C47" s="9">
         <v>2</v>
@@ -2753,10 +2757,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46225</v>
+        <v>46258</v>
       </c>
       <c r="C48" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2764,10 +2768,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="C49" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2775,10 +2779,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46091</v>
+        <v>46212</v>
       </c>
       <c r="C50" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2786,10 +2790,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C51" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2797,7 +2801,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2808,7 +2812,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2819,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2830,7 +2834,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46184</v>
+        <v>46276</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2841,10 +2845,10 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C56" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2852,10 +2856,10 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46210</v>
+        <v>46184</v>
       </c>
       <c r="C57" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2863,10 +2867,10 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C58" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2874,10 +2878,10 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46148</v>
+        <v>46210</v>
       </c>
       <c r="C59" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2885,7 +2889,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46175</v>
+        <v>46139</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2896,7 +2900,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2907,7 +2911,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46093</v>
+        <v>46175</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -2918,10 +2922,10 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46177</v>
+        <v>46125</v>
       </c>
       <c r="C63" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2929,7 +2933,7 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -2940,10 +2944,10 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46245</v>
+        <v>46177</v>
       </c>
       <c r="C65" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2951,7 +2955,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46213</v>
+        <v>46156</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2962,7 +2966,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46092</v>
+        <v>46245</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2973,7 +2977,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46226</v>
+        <v>46213</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2984,7 +2988,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46238</v>
+        <v>46092</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2995,7 +2999,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46188</v>
+        <v>46226</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -3006,7 +3010,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46101</v>
+        <v>46238</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3017,7 +3021,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46261</v>
+        <v>46188</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3025,24 +3029,24 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C73" s="9">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46009</v>
+        <v>46261</v>
       </c>
       <c r="C74" s="6">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3050,10 +3054,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C75" s="9">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3061,10 +3065,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="C76" s="6">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3072,10 +3076,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C77" s="9">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3083,10 +3087,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C78" s="6">
-        <v>24</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3094,10 +3098,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C79" s="9">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3105,10 +3109,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="C80" s="6">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3116,10 +3120,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C81" s="9">
-        <v>58</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3127,7 +3131,7 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C82" s="6">
         <v>47</v>
@@ -3138,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C83" s="9">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3149,10 +3153,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46262</v>
+        <v>46003</v>
       </c>
       <c r="C84" s="6">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3160,10 +3164,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C85" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3171,10 +3175,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46080</v>
+        <v>46262</v>
       </c>
       <c r="C86" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3182,10 +3186,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46084</v>
+        <v>46022</v>
       </c>
       <c r="C87" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3193,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46125</v>
+        <v>46080</v>
       </c>
       <c r="C88" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3204,10 +3208,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46209</v>
+        <v>46084</v>
       </c>
       <c r="C89" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3215,10 +3219,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C90" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3226,10 +3230,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46083</v>
+        <v>46209</v>
       </c>
       <c r="C91" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3237,10 +3241,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46105</v>
+        <v>46091</v>
       </c>
       <c r="C92" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3248,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46210</v>
+        <v>46083</v>
       </c>
       <c r="C93" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3259,10 +3263,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46211</v>
+        <v>46105</v>
       </c>
       <c r="C94" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3270,10 +3274,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46269</v>
+        <v>46210</v>
       </c>
       <c r="C95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3281,10 +3285,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46077</v>
+        <v>46211</v>
       </c>
       <c r="C96" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3292,10 +3296,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46118</v>
+        <v>46269</v>
       </c>
       <c r="C97" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3303,10 +3307,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C98" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3314,7 +3318,7 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46217</v>
+        <v>46118</v>
       </c>
       <c r="C99" s="9">
         <v>1</v>
@@ -3325,10 +3329,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46272</v>
+        <v>46078</v>
       </c>
       <c r="C100" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3336,7 +3340,7 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46099</v>
+        <v>46217</v>
       </c>
       <c r="C101" s="9">
         <v>1</v>
@@ -3347,7 +3351,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46104</v>
+        <v>46272</v>
       </c>
       <c r="C102" s="6">
         <v>3</v>
@@ -3358,7 +3362,7 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46267</v>
+        <v>46099</v>
       </c>
       <c r="C103" s="9">
         <v>1</v>
@@ -3369,7 +3373,7 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46273</v>
+        <v>46104</v>
       </c>
       <c r="C104" s="6">
         <v>3</v>
@@ -3380,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="C105" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3391,10 +3395,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46231</v>
+        <v>46273</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3402,10 +3406,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="C107" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3413,10 +3417,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46020</v>
+        <v>46231</v>
       </c>
       <c r="C108" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3424,10 +3428,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46076</v>
+        <v>46258</v>
       </c>
       <c r="C109" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3435,10 +3439,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46111</v>
+        <v>46020</v>
       </c>
       <c r="C110" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3446,10 +3450,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46087</v>
+        <v>46076</v>
       </c>
       <c r="C111" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3457,10 +3461,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46140</v>
+        <v>46111</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3468,10 +3472,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46113</v>
+        <v>46087</v>
       </c>
       <c r="C113" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3479,7 +3483,7 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="C114" s="6">
         <v>2</v>
@@ -3490,10 +3494,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3501,7 +3505,7 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46274</v>
+        <v>46119</v>
       </c>
       <c r="C116" s="6">
         <v>2</v>
@@ -3512,7 +3516,7 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C117" s="9">
         <v>1</v>
@@ -3523,10 +3527,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46141</v>
+        <v>46274</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3534,10 +3538,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46079</v>
+        <v>46098</v>
       </c>
       <c r="C119" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3545,7 +3549,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3556,10 +3560,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46148</v>
+        <v>46079</v>
       </c>
       <c r="C121" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3567,7 +3571,7 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46185</v>
+        <v>46139</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -3578,10 +3582,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46174</v>
+        <v>46148</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3589,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46092</v>
+        <v>46185</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -3600,10 +3604,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46021</v>
+        <v>46174</v>
       </c>
       <c r="C125" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3611,7 +3615,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46177</v>
+        <v>46092</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3622,10 +3626,10 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46252</v>
+        <v>46021</v>
       </c>
       <c r="C127" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3633,10 +3637,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46212</v>
+        <v>46177</v>
       </c>
       <c r="C128" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3644,10 +3648,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46086</v>
+        <v>46252</v>
       </c>
       <c r="C129" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3655,7 +3659,7 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46227</v>
+        <v>46212</v>
       </c>
       <c r="C130" s="6">
         <v>2</v>
@@ -3666,10 +3670,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46188</v>
+        <v>46086</v>
       </c>
       <c r="C131" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3677,10 +3681,10 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46147</v>
+        <v>46227</v>
       </c>
       <c r="C132" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3688,7 +3692,7 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46134</v>
+        <v>46188</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3699,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3710,7 +3714,7 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46190</v>
+        <v>46134</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3721,7 +3725,7 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46225</v>
+        <v>46182</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3729,24 +3733,24 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46003</v>
+        <v>46190</v>
       </c>
       <c r="C137" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="C138" s="6">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3754,10 +3758,10 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C139" s="9">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3765,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C140" s="6">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3776,10 +3780,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C141" s="9">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3787,10 +3791,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C142" s="6">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3798,10 +3802,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C143" s="9">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3809,10 +3813,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C144" s="6">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3820,10 +3824,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C145" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3831,10 +3835,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C146" s="6">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3842,7 +3846,7 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C147" s="9">
         <v>2</v>
@@ -3853,10 +3857,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C148" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3864,7 +3868,7 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46212</v>
+        <v>46013</v>
       </c>
       <c r="C149" s="9">
         <v>2</v>
@@ -3875,10 +3879,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C150" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3886,10 +3890,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="C151" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3897,10 +3901,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46209</v>
+        <v>46077</v>
       </c>
       <c r="C152" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3908,10 +3912,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="C153" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3919,10 +3923,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="C154" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3930,10 +3934,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C155" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3941,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C156" s="6">
         <v>1</v>
@@ -3952,7 +3956,7 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C157" s="9">
         <v>1</v>
@@ -3963,10 +3967,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C158" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3974,10 +3978,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C159" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3985,10 +3989,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C160" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3996,7 +4000,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C161" s="9">
         <v>4</v>
@@ -4007,10 +4011,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C162" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4018,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C163" s="9">
         <v>4</v>
@@ -4029,7 +4033,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46262</v>
+        <v>46134</v>
       </c>
       <c r="C164" s="6">
         <v>2</v>
@@ -4040,10 +4044,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4051,7 +4055,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46114</v>
+        <v>46262</v>
       </c>
       <c r="C166" s="6">
         <v>2</v>
@@ -4062,7 +4066,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4073,10 +4077,10 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C168" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4084,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46087</v>
+        <v>46135</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4095,7 +4099,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46108</v>
+        <v>46127</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4106,7 +4110,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46267</v>
+        <v>46087</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4117,7 +4121,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4128,10 +4132,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46168</v>
+        <v>46267</v>
       </c>
       <c r="C173" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4139,7 +4143,7 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46248</v>
+        <v>46020</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4150,10 +4154,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46252</v>
+        <v>46168</v>
       </c>
       <c r="C175" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4161,7 +4165,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46097</v>
+        <v>46248</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4172,7 +4176,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46177</v>
+        <v>46252</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4183,10 +4187,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C178" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4194,7 +4198,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46129</v>
+        <v>46177</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4205,10 +4209,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46080</v>
+        <v>46161</v>
       </c>
       <c r="C180" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4216,7 +4220,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46120</v>
+        <v>46129</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4227,7 +4231,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4238,7 +4242,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46155</v>
+        <v>46120</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4249,7 +4253,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4260,7 +4264,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4271,7 +4275,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46085</v>
+        <v>46150</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4282,7 +4286,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4293,10 +4297,10 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46126</v>
+        <v>46085</v>
       </c>
       <c r="C188" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4304,10 +4308,10 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C189" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4315,10 +4319,10 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46258</v>
+        <v>46126</v>
       </c>
       <c r="C190" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4326,10 +4330,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46192</v>
+        <v>46118</v>
       </c>
       <c r="C191" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4337,7 +4341,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46079</v>
+        <v>46258</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4345,24 +4349,24 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46003</v>
+        <v>46192</v>
       </c>
       <c r="C193" s="9">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C194" s="6">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4370,10 +4374,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C195" s="9">
-        <v>167</v>
+        <v>91</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4381,10 +4385,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C196" s="6">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4392,10 +4396,10 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C197" s="9">
-        <v>15</v>
+        <v>167</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4403,10 +4407,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C198" s="6">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4414,10 +4418,10 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C199" s="9">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4425,10 +4429,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C200" s="6">
-        <v>18</v>
+        <v>170</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4436,10 +4440,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C201" s="9">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4447,10 +4451,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C202" s="6">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4458,10 +4462,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C203" s="9">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4469,10 +4473,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46258</v>
+        <v>46007</v>
       </c>
       <c r="C204" s="6">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4480,10 +4484,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C205" s="9">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4491,10 +4495,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46209</v>
+        <v>46258</v>
       </c>
       <c r="C206" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4502,10 +4506,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46227</v>
+        <v>46080</v>
       </c>
       <c r="C207" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4513,10 +4517,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46090</v>
+        <v>46209</v>
       </c>
       <c r="C208" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4524,10 +4528,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="C209" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4535,10 +4539,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C210" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4546,10 +4550,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46015</v>
+        <v>46192</v>
       </c>
       <c r="C211" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4557,10 +4561,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C212" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4568,10 +4572,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C213" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4579,10 +4583,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="C214" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4590,10 +4594,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46265</v>
+        <v>46098</v>
       </c>
       <c r="C215" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4601,10 +4605,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C216" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4612,7 +4616,7 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C217" s="9">
         <v>1</v>
@@ -4623,10 +4627,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C218" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4634,10 +4638,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46083</v>
+        <v>46260</v>
       </c>
       <c r="C219" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4645,10 +4649,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46255</v>
+        <v>46128</v>
       </c>
       <c r="C220" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4656,7 +4660,7 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C221" s="9">
         <v>7</v>
@@ -4667,10 +4671,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="C222" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4678,10 +4682,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="C223" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4689,7 +4693,7 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="C224" s="6">
         <v>1</v>
@@ -4700,10 +4704,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="C225" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4711,7 +4715,7 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46154</v>
+        <v>46273</v>
       </c>
       <c r="C226" s="6">
         <v>1</v>
@@ -4722,10 +4726,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46226</v>
+        <v>46099</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4733,7 +4737,7 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C228" s="6">
         <v>1</v>
@@ -4744,7 +4748,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46022</v>
+        <v>46226</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4755,10 +4759,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C230" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4766,10 +4770,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="C231" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4777,10 +4781,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46237</v>
+        <v>46031</v>
       </c>
       <c r="C232" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4788,10 +4792,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C233" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4799,10 +4803,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46114</v>
+        <v>46237</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4810,10 +4814,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46216</v>
+        <v>46077</v>
       </c>
       <c r="C235" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4821,7 +4825,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4832,10 +4836,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46020</v>
+        <v>46216</v>
       </c>
       <c r="C237" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4843,7 +4847,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46106</v>
+        <v>46037</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -4854,10 +4858,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46211</v>
+        <v>46020</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4865,7 +4869,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46239</v>
+        <v>46106</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -4876,7 +4880,7 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46155</v>
+        <v>46211</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -4887,10 +4891,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46210</v>
+        <v>46239</v>
       </c>
       <c r="C242" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4898,7 +4902,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4909,10 +4913,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46132</v>
+        <v>46210</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4920,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4931,7 +4935,7 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46148</v>
+        <v>46132</v>
       </c>
       <c r="C246" s="6">
         <v>1</v>
@@ -4942,7 +4946,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46118</v>
+        <v>46108</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -4953,7 +4957,7 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46035</v>
+        <v>46148</v>
       </c>
       <c r="C248" s="6">
         <v>1</v>
@@ -4964,7 +4968,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46181</v>
+        <v>46118</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4975,7 +4979,7 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46087</v>
+        <v>46035</v>
       </c>
       <c r="C250" s="6">
         <v>1</v>
@@ -4986,10 +4990,10 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46030</v>
+        <v>46181</v>
       </c>
       <c r="C251" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4997,7 +5001,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46204</v>
+        <v>46087</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5008,10 +5012,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46176</v>
+        <v>46030</v>
       </c>
       <c r="C253" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5019,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46101</v>
+        <v>46204</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5030,7 +5034,7 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46213</v>
+        <v>46176</v>
       </c>
       <c r="C255" s="9">
         <v>1</v>
@@ -5041,7 +5045,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5049,24 +5053,24 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46001</v>
+        <v>46213</v>
       </c>
       <c r="C257" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C258" s="6">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5074,10 +5078,10 @@
         <v>21</v>
       </c>
       <c r="B259" s="8">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C259" s="9">
-        <v>70</v>
+        <v>151</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5085,10 +5089,10 @@
         <v>21</v>
       </c>
       <c r="B260" s="5">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C260" s="6">
-        <v>109</v>
+        <v>38</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5096,10 +5100,10 @@
         <v>21</v>
       </c>
       <c r="B261" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C261" s="9">
-        <v>145</v>
+        <v>70</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5107,10 +5111,10 @@
         <v>21</v>
       </c>
       <c r="B262" s="5">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C262" s="6">
-        <v>45</v>
+        <v>109</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5118,10 +5122,10 @@
         <v>21</v>
       </c>
       <c r="B263" s="8">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C263" s="9">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5129,10 +5133,10 @@
         <v>21</v>
       </c>
       <c r="B264" s="5">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C264" s="6">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5140,10 +5144,10 @@
         <v>21</v>
       </c>
       <c r="B265" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C265" s="9">
-        <v>26</v>
+        <v>127</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5151,10 +5155,10 @@
         <v>21</v>
       </c>
       <c r="B266" s="5">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="C266" s="6">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -5162,10 +5166,10 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C267" s="9">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -5173,10 +5177,10 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C268" s="6">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5184,10 +5188,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C269" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5195,10 +5199,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C270" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5206,10 +5210,10 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C271" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5217,10 +5221,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46079</v>
+        <v>46014</v>
       </c>
       <c r="C272" s="6">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5228,10 +5232,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="C273" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5239,10 +5243,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="C274" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5250,10 +5254,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46085</v>
+        <v>46167</v>
       </c>
       <c r="C275" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5261,7 +5265,7 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46120</v>
+        <v>46035</v>
       </c>
       <c r="C276" s="6">
         <v>2</v>
@@ -5272,10 +5276,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46114</v>
+        <v>46085</v>
       </c>
       <c r="C277" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5283,10 +5287,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="C278" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5294,7 +5298,7 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46192</v>
+        <v>46114</v>
       </c>
       <c r="C279" s="9">
         <v>1</v>
@@ -5305,10 +5309,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C280" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5316,10 +5320,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46127</v>
+        <v>46192</v>
       </c>
       <c r="C281" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5327,10 +5331,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="C282" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5338,10 +5342,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46090</v>
+        <v>46127</v>
       </c>
       <c r="C283" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5349,7 +5353,7 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46020</v>
+        <v>46091</v>
       </c>
       <c r="C284" s="6">
         <v>2</v>
@@ -5360,10 +5364,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C285" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5371,10 +5375,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46217</v>
+        <v>46020</v>
       </c>
       <c r="C286" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5382,10 +5386,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C287" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5393,10 +5397,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46209</v>
+        <v>46217</v>
       </c>
       <c r="C288" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5404,10 +5408,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46237</v>
+        <v>46078</v>
       </c>
       <c r="C289" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5415,10 +5419,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46148</v>
+        <v>46209</v>
       </c>
       <c r="C290" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5426,10 +5430,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46105</v>
+        <v>46237</v>
       </c>
       <c r="C291" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5437,10 +5441,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46087</v>
+        <v>46148</v>
       </c>
       <c r="C292" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5448,10 +5452,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="C293" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5459,10 +5463,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="C294" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5470,10 +5474,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C295" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5481,10 +5485,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46150</v>
+        <v>46086</v>
       </c>
       <c r="C296" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5492,10 +5496,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="C297" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5503,10 +5507,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46118</v>
+        <v>46150</v>
       </c>
       <c r="C298" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5514,10 +5518,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46231</v>
+        <v>46104</v>
       </c>
       <c r="C299" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5525,10 +5529,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C300" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5536,7 +5540,7 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46182</v>
+        <v>46231</v>
       </c>
       <c r="C301" s="9">
         <v>1</v>
@@ -5547,10 +5551,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46188</v>
+        <v>46076</v>
       </c>
       <c r="C302" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5558,7 +5562,7 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="C303" s="9">
         <v>1</v>
@@ -5569,10 +5573,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46093</v>
+        <v>46188</v>
       </c>
       <c r="C304" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5580,7 +5584,7 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C305" s="9">
         <v>1</v>
@@ -5591,7 +5595,7 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C306" s="6">
         <v>3</v>
@@ -5602,10 +5606,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C307" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5613,10 +5617,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46133</v>
+        <v>46092</v>
       </c>
       <c r="C308" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5624,10 +5628,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46189</v>
+        <v>46156</v>
       </c>
       <c r="C309" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5635,7 +5639,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46210</v>
+        <v>46133</v>
       </c>
       <c r="C310" s="6">
         <v>1</v>
@@ -5646,7 +5650,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46232</v>
+        <v>46189</v>
       </c>
       <c r="C311" s="9">
         <v>1</v>
@@ -5657,7 +5661,7 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46126</v>
+        <v>46210</v>
       </c>
       <c r="C312" s="6">
         <v>1</v>
@@ -5668,7 +5672,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46022</v>
+        <v>46232</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5679,10 +5683,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46100</v>
+        <v>46126</v>
       </c>
       <c r="C314" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5690,7 +5694,7 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C315" s="9">
         <v>1</v>
@@ -5701,10 +5705,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C316" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5712,10 +5716,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46077</v>
+        <v>46101</v>
       </c>
       <c r="C317" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5723,10 +5727,10 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C318" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -5734,10 +5738,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46233</v>
+        <v>46077</v>
       </c>
       <c r="C319" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5745,10 +5749,10 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C320" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -5756,7 +5760,7 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46113</v>
+        <v>46233</v>
       </c>
       <c r="C321" s="9">
         <v>1</v>
@@ -5767,10 +5771,10 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46253</v>
+        <v>46098</v>
       </c>
       <c r="C322" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -5778,7 +5782,7 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C323" s="9">
         <v>1</v>
@@ -5789,7 +5793,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5800,7 +5804,7 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C325" s="9">
         <v>1</v>
@@ -5811,7 +5815,7 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46031</v>
+        <v>46244</v>
       </c>
       <c r="C326" s="6">
         <v>1</v>
@@ -5822,9 +5826,31 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C327" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B328" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C328" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B329" s="8">
         <v>46155</v>
       </c>
-      <c r="C327" s="9">
+      <c r="C329" s="9">
         <v>1</v>
       </c>
     </row>
@@ -6404,7 +6430,7 @@
         <v>7</v>
       </c>
       <c r="E33">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -8611,10 +8637,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C190">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -8622,7 +8648,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="C191">
         <v>15</v>
@@ -10500,7 +10526,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10638,7 +10664,7 @@
         <v>276</v>
       </c>
       <c r="C9">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10671,7 +10697,7 @@
         <v>279</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -10814,7 +10840,7 @@
         <v>276</v>
       </c>
       <c r="C25">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10847,7 +10873,7 @@
         <v>277</v>
       </c>
       <c r="C28">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="549" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27685BB5-32D4-4E2A-830D-42211D215256}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E60759EB-D161-4A9C-8EB7-29A2061266C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -2007,10 +2007,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>0.96299999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2092,10 +2092,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E32">
-        <v>1.0680000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2109,10 +2109,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.04</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2230,9 +2230,9 @@
   <dimension ref="A1:C329"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2757,10 +2757,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46258</v>
+        <v>46225</v>
       </c>
       <c r="C48" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2768,10 +2768,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="C49" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2779,10 +2779,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46212</v>
+        <v>46091</v>
       </c>
       <c r="C50" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2790,10 +2790,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46091</v>
+        <v>46104</v>
       </c>
       <c r="C51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2801,7 +2801,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46104</v>
+        <v>46140</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2812,7 +2812,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46140</v>
+        <v>46106</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46106</v>
+        <v>46276</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46276</v>
+        <v>46113</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2845,7 +2845,7 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46113</v>
+        <v>46184</v>
       </c>
       <c r="C56" s="6">
         <v>1</v>
@@ -2856,10 +2856,10 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46184</v>
+        <v>46090</v>
       </c>
       <c r="C57" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2867,10 +2867,10 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46090</v>
+        <v>46210</v>
       </c>
       <c r="C58" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2878,10 +2878,10 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46210</v>
+        <v>46139</v>
       </c>
       <c r="C59" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2889,7 +2889,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2900,7 +2900,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46148</v>
+        <v>46175</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2911,7 +2911,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46175</v>
+        <v>46125</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -2922,7 +2922,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46125</v>
+        <v>46093</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2933,10 +2933,10 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46093</v>
+        <v>46177</v>
       </c>
       <c r="C64" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2944,10 +2944,10 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46177</v>
+        <v>46156</v>
       </c>
       <c r="C65" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2955,7 +2955,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46156</v>
+        <v>46245</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2966,7 +2966,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46245</v>
+        <v>46213</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2977,7 +2977,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46213</v>
+        <v>46092</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2988,7 +2988,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2999,7 +2999,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46226</v>
+        <v>46238</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -3010,7 +3010,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46238</v>
+        <v>46188</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3021,7 +3021,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46188</v>
+        <v>46101</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3032,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46101</v>
+        <v>46261</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3040,13 +3040,13 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46261</v>
+        <v>46007</v>
       </c>
       <c r="C74" s="6">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3054,10 +3054,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C75" s="9">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3065,10 +3065,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46009</v>
+        <v>46000</v>
       </c>
       <c r="C76" s="6">
-        <v>33</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3076,10 +3076,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C77" s="9">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3087,10 +3087,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C78" s="6">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3098,10 +3098,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C79" s="9">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3109,10 +3109,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C80" s="6">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3120,10 +3120,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46014</v>
+        <v>46002</v>
       </c>
       <c r="C81" s="9">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3131,10 +3131,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C82" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3142,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C83" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3153,10 +3153,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46003</v>
+        <v>46013</v>
       </c>
       <c r="C84" s="6">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3164,10 +3164,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46013</v>
+        <v>46262</v>
       </c>
       <c r="C85" s="9">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3175,7 +3175,7 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46262</v>
+        <v>46022</v>
       </c>
       <c r="C86" s="6">
         <v>2</v>
@@ -3186,10 +3186,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="C87" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3197,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="C88" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3208,10 +3208,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46084</v>
+        <v>46125</v>
       </c>
       <c r="C89" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3219,10 +3219,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46125</v>
+        <v>46209</v>
       </c>
       <c r="C90" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3230,7 +3230,7 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46209</v>
+        <v>46091</v>
       </c>
       <c r="C91" s="9">
         <v>2</v>
@@ -3241,10 +3241,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="C92" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3252,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46083</v>
+        <v>46105</v>
       </c>
       <c r="C93" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3263,7 +3263,7 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46105</v>
+        <v>46210</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
@@ -3274,10 +3274,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C95" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3285,10 +3285,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46211</v>
+        <v>46269</v>
       </c>
       <c r="C96" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3296,10 +3296,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46269</v>
+        <v>46077</v>
       </c>
       <c r="C97" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3307,10 +3307,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46077</v>
+        <v>46118</v>
       </c>
       <c r="C98" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3318,10 +3318,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46118</v>
+        <v>46078</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3329,10 +3329,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46078</v>
+        <v>46217</v>
       </c>
       <c r="C100" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3340,10 +3340,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46217</v>
+        <v>46272</v>
       </c>
       <c r="C101" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3351,10 +3351,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46272</v>
+        <v>46099</v>
       </c>
       <c r="C102" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3362,10 +3362,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="C103" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3373,10 +3373,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46104</v>
+        <v>46267</v>
       </c>
       <c r="C104" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3384,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="C105" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3395,10 +3395,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46273</v>
+        <v>46248</v>
       </c>
       <c r="C106" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3406,10 +3406,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46248</v>
+        <v>46231</v>
       </c>
       <c r="C107" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3417,10 +3417,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46231</v>
+        <v>46258</v>
       </c>
       <c r="C108" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3428,10 +3428,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46258</v>
+        <v>46020</v>
       </c>
       <c r="C109" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3439,10 +3439,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46020</v>
+        <v>46076</v>
       </c>
       <c r="C110" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3450,10 +3450,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46076</v>
+        <v>46111</v>
       </c>
       <c r="C111" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3461,10 +3461,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46111</v>
+        <v>46087</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3472,7 +3472,7 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46087</v>
+        <v>46140</v>
       </c>
       <c r="C113" s="9">
         <v>2</v>
@@ -3483,10 +3483,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46140</v>
+        <v>46113</v>
       </c>
       <c r="C114" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3494,10 +3494,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="C115" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3505,10 +3505,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46119</v>
+        <v>46108</v>
       </c>
       <c r="C116" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3516,10 +3516,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46108</v>
+        <v>46274</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3527,10 +3527,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46274</v>
+        <v>46098</v>
       </c>
       <c r="C118" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3538,7 +3538,7 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46098</v>
+        <v>46141</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -3549,10 +3549,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46141</v>
+        <v>46079</v>
       </c>
       <c r="C120" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3560,10 +3560,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46079</v>
+        <v>46139</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3571,10 +3571,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3582,10 +3582,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46148</v>
+        <v>46185</v>
       </c>
       <c r="C123" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3593,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46185</v>
+        <v>46174</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -3604,7 +3604,7 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46174</v>
+        <v>46092</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3615,10 +3615,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46092</v>
+        <v>46021</v>
       </c>
       <c r="C126" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3626,10 +3626,10 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46021</v>
+        <v>46177</v>
       </c>
       <c r="C127" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3637,10 +3637,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46177</v>
+        <v>46252</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3648,10 +3648,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46252</v>
+        <v>46212</v>
       </c>
       <c r="C129" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3659,10 +3659,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46212</v>
+        <v>46086</v>
       </c>
       <c r="C130" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3670,10 +3670,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46086</v>
+        <v>46227</v>
       </c>
       <c r="C131" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3681,10 +3681,10 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46227</v>
+        <v>46188</v>
       </c>
       <c r="C132" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3692,7 +3692,7 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46188</v>
+        <v>46147</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3703,7 +3703,7 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46147</v>
+        <v>46134</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3714,7 +3714,7 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46134</v>
+        <v>46182</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3736,7 +3736,7 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3744,13 +3744,13 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46225</v>
+        <v>46003</v>
       </c>
       <c r="C138" s="6">
-        <v>1</v>
+        <v>95</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3758,10 +3758,10 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C139" s="9">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3769,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C140" s="6">
-        <v>113</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,10 +3780,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46008</v>
+        <v>46000</v>
       </c>
       <c r="C141" s="9">
-        <v>13</v>
+        <v>96</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3791,10 +3791,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C142" s="6">
-        <v>96</v>
+        <v>38</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3802,10 +3802,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46007</v>
+        <v>46001</v>
       </c>
       <c r="C143" s="9">
-        <v>38</v>
+        <v>91</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3813,10 +3813,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46001</v>
+        <v>46010</v>
       </c>
       <c r="C144" s="6">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3824,10 +3824,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C145" s="9">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3835,10 +3835,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="C146" s="6">
-        <v>83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3846,10 +3846,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C147" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3857,10 +3857,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="C148" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3868,7 +3868,7 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C149" s="9">
         <v>2</v>
@@ -3879,7 +3879,7 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46021</v>
+        <v>46212</v>
       </c>
       <c r="C150" s="6">
         <v>2</v>
@@ -3890,10 +3890,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46212</v>
+        <v>46077</v>
       </c>
       <c r="C151" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3901,10 +3901,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="C152" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3912,10 +3912,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46167</v>
+        <v>46209</v>
       </c>
       <c r="C153" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3923,7 +3923,7 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46209</v>
+        <v>46189</v>
       </c>
       <c r="C154" s="6">
         <v>3</v>
@@ -3934,10 +3934,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46189</v>
+        <v>46245</v>
       </c>
       <c r="C155" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3945,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46245</v>
+        <v>46170</v>
       </c>
       <c r="C156" s="6">
         <v>1</v>
@@ -3956,7 +3956,7 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46170</v>
+        <v>46210</v>
       </c>
       <c r="C157" s="9">
         <v>1</v>
@@ -3967,7 +3967,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46210</v>
+        <v>46093</v>
       </c>
       <c r="C158" s="6">
         <v>1</v>
@@ -3978,10 +3978,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46093</v>
+        <v>46233</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3989,10 +3989,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46233</v>
+        <v>46090</v>
       </c>
       <c r="C160" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4000,10 +4000,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46090</v>
+        <v>46078</v>
       </c>
       <c r="C161" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4011,10 +4011,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="C162" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4022,10 +4022,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46084</v>
+        <v>46134</v>
       </c>
       <c r="C163" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4033,10 +4033,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46134</v>
+        <v>46083</v>
       </c>
       <c r="C164" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4044,10 +4044,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46083</v>
+        <v>46262</v>
       </c>
       <c r="C165" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4055,10 +4055,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46262</v>
+        <v>46022</v>
       </c>
       <c r="C166" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4066,10 +4066,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46022</v>
+        <v>46114</v>
       </c>
       <c r="C167" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4077,10 +4077,10 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="C168" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4088,7 +4088,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46135</v>
+        <v>46127</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4099,7 +4099,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46127</v>
+        <v>46087</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46087</v>
+        <v>46108</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4121,7 +4121,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46108</v>
+        <v>46267</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4132,7 +4132,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46267</v>
+        <v>46020</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4143,10 +4143,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46020</v>
+        <v>46168</v>
       </c>
       <c r="C174" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4154,10 +4154,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46168</v>
+        <v>46248</v>
       </c>
       <c r="C175" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4165,7 +4165,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4176,7 +4176,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46252</v>
+        <v>46097</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4187,7 +4187,7 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46097</v>
+        <v>46177</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4198,10 +4198,10 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46177</v>
+        <v>46161</v>
       </c>
       <c r="C179" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4209,10 +4209,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46161</v>
+        <v>46129</v>
       </c>
       <c r="C180" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4220,7 +4220,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46129</v>
+        <v>46080</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4231,7 +4231,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46080</v>
+        <v>46120</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4242,7 +4242,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4253,7 +4253,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46101</v>
+        <v>46155</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4264,7 +4264,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46155</v>
+        <v>46150</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4275,7 +4275,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4286,7 +4286,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46141</v>
+        <v>46085</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4297,7 +4297,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46085</v>
+        <v>46148</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4308,10 +4308,10 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46148</v>
+        <v>46126</v>
       </c>
       <c r="C189" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4319,7 +4319,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46126</v>
+        <v>46118</v>
       </c>
       <c r="C190" s="6">
         <v>2</v>
@@ -4330,10 +4330,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46118</v>
+        <v>46258</v>
       </c>
       <c r="C191" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4341,7 +4341,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46258</v>
+        <v>46192</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4352,7 +4352,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46192</v>
+        <v>46079</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4360,13 +4360,13 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46079</v>
+        <v>46003</v>
       </c>
       <c r="C194" s="6">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4374,10 +4374,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46003</v>
+        <v>46000</v>
       </c>
       <c r="C195" s="9">
-        <v>91</v>
+        <v>132</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4385,10 +4385,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C196" s="6">
-        <v>132</v>
+        <v>167</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4396,10 +4396,10 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C197" s="9">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4407,10 +4407,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46001</v>
+        <v>46014</v>
       </c>
       <c r="C198" s="6">
-        <v>173</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4418,10 +4418,10 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46014</v>
+        <v>46002</v>
       </c>
       <c r="C199" s="9">
-        <v>15</v>
+        <v>170</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4429,10 +4429,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="C200" s="6">
-        <v>170</v>
+        <v>17</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4440,10 +4440,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C201" s="9">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4451,10 +4451,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="C202" s="6">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4462,10 +4462,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="C203" s="9">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4473,10 +4473,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="C204" s="6">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4484,10 +4484,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46013</v>
+        <v>46258</v>
       </c>
       <c r="C205" s="9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4495,10 +4495,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46258</v>
+        <v>46080</v>
       </c>
       <c r="C206" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4506,7 +4506,7 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46080</v>
+        <v>46209</v>
       </c>
       <c r="C207" s="9">
         <v>2</v>
@@ -4517,10 +4517,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46209</v>
+        <v>46227</v>
       </c>
       <c r="C208" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4528,10 +4528,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46227</v>
+        <v>46090</v>
       </c>
       <c r="C209" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4539,10 +4539,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46090</v>
+        <v>46192</v>
       </c>
       <c r="C210" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4550,7 +4550,7 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46192</v>
+        <v>46079</v>
       </c>
       <c r="C211" s="9">
         <v>4</v>
@@ -4561,10 +4561,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46079</v>
+        <v>46015</v>
       </c>
       <c r="C212" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4572,10 +4572,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46015</v>
+        <v>46085</v>
       </c>
       <c r="C213" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4583,10 +4583,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="C214" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4594,10 +4594,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46098</v>
+        <v>46021</v>
       </c>
       <c r="C215" s="9">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4605,10 +4605,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46021</v>
+        <v>46265</v>
       </c>
       <c r="C216" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4616,10 +4616,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46265</v>
+        <v>46078</v>
       </c>
       <c r="C217" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4627,10 +4627,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46078</v>
+        <v>46260</v>
       </c>
       <c r="C218" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4638,10 +4638,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46260</v>
+        <v>46128</v>
       </c>
       <c r="C219" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4649,10 +4649,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46128</v>
+        <v>46083</v>
       </c>
       <c r="C220" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4660,10 +4660,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46083</v>
+        <v>46255</v>
       </c>
       <c r="C221" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4671,10 +4671,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46255</v>
+        <v>46076</v>
       </c>
       <c r="C222" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4682,10 +4682,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46076</v>
+        <v>46262</v>
       </c>
       <c r="C223" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4693,10 +4693,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46262</v>
+        <v>46084</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4704,10 +4704,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46084</v>
+        <v>46273</v>
       </c>
       <c r="C225" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4715,10 +4715,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46273</v>
+        <v>46099</v>
       </c>
       <c r="C226" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4726,10 +4726,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46099</v>
+        <v>46154</v>
       </c>
       <c r="C227" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4737,7 +4737,7 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46154</v>
+        <v>46226</v>
       </c>
       <c r="C228" s="6">
         <v>1</v>
@@ -4748,7 +4748,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4759,7 +4759,7 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46092</v>
+        <v>46022</v>
       </c>
       <c r="C230" s="6">
         <v>1</v>
@@ -4770,10 +4770,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4781,7 +4781,7 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46031</v>
+        <v>46120</v>
       </c>
       <c r="C232" s="6">
         <v>2</v>
@@ -4792,10 +4792,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46120</v>
+        <v>46237</v>
       </c>
       <c r="C233" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4803,10 +4803,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46237</v>
+        <v>46077</v>
       </c>
       <c r="C234" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4814,10 +4814,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46077</v>
+        <v>46114</v>
       </c>
       <c r="C235" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4825,10 +4825,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46114</v>
+        <v>46216</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4836,10 +4836,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46216</v>
+        <v>46037</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4847,7 +4847,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46037</v>
+        <v>46276</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -6328,7 +6328,7 @@
         <v>3</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -6413,7 +6413,7 @@
         <v>242</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6430,7 +6430,7 @@
         <v>7</v>
       </c>
       <c r="E33">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -7834,7 +7834,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -7845,7 +7845,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C118">
         <v>3</v>
@@ -7856,7 +7856,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -7867,10 +7867,10 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -7878,7 +7878,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7889,7 +7889,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7900,7 +7900,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7911,7 +7911,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7922,7 +7922,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7933,7 +7933,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7944,7 +7944,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -7955,7 +7955,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -7966,7 +7966,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -7977,7 +7977,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -7988,7 +7988,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8054,7 +8054,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -8164,7 +8164,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8230,7 +8230,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8384,7 +8384,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8406,7 +8406,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8428,7 +8428,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8450,7 +8450,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8527,7 +8527,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8538,7 +8538,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8549,7 +8549,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8560,7 +8560,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -10504,7 +10504,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10515,7 +10515,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10526,7 +10526,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10763,7 +10763,7 @@
         <v>280</v>
       </c>
       <c r="C18">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -10840,7 +10840,7 @@
         <v>276</v>
       </c>
       <c r="C25">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E60759EB-D161-4A9C-8EB7-29A2061266C5}"/>
+  <xr:revisionPtr revIDLastSave="565" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF99CF4A-C45E-4AE5-A8A4-3EEF35653D76}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="287">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -478,9 +478,6 @@
     <t>Escuela de Lenguaje El Trigal</t>
   </si>
   <si>
-    <t>Escuela Julio Tejedor Zúñiga</t>
-  </si>
-  <si>
     <t>Colegio Renacer</t>
   </si>
   <si>
@@ -688,9 +685,6 @@
     <t>Liceo Polivalente Rigoberto Fontt</t>
   </si>
   <si>
-    <t>Colegio Chillán</t>
-  </si>
-  <si>
     <t>Colegio La Merced</t>
   </si>
   <si>
@@ -857,9 +851,6 @@
   </si>
   <si>
     <t>Liceo Salvador González</t>
-  </si>
-  <si>
-    <t>Colegio Cumbres de Llay Llay</t>
   </si>
   <si>
     <t>Colegio Genesaret</t>
@@ -1650,10 +1641,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6">
-        <v>1.0860000000000001</v>
+        <v>1.103</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1718,10 +1709,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10">
-        <v>1.0940000000000001</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1820,10 +1811,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1837,10 +1828,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17">
-        <v>1.0740000000000001</v>
+        <v>1.0589999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1871,10 +1862,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19">
-        <v>1.0109999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1939,10 +1930,10 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E23">
-        <v>1.079</v>
+        <v>1.105</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1990,10 +1981,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26">
-        <v>1.012</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2075,10 +2066,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E31">
-        <v>1.0720000000000001</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2109,10 +2100,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E33">
-        <v>1.036</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2160,10 +2151,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E36">
-        <v>1.024</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2194,10 +2185,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E38">
-        <v>1.0880000000000001</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2227,7 +2218,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C329"/>
+  <dimension ref="A1:C336"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2265,7 +2256,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2562,7 +2553,7 @@
         <v>46020</v>
       </c>
       <c r="C30" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2878,7 +2869,7 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46139</v>
+        <v>46287</v>
       </c>
       <c r="C59" s="9">
         <v>1</v>
@@ -3040,13 +3031,13 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C74" s="6">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3054,10 +3045,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C75" s="9">
-        <v>33</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3065,10 +3056,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C76" s="6">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3076,10 +3067,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C77" s="9">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3087,10 +3078,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C78" s="6">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3098,10 +3089,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C79" s="9">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3109,10 +3100,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C80" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3120,10 +3111,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C81" s="9">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3131,10 +3122,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C82" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3142,10 +3133,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C83" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3153,10 +3144,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C84" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3164,10 +3155,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46262</v>
+        <v>46013</v>
       </c>
       <c r="C85" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3549,10 +3540,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C120" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3560,10 +3551,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C121" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3571,10 +3562,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C122" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3582,10 +3573,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3593,7 +3584,7 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -3604,7 +3595,7 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46092</v>
+        <v>46174</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3615,10 +3606,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46021</v>
+        <v>46286</v>
       </c>
       <c r="C126" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3626,7 +3617,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46177</v>
+        <v>46092</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3637,10 +3628,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46252</v>
+        <v>46021</v>
       </c>
       <c r="C128" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3648,10 +3639,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46212</v>
+        <v>46177</v>
       </c>
       <c r="C129" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3659,10 +3650,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46086</v>
+        <v>46252</v>
       </c>
       <c r="C130" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3670,7 +3661,7 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46227</v>
+        <v>46212</v>
       </c>
       <c r="C131" s="9">
         <v>2</v>
@@ -3681,10 +3672,10 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46188</v>
+        <v>46086</v>
       </c>
       <c r="C132" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3692,10 +3683,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46147</v>
+        <v>46227</v>
       </c>
       <c r="C133" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3703,7 +3694,7 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46134</v>
+        <v>46188</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3714,7 +3705,7 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3725,7 +3716,7 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46190</v>
+        <v>46134</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3736,7 +3727,7 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46225</v>
+        <v>46182</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3744,24 +3735,24 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46003</v>
+        <v>46190</v>
       </c>
       <c r="C138" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="C139" s="9">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3769,10 +3760,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C140" s="6">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,10 +3771,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C141" s="9">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3791,10 +3782,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C142" s="6">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3802,10 +3793,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C143" s="9">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3813,10 +3804,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C144" s="6">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3824,10 +3815,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C145" s="9">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3835,10 +3826,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C146" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3846,10 +3837,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C147" s="9">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3857,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C148" s="6">
         <v>2</v>
@@ -3868,10 +3859,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C149" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3879,7 +3870,7 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46212</v>
+        <v>46013</v>
       </c>
       <c r="C150" s="6">
         <v>2</v>
@@ -3890,10 +3881,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C151" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3901,10 +3892,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="C152" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3912,10 +3903,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46209</v>
+        <v>46077</v>
       </c>
       <c r="C153" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3923,10 +3914,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="C154" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3934,10 +3925,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="C155" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3945,10 +3936,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C156" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3956,7 +3947,7 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C157" s="9">
         <v>1</v>
@@ -3967,7 +3958,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C158" s="6">
         <v>1</v>
@@ -3978,10 +3969,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C159" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3989,10 +3980,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C160" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4000,10 +3991,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C161" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4011,7 +4002,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C162" s="6">
         <v>4</v>
@@ -4022,10 +4013,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C163" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4033,7 +4024,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C164" s="6">
         <v>4</v>
@@ -4044,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46262</v>
+        <v>46134</v>
       </c>
       <c r="C165" s="9">
         <v>2</v>
@@ -4055,10 +4046,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4066,7 +4057,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46114</v>
+        <v>46262</v>
       </c>
       <c r="C167" s="9">
         <v>2</v>
@@ -4077,7 +4068,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4088,10 +4079,10 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C169" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4099,7 +4090,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46087</v>
+        <v>46135</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4110,7 +4101,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46108</v>
+        <v>46287</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4121,7 +4112,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46267</v>
+        <v>46127</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4132,7 +4123,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46020</v>
+        <v>46087</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4143,10 +4134,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46168</v>
+        <v>46286</v>
       </c>
       <c r="C174" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4154,7 +4145,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46248</v>
+        <v>46108</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4165,7 +4156,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46252</v>
+        <v>46267</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4176,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4187,10 +4178,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4198,10 +4189,10 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46161</v>
+        <v>46248</v>
       </c>
       <c r="C179" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4209,7 +4200,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46129</v>
+        <v>46252</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4220,7 +4211,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46080</v>
+        <v>46097</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4231,7 +4222,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46120</v>
+        <v>46177</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4242,10 +4233,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46101</v>
+        <v>46161</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4253,7 +4244,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46155</v>
+        <v>46129</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4264,7 +4255,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46150</v>
+        <v>46080</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4275,7 +4266,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46141</v>
+        <v>46120</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4286,7 +4277,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46085</v>
+        <v>46101</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4297,7 +4288,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4308,10 +4299,10 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46126</v>
+        <v>46150</v>
       </c>
       <c r="C189" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4319,10 +4310,10 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46118</v>
+        <v>46141</v>
       </c>
       <c r="C190" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4330,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46258</v>
+        <v>46085</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4341,7 +4332,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46192</v>
+        <v>46148</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4352,54 +4343,54 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46079</v>
+        <v>46126</v>
       </c>
       <c r="C193" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46003</v>
+        <v>46118</v>
       </c>
       <c r="C194" s="6">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46000</v>
+        <v>46258</v>
       </c>
       <c r="C195" s="9">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46006</v>
+        <v>46192</v>
       </c>
       <c r="C196" s="6">
-        <v>167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46001</v>
+        <v>46079</v>
       </c>
       <c r="C197" s="9">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4407,10 +4398,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46014</v>
+        <v>46003</v>
       </c>
       <c r="C198" s="6">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4418,10 +4409,10 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C199" s="9">
-        <v>170</v>
+        <v>132</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4429,10 +4420,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C200" s="6">
-        <v>17</v>
+        <v>167</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4440,10 +4431,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C201" s="9">
-        <v>18</v>
+        <v>173</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4451,10 +4442,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C202" s="6">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4462,10 +4453,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C203" s="9">
-        <v>43</v>
+        <v>170</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4473,10 +4464,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C204" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4484,10 +4475,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46258</v>
+        <v>46010</v>
       </c>
       <c r="C205" s="9">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4495,10 +4486,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46080</v>
+        <v>46008</v>
       </c>
       <c r="C206" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4506,10 +4497,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46209</v>
+        <v>46007</v>
       </c>
       <c r="C207" s="9">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4517,10 +4508,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46227</v>
+        <v>46013</v>
       </c>
       <c r="C208" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4528,10 +4519,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46090</v>
+        <v>46258</v>
       </c>
       <c r="C209" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4539,10 +4530,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46192</v>
+        <v>46080</v>
       </c>
       <c r="C210" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4550,10 +4541,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46079</v>
+        <v>46209</v>
       </c>
       <c r="C211" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4561,7 +4552,7 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46015</v>
+        <v>46227</v>
       </c>
       <c r="C212" s="6">
         <v>1</v>
@@ -4572,7 +4563,7 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C213" s="9">
         <v>5</v>
@@ -4583,10 +4574,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46098</v>
+        <v>46192</v>
       </c>
       <c r="C214" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4594,10 +4585,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46021</v>
+        <v>46079</v>
       </c>
       <c r="C215" s="9">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4605,7 +4596,7 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46265</v>
+        <v>46015</v>
       </c>
       <c r="C216" s="6">
         <v>1</v>
@@ -4616,10 +4607,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C217" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4627,10 +4618,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46260</v>
+        <v>46098</v>
       </c>
       <c r="C218" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4638,10 +4629,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46128</v>
+        <v>46021</v>
       </c>
       <c r="C219" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4649,10 +4640,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46083</v>
+        <v>46265</v>
       </c>
       <c r="C220" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4660,10 +4651,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46255</v>
+        <v>46078</v>
       </c>
       <c r="C221" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4671,10 +4662,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46076</v>
+        <v>46260</v>
       </c>
       <c r="C222" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4682,10 +4673,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46262</v>
+        <v>46128</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4693,10 +4684,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C224" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4704,10 +4695,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46273</v>
+        <v>46255</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4715,10 +4706,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C226" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4726,7 +4717,7 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46154</v>
+        <v>46262</v>
       </c>
       <c r="C227" s="9">
         <v>1</v>
@@ -4737,10 +4728,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46226</v>
+        <v>46084</v>
       </c>
       <c r="C228" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4748,7 +4739,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46092</v>
+        <v>46273</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4759,10 +4750,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46022</v>
+        <v>46099</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4770,10 +4761,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46031</v>
+        <v>46154</v>
       </c>
       <c r="C231" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4781,10 +4772,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46120</v>
+        <v>46226</v>
       </c>
       <c r="C232" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4792,10 +4783,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46237</v>
+        <v>46092</v>
       </c>
       <c r="C233" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4803,10 +4794,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46077</v>
+        <v>46022</v>
       </c>
       <c r="C234" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4814,10 +4805,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4825,10 +4816,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="C236" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4836,10 +4827,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46037</v>
+        <v>46077</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4847,7 +4838,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46276</v>
+        <v>46114</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -4858,10 +4849,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46020</v>
+        <v>46216</v>
       </c>
       <c r="C239" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4869,7 +4860,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46106</v>
+        <v>46037</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -4880,7 +4871,7 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46211</v>
+        <v>46276</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -4891,10 +4882,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46239</v>
+        <v>46020</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4902,7 +4893,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4913,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46210</v>
+        <v>46287</v>
       </c>
       <c r="C244" s="6">
         <v>2</v>
@@ -4924,7 +4915,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46112</v>
+        <v>46211</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4935,7 +4926,7 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46132</v>
+        <v>46239</v>
       </c>
       <c r="C246" s="6">
         <v>1</v>
@@ -4946,7 +4937,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46108</v>
+        <v>46155</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -4957,10 +4948,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46148</v>
+        <v>46210</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4968,7 +4959,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46118</v>
+        <v>46112</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4979,7 +4970,7 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46035</v>
+        <v>46132</v>
       </c>
       <c r="C250" s="6">
         <v>1</v>
@@ -4990,7 +4981,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46181</v>
+        <v>46108</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -5001,7 +4992,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46087</v>
+        <v>46148</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5012,10 +5003,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46030</v>
+        <v>46118</v>
       </c>
       <c r="C253" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5023,7 +5014,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46204</v>
+        <v>46035</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5034,7 +5025,7 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="C255" s="9">
         <v>1</v>
@@ -5045,7 +5036,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5056,10 +5047,10 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46213</v>
+        <v>46030</v>
       </c>
       <c r="C257" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5067,7 +5058,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46142</v>
+        <v>46031</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5075,68 +5066,68 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46001</v>
+        <v>46204</v>
       </c>
       <c r="C259" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46008</v>
+        <v>46176</v>
       </c>
       <c r="C260" s="6">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46003</v>
+        <v>46286</v>
       </c>
       <c r="C261" s="9">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46002</v>
+        <v>46101</v>
       </c>
       <c r="C262" s="6">
-        <v>109</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46006</v>
+        <v>46213</v>
       </c>
       <c r="C263" s="9">
-        <v>145</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46007</v>
+        <v>46142</v>
       </c>
       <c r="C264" s="6">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5144,10 +5135,10 @@
         <v>21</v>
       </c>
       <c r="B265" s="8">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="C265" s="9">
-        <v>127</v>
+        <v>151</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5155,10 +5146,10 @@
         <v>21</v>
       </c>
       <c r="B266" s="5">
-        <v>46084</v>
+        <v>46008</v>
       </c>
       <c r="C266" s="6">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -5166,10 +5157,10 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C267" s="9">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -5177,10 +5168,10 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C268" s="6">
-        <v>19</v>
+        <v>109</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5188,10 +5179,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46021</v>
+        <v>46006</v>
       </c>
       <c r="C269" s="9">
-        <v>6</v>
+        <v>145</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5199,10 +5190,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C270" s="6">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5210,10 +5201,10 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46083</v>
+        <v>46000</v>
       </c>
       <c r="C271" s="9">
-        <v>8</v>
+        <v>127</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5221,10 +5212,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46014</v>
+        <v>46084</v>
       </c>
       <c r="C272" s="6">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5232,10 +5223,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46157</v>
+        <v>46013</v>
       </c>
       <c r="C273" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5243,10 +5234,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46079</v>
+        <v>46010</v>
       </c>
       <c r="C274" s="6">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5254,10 +5245,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46167</v>
+        <v>46021</v>
       </c>
       <c r="C275" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5265,10 +5256,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46035</v>
+        <v>46009</v>
       </c>
       <c r="C276" s="6">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5276,10 +5267,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="C277" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5287,10 +5278,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46120</v>
+        <v>46014</v>
       </c>
       <c r="C278" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5298,10 +5289,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46114</v>
+        <v>46157</v>
       </c>
       <c r="C279" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5309,7 +5300,7 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46094</v>
+        <v>46079</v>
       </c>
       <c r="C280" s="6">
         <v>3</v>
@@ -5320,7 +5311,7 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46192</v>
+        <v>46167</v>
       </c>
       <c r="C281" s="9">
         <v>1</v>
@@ -5331,10 +5322,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46080</v>
+        <v>46035</v>
       </c>
       <c r="C282" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5342,10 +5333,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46127</v>
+        <v>46085</v>
       </c>
       <c r="C283" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5353,7 +5344,7 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46091</v>
+        <v>46120</v>
       </c>
       <c r="C284" s="6">
         <v>2</v>
@@ -5364,7 +5355,7 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46090</v>
+        <v>46114</v>
       </c>
       <c r="C285" s="9">
         <v>1</v>
@@ -5375,10 +5366,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46020</v>
+        <v>46094</v>
       </c>
       <c r="C286" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5386,10 +5377,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46015</v>
+        <v>46192</v>
       </c>
       <c r="C287" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5397,10 +5388,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46217</v>
+        <v>46080</v>
       </c>
       <c r="C288" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5408,10 +5399,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46078</v>
+        <v>46127</v>
       </c>
       <c r="C289" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5419,10 +5410,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46209</v>
+        <v>46091</v>
       </c>
       <c r="C290" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5430,7 +5421,7 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46237</v>
+        <v>46090</v>
       </c>
       <c r="C291" s="9">
         <v>1</v>
@@ -5441,7 +5432,7 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46148</v>
+        <v>46020</v>
       </c>
       <c r="C292" s="6">
         <v>2</v>
@@ -5452,10 +5443,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46105</v>
+        <v>46015</v>
       </c>
       <c r="C293" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5463,10 +5454,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46087</v>
+        <v>46217</v>
       </c>
       <c r="C294" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5474,10 +5465,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46107</v>
+        <v>46078</v>
       </c>
       <c r="C295" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5485,10 +5476,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46086</v>
+        <v>46209</v>
       </c>
       <c r="C296" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5496,7 +5487,7 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46106</v>
+        <v>46237</v>
       </c>
       <c r="C297" s="9">
         <v>1</v>
@@ -5507,10 +5498,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="C298" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5518,10 +5509,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C299" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5529,10 +5520,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46118</v>
+        <v>46087</v>
       </c>
       <c r="C300" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5540,10 +5531,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46231</v>
+        <v>46107</v>
       </c>
       <c r="C301" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5551,10 +5542,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="C302" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5562,7 +5553,7 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46182</v>
+        <v>46106</v>
       </c>
       <c r="C303" s="9">
         <v>1</v>
@@ -5573,10 +5564,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46188</v>
+        <v>46150</v>
       </c>
       <c r="C304" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5584,10 +5575,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46154</v>
+        <v>46104</v>
       </c>
       <c r="C305" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5595,10 +5586,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C306" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5606,7 +5597,7 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46122</v>
+        <v>46231</v>
       </c>
       <c r="C307" s="9">
         <v>1</v>
@@ -5617,10 +5608,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C308" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5628,10 +5619,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46156</v>
+        <v>46182</v>
       </c>
       <c r="C309" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5639,7 +5630,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46133</v>
+        <v>46188</v>
       </c>
       <c r="C310" s="6">
         <v>1</v>
@@ -5650,7 +5641,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46189</v>
+        <v>46154</v>
       </c>
       <c r="C311" s="9">
         <v>1</v>
@@ -5661,10 +5652,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46210</v>
+        <v>46093</v>
       </c>
       <c r="C312" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5672,7 +5663,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46232</v>
+        <v>46122</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5683,10 +5674,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="C314" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5694,10 +5685,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46022</v>
+        <v>46156</v>
       </c>
       <c r="C315" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5705,10 +5696,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46100</v>
+        <v>46287</v>
       </c>
       <c r="C316" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5716,7 +5707,7 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46101</v>
+        <v>46133</v>
       </c>
       <c r="C317" s="9">
         <v>1</v>
@@ -5727,10 +5718,10 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46097</v>
+        <v>46189</v>
       </c>
       <c r="C318" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -5738,10 +5729,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46077</v>
+        <v>46210</v>
       </c>
       <c r="C319" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5749,7 +5740,7 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46108</v>
+        <v>46232</v>
       </c>
       <c r="C320" s="6">
         <v>1</v>
@@ -5760,7 +5751,7 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46233</v>
+        <v>46126</v>
       </c>
       <c r="C321" s="9">
         <v>1</v>
@@ -5771,10 +5762,10 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46098</v>
+        <v>46022</v>
       </c>
       <c r="C322" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -5782,10 +5773,10 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="C323" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -5793,7 +5784,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46253</v>
+        <v>46101</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5804,10 +5795,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="C325" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5815,10 +5806,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46244</v>
+        <v>46077</v>
       </c>
       <c r="C326" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5826,7 +5817,7 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46153</v>
+        <v>46108</v>
       </c>
       <c r="C327" s="9">
         <v>1</v>
@@ -5837,7 +5828,7 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46031</v>
+        <v>46233</v>
       </c>
       <c r="C328" s="6">
         <v>1</v>
@@ -5848,9 +5839,86 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C329" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B330" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C330" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B331" s="8">
+        <v>46253</v>
+      </c>
+      <c r="C331" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B332" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C332" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B333" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C333" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B334" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C334" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C335" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B336" s="5">
         <v>46155</v>
       </c>
-      <c r="C329" s="9">
+      <c r="C336" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5971,7 +6039,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6039,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -6070,10 +6138,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6141,7 +6209,7 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -6152,7 +6220,7 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -6186,7 +6254,7 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -6260,7 +6328,7 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -6305,7 +6373,7 @@
         <v>11</v>
       </c>
       <c r="C26">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -6396,7 +6464,7 @@
         <v>5</v>
       </c>
       <c r="E31">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -6424,7 +6492,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D33">
         <v>7</v>
@@ -6478,7 +6546,7 @@
         <v>107</v>
       </c>
       <c r="D36">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36">
         <v>65</v>
@@ -6515,7 +6583,7 @@
         <v>10</v>
       </c>
       <c r="E38">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6558,7 +6626,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6613,7 +6681,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -6624,7 +6692,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -6635,10 +6703,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -6646,7 +6714,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -6657,7 +6725,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -6668,7 +6736,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -6679,7 +6747,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6690,7 +6758,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6921,7 +6989,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6987,10 +7055,10 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -7218,7 +7286,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7515,7 +7583,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7713,7 +7781,7 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C106">
         <v>6</v>
@@ -7724,7 +7792,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C107">
         <v>6</v>
@@ -7746,7 +7814,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C109">
         <v>5</v>
@@ -7757,7 +7825,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C110">
         <v>5</v>
@@ -7768,7 +7836,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -7779,7 +7847,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -7790,7 +7858,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -7801,7 +7869,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -7812,7 +7880,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -7856,7 +7924,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -7878,7 +7946,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7900,7 +7968,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7944,7 +8012,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -8021,7 +8089,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>178</v>
+        <v>268</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8032,7 +8100,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -8043,7 +8111,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -8054,7 +8122,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -8065,7 +8133,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -8076,7 +8144,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8087,7 +8155,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8098,7 +8166,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -8109,7 +8177,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8120,7 +8188,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -8131,7 +8199,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -8142,7 +8210,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -8153,7 +8221,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8164,7 +8232,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8175,7 +8243,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8186,7 +8254,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8197,7 +8265,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8208,7 +8276,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8219,7 +8287,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8230,7 +8298,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8241,7 +8309,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8252,7 +8320,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8263,7 +8331,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8285,7 +8353,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -8296,7 +8364,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8307,7 +8375,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8318,7 +8386,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8329,7 +8397,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8340,7 +8408,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8351,7 +8419,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>271</v>
+        <v>141</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8362,7 +8430,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8373,7 +8441,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8384,7 +8452,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8395,7 +8463,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8406,7 +8474,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8417,7 +8485,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8439,7 +8507,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8450,7 +8518,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8461,7 +8529,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8472,7 +8540,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8483,7 +8551,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8494,7 +8562,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8505,7 +8573,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8516,7 +8584,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8527,7 +8595,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>138</v>
+        <v>67</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8538,7 +8606,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8549,7 +8617,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8560,7 +8628,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8571,7 +8639,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8582,7 +8650,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8593,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -8601,13 +8669,13 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C187">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8615,10 +8683,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C188">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8626,10 +8694,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C189">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8637,7 +8705,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C190">
         <v>16</v>
@@ -8648,10 +8716,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C191">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -8659,10 +8727,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="C192">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8670,10 +8738,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C193">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8684,7 +8752,7 @@
         <v>188</v>
       </c>
       <c r="C194">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -8692,10 +8760,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="C195">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8703,7 +8771,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C196">
         <v>11</v>
@@ -8714,10 +8782,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C197">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -8725,7 +8793,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C198">
         <v>10</v>
@@ -8736,10 +8804,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C199">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8747,7 +8815,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C200">
         <v>9</v>
@@ -8758,10 +8826,10 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C201">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -8769,10 +8837,10 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C202">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -8780,10 +8848,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8791,7 +8859,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="C204">
         <v>7</v>
@@ -8802,10 +8870,10 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="C205">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -8813,10 +8881,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>194</v>
+        <v>84</v>
       </c>
       <c r="C206">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -8824,10 +8892,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8835,7 +8903,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -8846,7 +8914,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8868,7 +8936,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C211">
         <v>5</v>
@@ -8879,7 +8947,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8890,7 +8958,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8901,7 +8969,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -8912,7 +8980,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -8923,10 +8991,10 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C216">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -8934,7 +9002,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8945,7 +9013,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8956,7 +9024,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8967,7 +9035,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8978,7 +9046,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8989,7 +9057,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -9000,7 +9068,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9011,7 +9079,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>289</v>
+        <v>74</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -9022,7 +9090,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -9033,10 +9101,10 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -9044,7 +9112,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -9055,7 +9123,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>201</v>
+        <v>64</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -9066,7 +9134,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9077,7 +9145,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9088,7 +9156,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9099,7 +9167,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -9110,10 +9178,10 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -9121,7 +9189,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -9132,7 +9200,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>207</v>
+        <v>112</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9143,7 +9211,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9154,7 +9222,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9165,7 +9233,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9176,7 +9244,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9187,7 +9255,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>235</v>
+        <v>123</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9198,7 +9266,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9209,7 +9277,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9220,7 +9288,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>202</v>
+        <v>58</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9231,7 +9299,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>58</v>
+        <v>203</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9242,7 +9310,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9253,7 +9321,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9264,7 +9332,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9275,7 +9343,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9286,7 +9354,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9297,7 +9365,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9308,7 +9376,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>233</v>
+        <v>69</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9319,7 +9387,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>123</v>
+        <v>225</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9330,7 +9398,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9341,7 +9409,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9352,7 +9420,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9363,7 +9431,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9374,7 +9442,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9385,7 +9453,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9396,7 +9464,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>112</v>
+        <v>226</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9407,7 +9475,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9418,7 +9486,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9429,7 +9497,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9440,7 +9508,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9451,7 +9519,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9462,7 +9530,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9473,7 +9541,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9484,7 +9552,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9495,7 +9563,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9506,7 +9574,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>219</v>
+        <v>116</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9517,7 +9585,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9528,7 +9596,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9539,7 +9607,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9550,7 +9618,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9583,7 +9651,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C276">
         <v>10</v>
@@ -9597,7 +9665,7 @@
         <v>101</v>
       </c>
       <c r="C277">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -9605,7 +9673,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C278">
         <v>8</v>
@@ -9616,7 +9684,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C279">
         <v>6</v>
@@ -9638,7 +9706,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -9660,7 +9728,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9671,7 +9739,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9682,7 +9750,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -9693,7 +9761,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -9704,7 +9772,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -9726,7 +9794,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -9737,7 +9805,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9748,7 +9816,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>113</v>
+        <v>241</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9759,7 +9827,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>124</v>
+        <v>240</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9770,7 +9838,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>243</v>
+        <v>123</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9781,7 +9849,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9792,7 +9860,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9803,7 +9871,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9814,7 +9882,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9825,7 +9893,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9836,7 +9904,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9858,7 +9926,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9869,7 +9937,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9880,7 +9948,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9891,7 +9959,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9902,7 +9970,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>245</v>
+        <v>191</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9913,7 +9981,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9924,7 +9992,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9935,7 +10003,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>84</v>
+        <v>245</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9946,7 +10014,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9957,7 +10025,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9968,7 +10036,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9979,7 +10047,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>244</v>
+        <v>70</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9990,7 +10058,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -10001,7 +10069,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -10012,7 +10080,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -10023,7 +10091,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -10034,7 +10102,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>268</v>
+        <v>112</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -10045,7 +10113,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>135</v>
+        <v>249</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10056,7 +10124,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10067,7 +10135,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10078,7 +10146,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10089,7 +10157,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>257</v>
+        <v>134</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10100,7 +10168,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10111,7 +10179,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10122,7 +10190,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10133,7 +10201,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10144,7 +10212,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10155,7 +10223,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>179</v>
+        <v>251</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10166,7 +10234,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10177,7 +10245,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>144</v>
+        <v>266</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10188,7 +10256,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10199,7 +10267,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10210,7 +10278,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10221,7 +10289,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10232,7 +10300,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10254,7 +10322,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10265,7 +10333,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>91</v>
+        <v>265</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10276,7 +10344,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10287,7 +10355,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>267</v>
+        <v>91</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10298,7 +10366,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10309,7 +10377,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10320,7 +10388,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10331,7 +10399,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>169</v>
+        <v>252</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10342,7 +10410,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>252</v>
+        <v>143</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10353,7 +10421,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10364,7 +10432,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10375,7 +10443,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10386,7 +10454,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10397,22 +10465,14 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C350">
         <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B351" t="s">
-        <v>264</v>
-      </c>
-      <c r="C351">
-        <v>1</v>
-      </c>
+      <c r="A351" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10449,7 +10509,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10482,7 +10542,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10493,7 +10553,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10515,7 +10575,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10537,7 +10597,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10548,7 +10608,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -10573,10 +10633,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10584,7 +10644,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C2">
         <v>66</v>
@@ -10595,10 +10655,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C3">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10606,7 +10666,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -10617,10 +10677,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10628,7 +10688,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -10639,7 +10699,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -10650,7 +10710,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -10661,10 +10721,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C9">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10672,10 +10732,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10683,7 +10743,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C11">
         <v>29</v>
@@ -10694,10 +10754,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C12">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -10705,7 +10765,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -10716,10 +10776,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C14">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10727,7 +10787,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -10738,10 +10798,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -10749,10 +10809,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C17">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -10760,7 +10820,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C18">
         <v>36</v>
@@ -10771,7 +10831,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -10782,7 +10842,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -10793,7 +10853,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -10804,7 +10864,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -10815,7 +10875,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -10826,7 +10886,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C24">
         <v>40</v>
@@ -10837,10 +10897,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C25">
-        <v>867</v>
+        <v>864</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10848,7 +10908,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -10859,10 +10919,10 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C27">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -10870,10 +10930,10 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C28">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -10881,7 +10941,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C29">
         <v>79</v>
@@ -10892,7 +10952,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -10903,7 +10963,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10914,7 +10974,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -10925,7 +10985,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10936,7 +10996,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C34">
         <v>704</v>
@@ -10947,7 +11007,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -10958,7 +11018,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C36">
         <v>22</v>
@@ -10969,7 +11029,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C37">
         <v>62</v>
@@ -10980,7 +11040,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C38">
         <v>58</v>
@@ -10991,7 +11051,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C39">
         <v>25</v>
@@ -11002,7 +11062,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -11013,7 +11073,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -11024,7 +11084,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -11035,7 +11095,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -11067,7 +11127,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11174,7 +11234,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -11284,7 +11344,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -11394,7 +11454,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="565" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF99CF4A-C45E-4AE5-A8A4-3EEF35653D76}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F5C7921-131F-464F-A566-82208D75264B}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -500,9 +500,6 @@
   </si>
   <si>
     <t>Escuela de Lenguaje Yamanqui</t>
-  </si>
-  <si>
-    <t>Escuela República del Ecuador</t>
   </si>
   <si>
     <t>Colegio Madres Dominicas</t>
@@ -1777,10 +1774,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14">
-        <v>1.081</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1981,10 +1978,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.98799999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1998,10 +1995,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E27">
-        <v>0.97199999999999998</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2100,10 +2097,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.0329999999999999</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2218,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C336"/>
+  <dimension ref="A1:C338"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2880,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46148</v>
+        <v>46289</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2891,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2902,7 +2899,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -2913,7 +2910,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2924,10 +2921,10 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C64" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2935,10 +2932,10 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C65" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2946,7 +2943,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2957,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2968,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2979,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2990,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -3001,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3012,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3023,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3034,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3042,13 +3039,13 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C75" s="9">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3056,10 +3053,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C76" s="6">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3067,10 +3064,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C77" s="9">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3078,10 +3075,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C78" s="6">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3089,10 +3086,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C79" s="9">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3100,10 +3097,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C80" s="6">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3111,10 +3108,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C81" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3122,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C82" s="6">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3133,10 +3130,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C83" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3144,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C84" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3155,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C85" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3166,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C86" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3177,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C87" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3188,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C88" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3199,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C89" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3210,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C90" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3221,7 +3218,7 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C91" s="9">
         <v>2</v>
@@ -3232,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C92" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3243,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C93" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3254,7 +3251,7 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
@@ -3265,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C95" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3276,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C96" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3287,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C97" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3298,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C98" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3309,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C99" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3320,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46217</v>
+        <v>46078</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3331,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46272</v>
+        <v>46217</v>
       </c>
       <c r="C101" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3342,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C102" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3353,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C103" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3364,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C104" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3375,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C105" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3386,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C106" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3397,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C107" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3408,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C108" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3419,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C109" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3430,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C110" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3441,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C111" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3452,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3463,7 +3460,7 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C113" s="9">
         <v>2</v>
@@ -3474,10 +3471,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C114" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3485,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C115" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3496,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3507,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3518,10 +3515,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3529,7 +3526,7 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -3540,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3551,10 +3548,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3562,10 +3559,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3573,10 +3570,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C123" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3584,10 +3581,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3595,7 +3592,7 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3606,7 +3603,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3617,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3628,10 +3625,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C128" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3639,10 +3636,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C129" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3650,10 +3647,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C130" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3661,10 +3658,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C131" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3672,10 +3669,10 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46086</v>
+        <v>46212</v>
       </c>
       <c r="C132" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3683,10 +3680,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46227</v>
+        <v>46288</v>
       </c>
       <c r="C133" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3694,10 +3691,10 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46188</v>
+        <v>46086</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3705,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46147</v>
+        <v>46227</v>
       </c>
       <c r="C135" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3716,7 +3713,7 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46134</v>
+        <v>46188</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3727,7 +3724,7 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3738,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46190</v>
+        <v>46134</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3749,7 +3746,7 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46225</v>
+        <v>46182</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3757,24 +3754,24 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46003</v>
+        <v>46190</v>
       </c>
       <c r="C140" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="C141" s="9">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3782,10 +3779,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C142" s="6">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3793,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C143" s="9">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3804,10 +3801,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C144" s="6">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3815,10 +3812,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C145" s="9">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3826,10 +3823,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C146" s="6">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3837,10 +3834,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C147" s="9">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3848,10 +3845,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C148" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3859,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C149" s="9">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3870,7 +3867,7 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C150" s="6">
         <v>2</v>
@@ -3881,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C151" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3892,7 +3889,7 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46212</v>
+        <v>46013</v>
       </c>
       <c r="C152" s="6">
         <v>2</v>
@@ -3903,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C153" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3914,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="C154" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3925,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46209</v>
+        <v>46077</v>
       </c>
       <c r="C155" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3936,10 +3933,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="C156" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3947,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3958,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C158" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3969,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C159" s="9">
         <v>1</v>
@@ -3980,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C160" s="6">
         <v>1</v>
@@ -3991,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C161" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4002,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C162" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4013,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C163" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4024,7 +4021,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C164" s="6">
         <v>4</v>
@@ -4035,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C165" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4046,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C166" s="6">
         <v>4</v>
@@ -4057,7 +4054,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46262</v>
+        <v>46134</v>
       </c>
       <c r="C167" s="9">
         <v>2</v>
@@ -4068,10 +4065,10 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C168" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4079,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46114</v>
+        <v>46262</v>
       </c>
       <c r="C169" s="9">
         <v>2</v>
@@ -4090,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4101,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46287</v>
+        <v>46114</v>
       </c>
       <c r="C171" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4112,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4123,7 +4120,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46087</v>
+        <v>46287</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4134,7 +4131,7 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46286</v>
+        <v>46127</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4145,7 +4142,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4156,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46267</v>
+        <v>46286</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4167,7 +4164,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4178,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46168</v>
+        <v>46267</v>
       </c>
       <c r="C178" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4189,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46248</v>
+        <v>46020</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4200,10 +4197,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46252</v>
+        <v>46168</v>
       </c>
       <c r="C180" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4211,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46097</v>
+        <v>46248</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4222,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46177</v>
+        <v>46252</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4233,10 +4230,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C183" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4244,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46129</v>
+        <v>46177</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4255,10 +4252,10 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46080</v>
+        <v>46161</v>
       </c>
       <c r="C185" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4266,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46120</v>
+        <v>46129</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4277,7 +4274,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4288,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46155</v>
+        <v>46120</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4299,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4310,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4321,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46085</v>
+        <v>46150</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4332,7 +4329,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4343,10 +4340,10 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46126</v>
+        <v>46085</v>
       </c>
       <c r="C193" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4354,10 +4351,10 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C194" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4365,10 +4362,10 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46258</v>
+        <v>46126</v>
       </c>
       <c r="C195" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4376,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46192</v>
+        <v>46118</v>
       </c>
       <c r="C196" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4387,7 +4384,7 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46079</v>
+        <v>46258</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4395,24 +4392,24 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46003</v>
+        <v>46192</v>
       </c>
       <c r="C198" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C199" s="9">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4420,10 +4417,10 @@
         <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C200" s="6">
-        <v>167</v>
+        <v>91</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4431,10 +4428,10 @@
         <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C201" s="9">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4442,10 +4439,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C202" s="6">
-        <v>15</v>
+        <v>167</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4453,10 +4450,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C203" s="9">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4464,10 +4461,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C204" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4475,10 +4472,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C205" s="9">
-        <v>18</v>
+        <v>168</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4486,10 +4483,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C206" s="6">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4497,10 +4494,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C207" s="9">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4508,10 +4505,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C208" s="6">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4519,10 +4516,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46258</v>
+        <v>46007</v>
       </c>
       <c r="C209" s="9">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4530,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C210" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4541,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46209</v>
+        <v>46258</v>
       </c>
       <c r="C211" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4552,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46227</v>
+        <v>46080</v>
       </c>
       <c r="C212" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4563,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46090</v>
+        <v>46209</v>
       </c>
       <c r="C213" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4574,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="C214" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4585,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C215" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4596,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46015</v>
+        <v>46192</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4607,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C217" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4618,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C218" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4629,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="C219" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4640,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46265</v>
+        <v>46098</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4651,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C221" s="9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4662,7 +4659,7 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C222" s="6">
         <v>1</v>
@@ -4673,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C223" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4684,10 +4681,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46083</v>
+        <v>46260</v>
       </c>
       <c r="C224" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4695,10 +4692,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46255</v>
+        <v>46128</v>
       </c>
       <c r="C225" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4706,7 +4703,7 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C226" s="6">
         <v>7</v>
@@ -4717,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4728,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="C228" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4739,7 +4736,7 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="C229" s="9">
         <v>1</v>
@@ -4750,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="C230" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4761,7 +4758,7 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46154</v>
+        <v>46273</v>
       </c>
       <c r="C231" s="9">
         <v>1</v>
@@ -4772,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46226</v>
+        <v>46099</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,7 +4780,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C233" s="9">
         <v>1</v>
@@ -4794,7 +4791,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46022</v>
+        <v>46226</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4805,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46120</v>
+        <v>46092</v>
       </c>
       <c r="C235" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46237</v>
+        <v>46022</v>
       </c>
       <c r="C236" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,10 +4824,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C237" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46114</v>
+        <v>46237</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4849,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46216</v>
+        <v>46077</v>
       </c>
       <c r="C239" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4860,7 +4857,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -4871,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46276</v>
+        <v>46216</v>
       </c>
       <c r="C241" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4882,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C242" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4893,7 +4890,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46106</v>
+        <v>46276</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4904,10 +4901,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46287</v>
+        <v>46020</v>
       </c>
       <c r="C244" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4915,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46211</v>
+        <v>46106</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4926,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46239</v>
+        <v>46287</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4937,7 +4934,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46155</v>
+        <v>46211</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -4948,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46210</v>
+        <v>46239</v>
       </c>
       <c r="C248" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4959,7 +4956,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4970,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46132</v>
+        <v>46210</v>
       </c>
       <c r="C250" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4981,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4992,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46148</v>
+        <v>46132</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5003,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46118</v>
+        <v>46108</v>
       </c>
       <c r="C253" s="9">
         <v>1</v>
@@ -5014,7 +5011,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46035</v>
+        <v>46148</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5025,7 +5022,7 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46181</v>
+        <v>46118</v>
       </c>
       <c r="C255" s="9">
         <v>1</v>
@@ -5036,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46087</v>
+        <v>46035</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5047,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46030</v>
+        <v>46181</v>
       </c>
       <c r="C257" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46031</v>
+        <v>46087</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5069,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46204</v>
+        <v>46030</v>
       </c>
       <c r="C259" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5080,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46176</v>
+        <v>46031</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
@@ -5091,7 +5088,7 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46286</v>
+        <v>46204</v>
       </c>
       <c r="C261" s="9">
         <v>1</v>
@@ -5102,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46101</v>
+        <v>46176</v>
       </c>
       <c r="C262" s="6">
         <v>1</v>
@@ -5113,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46213</v>
+        <v>46286</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5124,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5132,24 +5129,24 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46001</v>
+        <v>46213</v>
       </c>
       <c r="C265" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C266" s="6">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,10 +5154,10 @@
         <v>21</v>
       </c>
       <c r="B267" s="8">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C267" s="9">
-        <v>70</v>
+        <v>151</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -5168,10 +5165,10 @@
         <v>21</v>
       </c>
       <c r="B268" s="5">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C268" s="6">
-        <v>109</v>
+        <v>38</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5179,10 +5176,10 @@
         <v>21</v>
       </c>
       <c r="B269" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C269" s="9">
-        <v>145</v>
+        <v>70</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5190,10 +5187,10 @@
         <v>21</v>
       </c>
       <c r="B270" s="5">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C270" s="6">
-        <v>45</v>
+        <v>109</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5201,10 +5198,10 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C271" s="9">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5212,10 +5209,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C272" s="6">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5223,10 +5220,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C273" s="9">
-        <v>25</v>
+        <v>127</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5234,10 +5231,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="C274" s="6">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5245,10 +5242,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C275" s="9">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5256,10 +5253,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C276" s="6">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5267,10 +5264,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C277" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5278,10 +5275,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C278" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5289,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C279" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5300,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46079</v>
+        <v>46014</v>
       </c>
       <c r="C280" s="6">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5311,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="C281" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5322,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="C282" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5333,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46085</v>
+        <v>46167</v>
       </c>
       <c r="C283" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5344,7 +5341,7 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46120</v>
+        <v>46035</v>
       </c>
       <c r="C284" s="6">
         <v>2</v>
@@ -5355,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46114</v>
+        <v>46085</v>
       </c>
       <c r="C285" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5366,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="C286" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5377,7 +5374,7 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46192</v>
+        <v>46114</v>
       </c>
       <c r="C287" s="9">
         <v>1</v>
@@ -5388,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C288" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5399,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46127</v>
+        <v>46192</v>
       </c>
       <c r="C289" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5410,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="C290" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5421,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46090</v>
+        <v>46127</v>
       </c>
       <c r="C291" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5432,7 +5429,7 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46020</v>
+        <v>46091</v>
       </c>
       <c r="C292" s="6">
         <v>2</v>
@@ -5443,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C293" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5454,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46217</v>
+        <v>46020</v>
       </c>
       <c r="C294" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5465,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C295" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5476,10 +5473,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46209</v>
+        <v>46217</v>
       </c>
       <c r="C296" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5487,10 +5484,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46237</v>
+        <v>46078</v>
       </c>
       <c r="C297" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5498,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46148</v>
+        <v>46209</v>
       </c>
       <c r="C298" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5509,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46105</v>
+        <v>46237</v>
       </c>
       <c r="C299" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5520,10 +5517,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46087</v>
+        <v>46148</v>
       </c>
       <c r="C300" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5531,10 +5528,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="C301" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5542,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="C302" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5553,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C303" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5564,10 +5561,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46150</v>
+        <v>46086</v>
       </c>
       <c r="C304" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5575,10 +5572,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="C305" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5586,10 +5583,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46118</v>
+        <v>46150</v>
       </c>
       <c r="C306" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5597,10 +5594,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46231</v>
+        <v>46104</v>
       </c>
       <c r="C307" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5608,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C308" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5619,7 +5616,7 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46182</v>
+        <v>46231</v>
       </c>
       <c r="C309" s="9">
         <v>1</v>
@@ -5630,10 +5627,10 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46188</v>
+        <v>46076</v>
       </c>
       <c r="C310" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -5641,7 +5638,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="C311" s="9">
         <v>1</v>
@@ -5652,10 +5649,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46093</v>
+        <v>46188</v>
       </c>
       <c r="C312" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5663,7 +5660,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5674,7 +5671,7 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C314" s="6">
         <v>3</v>
@@ -5685,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C315" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5696,10 +5693,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46287</v>
+        <v>46092</v>
       </c>
       <c r="C316" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5707,10 +5704,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="C317" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5718,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46189</v>
+        <v>46287</v>
       </c>
       <c r="C318" s="6">
         <v>1</v>
@@ -5729,7 +5726,7 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46210</v>
+        <v>46133</v>
       </c>
       <c r="C319" s="9">
         <v>1</v>
@@ -5740,7 +5737,7 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46232</v>
+        <v>46189</v>
       </c>
       <c r="C320" s="6">
         <v>1</v>
@@ -5751,7 +5748,7 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46126</v>
+        <v>46210</v>
       </c>
       <c r="C321" s="9">
         <v>1</v>
@@ -5762,7 +5759,7 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46022</v>
+        <v>46232</v>
       </c>
       <c r="C322" s="6">
         <v>1</v>
@@ -5773,10 +5770,10 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46100</v>
+        <v>46126</v>
       </c>
       <c r="C323" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -5784,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5795,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C325" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5806,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46077</v>
+        <v>46101</v>
       </c>
       <c r="C326" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5817,10 +5814,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C327" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5828,10 +5825,10 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46233</v>
+        <v>46077</v>
       </c>
       <c r="C328" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -5839,10 +5836,10 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C329" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -5850,7 +5847,7 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46113</v>
+        <v>46233</v>
       </c>
       <c r="C330" s="6">
         <v>1</v>
@@ -5861,10 +5858,10 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46253</v>
+        <v>46098</v>
       </c>
       <c r="C331" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -5872,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C332" s="6">
         <v>1</v>
@@ -5883,7 +5880,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5894,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5905,7 +5902,7 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46031</v>
+        <v>46244</v>
       </c>
       <c r="C335" s="9">
         <v>1</v>
@@ -5916,9 +5913,31 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C336" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B337" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C337" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B338" s="5">
         <v>46155</v>
       </c>
-      <c r="C336" s="6">
+      <c r="C338" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6175,7 +6194,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6373,7 +6392,7 @@
         <v>11</v>
       </c>
       <c r="C26">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -6390,7 +6409,7 @@
         <v>12</v>
       </c>
       <c r="C27">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -6498,7 +6517,7 @@
         <v>7</v>
       </c>
       <c r="E33">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6626,7 +6645,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6989,7 +7008,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -7055,7 +7074,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C40">
         <v>11</v>
@@ -7286,7 +7305,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7583,7 +7602,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7924,7 +7943,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -8045,7 +8064,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -8056,7 +8075,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8078,7 +8097,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -8089,7 +8108,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8100,7 +8119,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -8133,7 +8152,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -8144,7 +8163,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8155,7 +8174,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8177,7 +8196,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8188,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -8221,7 +8240,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8243,7 +8262,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8254,7 +8273,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8265,7 +8284,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8276,7 +8295,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8287,7 +8306,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8298,7 +8317,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8309,7 +8328,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8320,7 +8339,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8331,7 +8350,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8364,7 +8383,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8375,7 +8394,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8386,7 +8405,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8397,7 +8416,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8408,7 +8427,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8419,7 +8438,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8430,7 +8449,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8441,7 +8460,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8463,7 +8482,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8474,7 +8493,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8485,7 +8504,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8496,7 +8515,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8507,7 +8526,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8518,7 +8537,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8529,7 +8548,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8540,7 +8559,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>235</v>
+        <v>147</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8551,7 +8570,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8562,7 +8581,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8573,7 +8592,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8595,7 +8614,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8617,7 +8636,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8628,7 +8647,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8639,7 +8658,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8650,7 +8669,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8661,7 +8680,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -8669,13 +8688,13 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C187">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8683,10 +8702,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C188">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8694,10 +8713,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C189">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8705,7 +8724,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="C190">
         <v>16</v>
@@ -8716,10 +8735,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="C191">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -8727,10 +8746,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>66</v>
+        <v>185</v>
       </c>
       <c r="C192">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8738,10 +8757,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C193">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8749,10 +8768,10 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C194">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -8760,10 +8779,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="C195">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8771,7 +8790,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C196">
         <v>11</v>
@@ -8782,10 +8801,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C197">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -8804,10 +8823,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C199">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8815,7 +8834,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="C200">
         <v>9</v>
@@ -8826,7 +8845,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="C201">
         <v>9</v>
@@ -8837,10 +8856,10 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C202">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -8848,10 +8867,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="C203">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8859,7 +8878,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="C204">
         <v>7</v>
@@ -8870,7 +8889,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C205">
         <v>7</v>
@@ -8881,10 +8900,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="C206">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -8892,10 +8911,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C207">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8914,7 +8933,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8936,10 +8955,10 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C211">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -8947,7 +8966,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8969,7 +8988,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -8980,7 +8999,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -8991,10 +9010,10 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C216">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -9002,7 +9021,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -9013,7 +9032,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -9024,7 +9043,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -9035,7 +9054,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -9046,7 +9065,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -9057,7 +9076,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -9068,7 +9087,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9079,7 +9098,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -9090,7 +9109,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>194</v>
+        <v>285</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -9101,10 +9120,10 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>286</v>
+        <v>199</v>
       </c>
       <c r="C226">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -9134,7 +9153,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9145,7 +9164,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9156,7 +9175,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9167,7 +9186,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -9178,10 +9197,10 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C233">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -9189,7 +9208,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -9200,7 +9219,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9211,7 +9230,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9222,7 +9241,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9233,7 +9252,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9244,7 +9263,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9255,7 +9274,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9266,7 +9285,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>118</v>
+        <v>212</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9277,7 +9296,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9288,7 +9307,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9299,7 +9318,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9310,7 +9329,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9321,7 +9340,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9332,7 +9351,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9343,7 +9362,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9354,7 +9373,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9365,7 +9384,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9376,7 +9395,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9387,7 +9406,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>225</v>
+        <v>69</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9398,7 +9417,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9409,7 +9428,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9420,7 +9439,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9431,7 +9450,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9442,7 +9461,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9453,7 +9472,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9464,7 +9483,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9486,7 +9505,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9497,7 +9516,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9519,7 +9538,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9530,7 +9549,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9541,7 +9560,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9552,7 +9571,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9563,7 +9582,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9574,7 +9593,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9585,7 +9604,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9596,7 +9615,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9607,7 +9626,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9618,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9651,7 +9670,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C276">
         <v>10</v>
@@ -9673,7 +9692,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C278">
         <v>8</v>
@@ -9684,7 +9703,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C279">
         <v>6</v>
@@ -9706,7 +9725,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -9717,7 +9736,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9739,7 +9758,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9761,7 +9780,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -9772,7 +9791,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -9805,7 +9824,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9816,7 +9835,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9827,7 +9846,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9849,7 +9868,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9926,7 +9945,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9937,7 +9956,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9948,7 +9967,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9970,7 +9989,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9981,7 +10000,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -10003,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -10025,7 +10044,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -10036,7 +10055,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -10069,7 +10088,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -10080,7 +10099,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -10091,7 +10110,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -10113,7 +10132,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10124,7 +10143,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10135,7 +10154,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10146,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10168,7 +10187,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10179,7 +10198,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10190,7 +10209,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10201,7 +10220,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10212,7 +10231,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10223,7 +10242,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10234,7 +10253,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10245,7 +10264,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10256,7 +10275,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10267,7 +10286,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10289,7 +10308,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10300,7 +10319,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10333,7 +10352,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10344,7 +10363,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10366,7 +10385,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10377,7 +10396,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10388,7 +10407,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10399,7 +10418,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10432,7 +10451,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10443,7 +10462,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10454,7 +10473,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10465,7 +10484,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -10542,7 +10561,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10553,7 +10572,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10586,7 +10605,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10633,10 +10652,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" t="s">
         <v>270</v>
-      </c>
-      <c r="C1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10644,7 +10663,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C2">
         <v>66</v>
@@ -10655,7 +10674,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C3">
         <v>512</v>
@@ -10666,7 +10685,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -10677,7 +10696,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C5">
         <v>13</v>
@@ -10688,7 +10707,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -10699,7 +10718,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -10710,7 +10729,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C8">
         <v>28</v>
@@ -10721,10 +10740,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C9">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10732,7 +10751,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C10">
         <v>27</v>
@@ -10743,7 +10762,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C11">
         <v>29</v>
@@ -10754,7 +10773,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C12">
         <v>28</v>
@@ -10765,7 +10784,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -10776,10 +10795,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10787,7 +10806,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -10798,7 +10817,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -10809,7 +10828,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C17">
         <v>25</v>
@@ -10820,10 +10839,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C18">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -10831,7 +10850,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -10842,7 +10861,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -10853,7 +10872,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -10864,7 +10883,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -10875,7 +10894,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -10886,7 +10905,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C24">
         <v>40</v>
@@ -10897,7 +10916,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C25">
         <v>864</v>
@@ -10908,7 +10927,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -10919,7 +10938,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C27">
         <v>115</v>
@@ -10930,7 +10949,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C28">
         <v>140</v>
@@ -10941,10 +10960,10 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C29">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -10952,7 +10971,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -10963,7 +10982,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10974,7 +10993,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -10985,7 +11004,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10996,7 +11015,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C34">
         <v>704</v>
@@ -11007,7 +11026,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -11018,7 +11037,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C36">
         <v>22</v>
@@ -11029,7 +11048,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C37">
         <v>62</v>
@@ -11040,7 +11059,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C38">
         <v>58</v>
@@ -11051,7 +11070,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C39">
         <v>25</v>
@@ -11062,7 +11081,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -11073,7 +11092,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -11084,7 +11103,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -11095,7 +11114,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -11127,7 +11146,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11234,7 +11253,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -11344,7 +11363,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -11454,7 +11473,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F5C7921-131F-464F-A566-82208D75264B}"/>
+  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21A71EFD-47D3-4B08-B93E-21C841A6FCCF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1621,10 +1621,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5">
-        <v>1.294</v>
+        <v>1.2649999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1859,10 +1859,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2012,10 +2012,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28">
-        <v>1.0289999999999999</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2029,10 +2029,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E29">
-        <v>1.0620000000000001</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E32">
-        <v>1.0660000000000001</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C338"/>
+  <dimension ref="A1:C342"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2844,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46090</v>
+        <v>46290</v>
       </c>
       <c r="C57" s="9">
         <v>3</v>
@@ -2855,10 +2855,10 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46210</v>
+        <v>46090</v>
       </c>
       <c r="C58" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2866,10 +2866,10 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C59" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2877,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="C60" s="6">
         <v>1</v>
@@ -2888,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46148</v>
+        <v>46289</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2899,7 +2899,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -2910,7 +2910,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2921,7 +2921,7 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -2932,10 +2932,10 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C65" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2943,10 +2943,10 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C66" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2954,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2965,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2976,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -2998,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3031,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B76" s="5">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C76" s="6">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3064,10 +3064,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C77" s="9">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3075,10 +3075,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C78" s="6">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3086,10 +3086,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C79" s="9">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3097,10 +3097,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C80" s="6">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3108,10 +3108,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C81" s="9">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3119,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C82" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3130,10 +3130,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C83" s="9">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3141,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C84" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C85" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C86" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C87" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C88" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C89" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C90" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C91" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,7 +3229,7 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C92" s="6">
         <v>2</v>
@@ -3240,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C93" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3251,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C94" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3262,7 +3262,7 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C95" s="9">
         <v>1</v>
@@ -3273,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C96" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3284,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C97" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3295,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C98" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3317,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C100" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46217</v>
+        <v>46078</v>
       </c>
       <c r="C101" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3339,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46272</v>
+        <v>46217</v>
       </c>
       <c r="C102" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3350,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C103" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3361,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C104" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3372,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C105" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3383,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C106" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3394,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C107" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3405,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C108" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3416,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C109" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3427,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C110" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3438,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C111" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3449,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3460,10 +3460,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C113" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3471,7 +3471,7 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C114" s="6">
         <v>2</v>
@@ -3482,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C115" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3493,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C116" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3504,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3515,10 +3515,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C118" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3526,10 +3526,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3537,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3548,7 +3548,7 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C121" s="9">
         <v>1</v>
@@ -3559,10 +3559,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C122" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3570,10 +3570,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3581,10 +3581,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C124" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3592,10 +3592,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C125" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3603,7 +3603,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3625,7 +3625,7 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3636,10 +3636,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C129" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3647,10 +3647,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3658,10 +3658,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C131" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3669,10 +3669,10 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C132" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3680,10 +3680,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46288</v>
+        <v>46212</v>
       </c>
       <c r="C133" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3691,10 +3691,10 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46086</v>
+        <v>46288</v>
       </c>
       <c r="C134" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3702,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46227</v>
+        <v>46086</v>
       </c>
       <c r="C135" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3713,10 +3713,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46188</v>
+        <v>46227</v>
       </c>
       <c r="C136" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3724,7 +3724,7 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46147</v>
+        <v>46289</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46134</v>
+        <v>46188</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3746,7 +3746,7 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3757,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46190</v>
+        <v>46134</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3768,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46225</v>
+        <v>46182</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3776,24 +3776,24 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46003</v>
+        <v>46190</v>
       </c>
       <c r="C142" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="C143" s="9">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3801,10 +3801,10 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C144" s="6">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3812,10 +3812,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C145" s="9">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3823,10 +3823,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C146" s="6">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3834,10 +3834,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C147" s="9">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3845,10 +3845,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C148" s="6">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3856,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C149" s="9">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3867,10 +3867,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C150" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3878,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C151" s="9">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3889,7 +3889,7 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C152" s="6">
         <v>2</v>
@@ -3900,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C153" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,7 +3911,7 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46212</v>
+        <v>46013</v>
       </c>
       <c r="C154" s="6">
         <v>2</v>
@@ -3922,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C155" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3933,10 +3933,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="C156" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3944,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46209</v>
+        <v>46077</v>
       </c>
       <c r="C157" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3955,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="C158" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3966,10 +3966,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3977,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C160" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3988,7 +3988,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C161" s="9">
         <v>1</v>
@@ -3999,7 +3999,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C162" s="6">
         <v>1</v>
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C163" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4021,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C164" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4032,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C165" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4043,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C166" s="6">
         <v>4</v>
@@ -4054,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C167" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C168" s="6">
         <v>4</v>
@@ -4076,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46262</v>
+        <v>46134</v>
       </c>
       <c r="C169" s="9">
         <v>2</v>
@@ -4087,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C170" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4098,7 +4098,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46114</v>
+        <v>46262</v>
       </c>
       <c r="C171" s="9">
         <v>2</v>
@@ -4109,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4120,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46287</v>
+        <v>46114</v>
       </c>
       <c r="C173" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4131,7 +4131,7 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4142,7 +4142,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46087</v>
+        <v>46287</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46286</v>
+        <v>46127</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4164,7 +4164,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46267</v>
+        <v>46286</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4197,10 +4197,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46168</v>
+        <v>46267</v>
       </c>
       <c r="C180" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46248</v>
+        <v>46020</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4219,10 +4219,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46252</v>
+        <v>46168</v>
       </c>
       <c r="C182" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4230,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46097</v>
+        <v>46248</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46177</v>
+        <v>46252</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4252,10 +4252,10 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C185" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4263,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46129</v>
+        <v>46177</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4274,10 +4274,10 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46080</v>
+        <v>46161</v>
       </c>
       <c r="C187" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4285,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46120</v>
+        <v>46129</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4296,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46155</v>
+        <v>46120</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4318,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4329,7 +4329,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4340,7 +4340,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46085</v>
+        <v>46150</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4362,10 +4362,10 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46126</v>
+        <v>46085</v>
       </c>
       <c r="C195" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4373,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C196" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4384,10 +4384,10 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46258</v>
+        <v>46126</v>
       </c>
       <c r="C197" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4395,10 +4395,10 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46192</v>
+        <v>46118</v>
       </c>
       <c r="C198" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4406,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46079</v>
+        <v>46258</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4414,24 +4414,24 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46003</v>
+        <v>46192</v>
       </c>
       <c r="C200" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C201" s="9">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4439,10 +4439,10 @@
         <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C202" s="6">
-        <v>167</v>
+        <v>91</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4450,10 +4450,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C203" s="9">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4461,10 +4461,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C204" s="6">
-        <v>15</v>
+        <v>167</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4472,10 +4472,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C205" s="9">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4483,10 +4483,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C206" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4494,10 +4494,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C207" s="9">
-        <v>18</v>
+        <v>168</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4505,10 +4505,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C208" s="6">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C209" s="9">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4527,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C210" s="6">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4538,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46258</v>
+        <v>46007</v>
       </c>
       <c r="C211" s="9">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C212" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46209</v>
+        <v>46258</v>
       </c>
       <c r="C213" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46227</v>
+        <v>46080</v>
       </c>
       <c r="C214" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46090</v>
+        <v>46209</v>
       </c>
       <c r="C215" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="C216" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C217" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46015</v>
+        <v>46192</v>
       </c>
       <c r="C218" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C219" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4637,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C220" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4648,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="C221" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46265</v>
+        <v>46098</v>
       </c>
       <c r="C222" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4670,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C223" s="9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,7 +4681,7 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="C224" s="6">
         <v>1</v>
@@ -4692,10 +4692,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C225" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4703,10 +4703,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46083</v>
+        <v>46260</v>
       </c>
       <c r="C226" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46255</v>
+        <v>46128</v>
       </c>
       <c r="C227" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C228" s="6">
         <v>7</v>
@@ -4736,10 +4736,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="C229" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="C230" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,7 +4758,7 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46273</v>
+        <v>46262</v>
       </c>
       <c r="C231" s="9">
         <v>1</v>
@@ -4769,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="C232" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,7 +4780,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46154</v>
+        <v>46273</v>
       </c>
       <c r="C233" s="9">
         <v>1</v>
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46226</v>
+        <v>46099</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,7 +4802,7 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C235" s="9">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46022</v>
+        <v>46226</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4824,10 +4824,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46120</v>
+        <v>46092</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46237</v>
+        <v>46022</v>
       </c>
       <c r="C238" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C239" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4857,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46114</v>
+        <v>46237</v>
       </c>
       <c r="C240" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46216</v>
+        <v>46077</v>
       </c>
       <c r="C241" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,7 +4879,7 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -4890,10 +4890,10 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46276</v>
+        <v>46216</v>
       </c>
       <c r="C243" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,10 +4901,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C244" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46106</v>
+        <v>46289</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4923,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46287</v>
+        <v>46276</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,10 +4934,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46211</v>
+        <v>46020</v>
       </c>
       <c r="C247" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,7 +4945,7 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46239</v>
+        <v>46106</v>
       </c>
       <c r="C248" s="6">
         <v>1</v>
@@ -4956,10 +4956,10 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46155</v>
+        <v>46287</v>
       </c>
       <c r="C249" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C250" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46112</v>
+        <v>46239</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46132</v>
+        <v>46155</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5000,10 +5000,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46108</v>
+        <v>46210</v>
       </c>
       <c r="C253" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5011,7 +5011,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5022,7 +5022,7 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="C255" s="9">
         <v>1</v>
@@ -5033,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46035</v>
+        <v>46108</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5044,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46181</v>
+        <v>46148</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5055,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46087</v>
+        <v>46118</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5066,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="C259" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5077,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46031</v>
+        <v>46181</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
@@ -5088,7 +5088,7 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46204</v>
+        <v>46290</v>
       </c>
       <c r="C261" s="9">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46176</v>
+        <v>46087</v>
       </c>
       <c r="C262" s="6">
         <v>1</v>
@@ -5110,10 +5110,10 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46286</v>
+        <v>46030</v>
       </c>
       <c r="C263" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5121,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46101</v>
+        <v>46031</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5132,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46213</v>
+        <v>46204</v>
       </c>
       <c r="C265" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46142</v>
+        <v>46176</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5151,46 +5151,46 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46001</v>
+        <v>46286</v>
       </c>
       <c r="C267" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46008</v>
+        <v>46101</v>
       </c>
       <c r="C268" s="6">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46003</v>
+        <v>46213</v>
       </c>
       <c r="C269" s="9">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46002</v>
+        <v>46142</v>
       </c>
       <c r="C270" s="6">
-        <v>109</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5198,10 +5198,10 @@
         <v>21</v>
       </c>
       <c r="B271" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C271" s="9">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5209,10 +5209,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C272" s="6">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5220,10 +5220,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C273" s="9">
-        <v>127</v>
+        <v>70</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5231,10 +5231,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46084</v>
+        <v>46002</v>
       </c>
       <c r="C274" s="6">
-        <v>10</v>
+        <v>109</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5242,10 +5242,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="C275" s="9">
-        <v>25</v>
+        <v>145</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5253,10 +5253,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C276" s="6">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5264,10 +5264,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46021</v>
+        <v>46000</v>
       </c>
       <c r="C277" s="9">
-        <v>6</v>
+        <v>127</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5275,10 +5275,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46009</v>
+        <v>46084</v>
       </c>
       <c r="C278" s="6">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5286,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46083</v>
+        <v>46013</v>
       </c>
       <c r="C279" s="9">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5297,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C280" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5308,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46157</v>
+        <v>46021</v>
       </c>
       <c r="C281" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46079</v>
+        <v>46009</v>
       </c>
       <c r="C282" s="6">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46167</v>
+        <v>46083</v>
       </c>
       <c r="C283" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,10 +5341,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46035</v>
+        <v>46014</v>
       </c>
       <c r="C284" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5352,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46085</v>
+        <v>46157</v>
       </c>
       <c r="C285" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5363,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46120</v>
+        <v>46079</v>
       </c>
       <c r="C286" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,7 +5374,7 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46114</v>
+        <v>46167</v>
       </c>
       <c r="C287" s="9">
         <v>1</v>
@@ -5385,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46094</v>
+        <v>46035</v>
       </c>
       <c r="C288" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46192</v>
+        <v>46085</v>
       </c>
       <c r="C289" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46080</v>
+        <v>46120</v>
       </c>
       <c r="C290" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C291" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C292" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5440,7 +5440,7 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46090</v>
+        <v>46192</v>
       </c>
       <c r="C293" s="9">
         <v>1</v>
@@ -5451,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46020</v>
+        <v>46080</v>
       </c>
       <c r="C294" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46015</v>
+        <v>46127</v>
       </c>
       <c r="C295" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5473,10 +5473,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46217</v>
+        <v>46091</v>
       </c>
       <c r="C296" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5484,10 +5484,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C297" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5495,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46209</v>
+        <v>46020</v>
       </c>
       <c r="C298" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46237</v>
+        <v>46015</v>
       </c>
       <c r="C299" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5517,10 +5517,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46148</v>
+        <v>46217</v>
       </c>
       <c r="C300" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5528,10 +5528,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46105</v>
+        <v>46078</v>
       </c>
       <c r="C301" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5539,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46087</v>
+        <v>46209</v>
       </c>
       <c r="C302" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46107</v>
+        <v>46237</v>
       </c>
       <c r="C303" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5561,10 +5561,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46086</v>
+        <v>46148</v>
       </c>
       <c r="C304" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5572,10 +5572,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="C305" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5583,7 +5583,7 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46150</v>
+        <v>46087</v>
       </c>
       <c r="C306" s="6">
         <v>3</v>
@@ -5594,7 +5594,7 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="C307" s="9">
         <v>3</v>
@@ -5605,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46118</v>
+        <v>46086</v>
       </c>
       <c r="C308" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,7 +5616,7 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46231</v>
+        <v>46106</v>
       </c>
       <c r="C309" s="9">
         <v>1</v>
@@ -5627,10 +5627,10 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46076</v>
+        <v>46150</v>
       </c>
       <c r="C310" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -5638,10 +5638,10 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46182</v>
+        <v>46104</v>
       </c>
       <c r="C311" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -5649,7 +5649,7 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46188</v>
+        <v>46118</v>
       </c>
       <c r="C312" s="6">
         <v>1</v>
@@ -5660,7 +5660,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46154</v>
+        <v>46231</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5671,10 +5671,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="C314" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5682,7 +5682,7 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46122</v>
+        <v>46182</v>
       </c>
       <c r="C315" s="9">
         <v>1</v>
@@ -5693,10 +5693,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46092</v>
+        <v>46188</v>
       </c>
       <c r="C316" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5704,10 +5704,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="C317" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5715,10 +5715,10 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46287</v>
+        <v>46093</v>
       </c>
       <c r="C318" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -5726,7 +5726,7 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="C319" s="9">
         <v>1</v>
@@ -5737,10 +5737,10 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46189</v>
+        <v>46092</v>
       </c>
       <c r="C320" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -5748,10 +5748,10 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46210</v>
+        <v>46156</v>
       </c>
       <c r="C321" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,7 +5759,7 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46232</v>
+        <v>46287</v>
       </c>
       <c r="C322" s="6">
         <v>1</v>
@@ -5770,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="C323" s="9">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46022</v>
+        <v>46189</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5792,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46100</v>
+        <v>46210</v>
       </c>
       <c r="C325" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46101</v>
+        <v>46232</v>
       </c>
       <c r="C326" s="6">
         <v>1</v>
@@ -5814,10 +5814,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46097</v>
+        <v>46126</v>
       </c>
       <c r="C327" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5825,10 +5825,10 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46077</v>
+        <v>46022</v>
       </c>
       <c r="C328" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -5836,10 +5836,10 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C329" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -5847,7 +5847,7 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46233</v>
+        <v>46101</v>
       </c>
       <c r="C330" s="6">
         <v>1</v>
@@ -5858,10 +5858,10 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C331" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -5869,10 +5869,10 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46113</v>
+        <v>46077</v>
       </c>
       <c r="C332" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -5880,7 +5880,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46253</v>
+        <v>46108</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46142</v>
+        <v>46233</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,10 +5902,10 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46244</v>
+        <v>46098</v>
       </c>
       <c r="C335" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46153</v>
+        <v>46113</v>
       </c>
       <c r="C336" s="6">
         <v>1</v>
@@ -5924,7 +5924,7 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46031</v>
+        <v>46253</v>
       </c>
       <c r="C337" s="9">
         <v>1</v>
@@ -5935,9 +5935,53 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C338" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B339" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C339" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B340" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C340" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B341" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C341" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B342" s="5">
         <v>46155</v>
       </c>
-      <c r="C338" s="6">
+      <c r="C342" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6041,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6279,7 +6323,7 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,7 +6476,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6449,7 +6493,7 @@
         <v>3</v>
       </c>
       <c r="E29">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6500,7 +6544,7 @@
         <v>242</v>
       </c>
       <c r="E32">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -7217,7 +7261,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -7228,7 +7272,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>236</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -7239,7 +7283,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -7261,7 +7305,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -7283,7 +7327,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -7294,7 +7338,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -7305,7 +7349,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7316,7 +7360,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -7327,7 +7371,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -7338,7 +7382,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -7349,7 +7393,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -7360,10 +7404,10 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -7371,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>112</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7382,7 +7426,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7393,7 +7437,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7404,7 +7448,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7415,7 +7459,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7426,7 +7470,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7437,7 +7481,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7448,7 +7492,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7459,7 +7503,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7470,7 +7514,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7481,7 +7525,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7492,7 +7536,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7503,7 +7547,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7514,7 +7558,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7525,7 +7569,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -7536,7 +7580,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -7547,7 +7591,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7558,7 +7602,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7569,7 +7613,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -7580,7 +7624,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7591,7 +7635,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7602,7 +7646,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>185</v>
+        <v>91</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7613,7 +7657,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -7624,7 +7668,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7635,7 +7679,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7646,7 +7690,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7657,7 +7701,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7668,7 +7712,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7679,7 +7723,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7690,7 +7734,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7701,7 +7745,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7770,7 +7814,7 @@
         <v>117</v>
       </c>
       <c r="C103">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -7800,7 +7844,7 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C106">
         <v>6</v>
@@ -7811,7 +7855,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="C107">
         <v>6</v>
@@ -7822,7 +7866,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C108">
         <v>6</v>
@@ -7833,10 +7877,10 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -7855,7 +7899,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -7888,7 +7932,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -8801,7 +8845,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C197">
         <v>10</v>
@@ -8812,7 +8856,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C198">
         <v>10</v>
@@ -8823,7 +8867,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C199">
         <v>9</v>
@@ -8845,7 +8889,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C201">
         <v>9</v>
@@ -8856,7 +8900,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>65</v>
+        <v>192</v>
       </c>
       <c r="C202">
         <v>8</v>
@@ -8867,10 +8911,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C203">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8878,10 +8922,10 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C204">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -8889,7 +8933,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="C205">
         <v>7</v>
@@ -8933,7 +8977,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8944,7 +8988,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C210">
         <v>5</v>
@@ -8955,7 +8999,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8966,7 +9010,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8977,7 +9021,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8988,7 +9032,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -8999,7 +9043,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -9010,7 +9054,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -9021,7 +9065,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -9032,7 +9076,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -9054,7 +9098,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>59</v>
+        <v>285</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -9065,7 +9109,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -9076,7 +9120,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -9087,7 +9131,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9109,7 +9153,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -9120,7 +9164,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -9131,7 +9175,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -9142,7 +9186,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>64</v>
+        <v>195</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -9153,7 +9197,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9164,7 +9208,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9175,7 +9219,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9186,7 +9230,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -9197,10 +9241,10 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -9208,7 +9252,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -9219,7 +9263,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9230,7 +9274,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9241,7 +9285,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9252,7 +9296,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9263,7 +9307,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>226</v>
+        <v>118</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9274,7 +9318,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9285,7 +9329,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9296,7 +9340,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9307,7 +9351,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>112</v>
+        <v>207</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9318,7 +9362,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9329,7 +9373,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>219</v>
+        <v>69</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9340,7 +9384,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9351,7 +9395,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9362,7 +9406,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9373,7 +9417,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9384,7 +9428,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9395,7 +9439,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9406,7 +9450,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9417,7 +9461,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9428,7 +9472,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9439,7 +9483,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>123</v>
+        <v>222</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9450,7 +9494,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9461,7 +9505,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9472,7 +9516,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9483,7 +9527,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9494,7 +9538,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9505,7 +9549,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9516,7 +9560,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9527,7 +9571,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9538,7 +9582,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9549,7 +9593,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9560,7 +9604,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9571,7 +9615,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9582,7 +9626,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9593,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9604,7 +9648,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9615,7 +9659,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9626,7 +9670,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -10528,7 +10572,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10561,7 +10605,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10572,7 +10616,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10594,7 +10638,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10605,7 +10649,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10677,7 +10721,7 @@
         <v>272</v>
       </c>
       <c r="C3">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10743,7 +10787,7 @@
         <v>272</v>
       </c>
       <c r="C9">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10798,7 +10842,7 @@
         <v>275</v>
       </c>
       <c r="C14">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10919,7 +10963,7 @@
         <v>272</v>
       </c>
       <c r="C25">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10952,7 +10996,7 @@
         <v>273</v>
       </c>
       <c r="C28">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="585" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21A71EFD-47D3-4B08-B93E-21C841A6FCCF}"/>
+  <xr:revisionPtr revIDLastSave="604" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D4D3B34-7D1C-44E4-BE81-97FCCD897D75}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1757,10 +1757,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>1.0569999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1842,10 +1842,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E18">
-        <v>1.1599999999999999</v>
+        <v>1.133</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1910,10 +1910,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22">
-        <v>1.393</v>
+        <v>1.357</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E32">
-        <v>1.073</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,10 +2097,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E33">
-        <v>1.036</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2165,10 +2165,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E37">
-        <v>1.0049999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E38">
-        <v>1.093</v>
+        <v>1.0880000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C342"/>
+  <dimension ref="A1:C343"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,7 +2253,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2756,10 +2756,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46212</v>
+        <v>46293</v>
       </c>
       <c r="C49" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2767,10 +2767,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46091</v>
+        <v>46212</v>
       </c>
       <c r="C50" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2778,10 +2778,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C51" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2789,7 +2789,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2800,7 +2800,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46276</v>
+        <v>46106</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46113</v>
+        <v>46276</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46184</v>
+        <v>46113</v>
       </c>
       <c r="C56" s="6">
         <v>1</v>
@@ -2932,7 +2932,7 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46093</v>
+        <v>46295</v>
       </c>
       <c r="C65" s="9">
         <v>1</v>
@@ -2943,10 +2943,10 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C66" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2954,10 +2954,10 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C67" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2965,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2976,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -2998,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3031,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -3053,7 +3053,7 @@
         <v>16</v>
       </c>
       <c r="B76" s="5">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C76" s="6">
         <v>1</v>
@@ -3061,13 +3061,13 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B77" s="8">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C77" s="9">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3075,10 +3075,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C78" s="6">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3086,10 +3086,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C79" s="9">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3097,10 +3097,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C80" s="6">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3108,10 +3108,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C81" s="9">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3119,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C82" s="6">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3130,10 +3130,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C83" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3141,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C84" s="6">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C85" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C86" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C87" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C88" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C89" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C90" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C91" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C92" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3240,7 +3240,7 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C93" s="9">
         <v>2</v>
@@ -3251,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C94" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3262,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C95" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3273,7 +3273,7 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C96" s="6">
         <v>1</v>
@@ -3284,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C97" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3295,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C98" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C99" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3317,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C101" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3339,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46217</v>
+        <v>46078</v>
       </c>
       <c r="C102" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3350,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46272</v>
+        <v>46217</v>
       </c>
       <c r="C103" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3361,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C104" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3372,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C105" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3383,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3394,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C107" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3405,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C108" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3416,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C109" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3427,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C110" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3438,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C111" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3449,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C112" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3460,10 +3460,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3471,10 +3471,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C114" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3482,7 +3482,7 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C115" s="9">
         <v>2</v>
@@ -3493,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C116" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3504,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3515,10 +3515,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3526,10 +3526,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C119" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3537,10 +3537,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C120" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3548,7 +3548,7 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C121" s="9">
         <v>1</v>
@@ -3559,7 +3559,7 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -3570,10 +3570,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C123" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3581,10 +3581,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3592,10 +3592,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C125" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3603,10 +3603,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C126" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3625,7 +3625,7 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3636,7 +3636,7 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3647,10 +3647,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C130" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3658,10 +3658,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C131" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3669,10 +3669,10 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C132" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3680,10 +3680,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C133" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3691,10 +3691,10 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46288</v>
+        <v>46212</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3702,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46086</v>
+        <v>46288</v>
       </c>
       <c r="C135" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3713,10 +3713,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46227</v>
+        <v>46086</v>
       </c>
       <c r="C136" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3724,10 +3724,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="C137" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3735,7 +3735,7 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46188</v>
+        <v>46289</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3746,7 +3746,7 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46147</v>
+        <v>46188</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3757,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3768,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3779,7 +3779,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3790,7 +3790,7 @@
         <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46225</v>
+        <v>46190</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3798,13 +3798,13 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B144" s="5">
-        <v>46003</v>
+        <v>46225</v>
       </c>
       <c r="C144" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3812,10 +3812,10 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C145" s="9">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3823,10 +3823,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C146" s="6">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3834,10 +3834,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C147" s="9">
-        <v>96</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3845,10 +3845,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C148" s="6">
-        <v>38</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3856,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C149" s="9">
-        <v>91</v>
+        <v>38</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3867,10 +3867,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C150" s="6">
-        <v>8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3878,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C151" s="9">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3889,10 +3889,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C152" s="6">
-        <v>2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3900,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C153" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C154" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3922,7 +3922,7 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C155" s="9">
         <v>2</v>
@@ -3933,7 +3933,7 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46212</v>
+        <v>46021</v>
       </c>
       <c r="C156" s="6">
         <v>2</v>
@@ -3944,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46077</v>
+        <v>46212</v>
       </c>
       <c r="C157" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3955,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C158" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3966,10 +3966,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46209</v>
+        <v>46167</v>
       </c>
       <c r="C159" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3977,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="C160" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3988,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46245</v>
+        <v>46189</v>
       </c>
       <c r="C161" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3999,7 +3999,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46170</v>
+        <v>46245</v>
       </c>
       <c r="C162" s="6">
         <v>1</v>
@@ -4010,7 +4010,7 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46210</v>
+        <v>46170</v>
       </c>
       <c r="C163" s="9">
         <v>1</v>
@@ -4021,7 +4021,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46093</v>
+        <v>46210</v>
       </c>
       <c r="C164" s="6">
         <v>1</v>
@@ -4032,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46233</v>
+        <v>46093</v>
       </c>
       <c r="C165" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4043,10 +4043,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46090</v>
+        <v>46233</v>
       </c>
       <c r="C166" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4054,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C167" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4065,10 +4065,10 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C168" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4076,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C169" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4087,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C170" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4098,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46262</v>
+        <v>46083</v>
       </c>
       <c r="C171" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4109,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46022</v>
+        <v>46262</v>
       </c>
       <c r="C172" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4120,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C173" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4131,10 +4131,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C174" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4142,7 +4142,7 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46287</v>
+        <v>46135</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46127</v>
+        <v>46287</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4164,7 +4164,7 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4175,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46286</v>
+        <v>46087</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46108</v>
+        <v>46286</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4197,7 +4197,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46267</v>
+        <v>46108</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46020</v>
+        <v>46267</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4219,10 +4219,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46168</v>
+        <v>46020</v>
       </c>
       <c r="C182" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4230,10 +4230,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46248</v>
+        <v>46168</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46097</v>
+        <v>46252</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4263,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4274,10 +4274,10 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C187" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4285,10 +4285,10 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C188" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4296,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46120</v>
+        <v>46080</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4318,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4329,7 +4329,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4340,7 +4340,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C196" s="6">
         <v>1</v>
@@ -4384,10 +4384,10 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="C197" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4395,7 +4395,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="C198" s="6">
         <v>2</v>
@@ -4406,10 +4406,10 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46258</v>
+        <v>46118</v>
       </c>
       <c r="C199" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46192</v>
+        <v>46258</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4428,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4436,13 +4436,13 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C202" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4450,10 +4450,10 @@
         <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C203" s="9">
-        <v>132</v>
+        <v>91</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4461,10 +4461,10 @@
         <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C204" s="6">
-        <v>167</v>
+        <v>132</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4472,10 +4472,10 @@
         <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C205" s="9">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4483,10 +4483,10 @@
         <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C206" s="6">
-        <v>15</v>
+        <v>173</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4494,10 +4494,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C207" s="9">
-        <v>168</v>
+        <v>15</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4505,10 +4505,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C208" s="6">
-        <v>16</v>
+        <v>168</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C209" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4527,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C210" s="6">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4538,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C211" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C212" s="6">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46258</v>
+        <v>46013</v>
       </c>
       <c r="C213" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46080</v>
+        <v>46258</v>
       </c>
       <c r="C214" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,7 +4582,7 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46209</v>
+        <v>46080</v>
       </c>
       <c r="C215" s="9">
         <v>2</v>
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46227</v>
+        <v>46209</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46090</v>
+        <v>46227</v>
       </c>
       <c r="C217" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46192</v>
+        <v>46090</v>
       </c>
       <c r="C218" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,7 +4626,7 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C219" s="9">
         <v>4</v>
@@ -4637,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4648,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C221" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C222" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4670,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C223" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,10 +4681,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46265</v>
+        <v>46021</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4692,10 +4692,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46078</v>
+        <v>46265</v>
       </c>
       <c r="C225" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4703,10 +4703,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46260</v>
+        <v>46078</v>
       </c>
       <c r="C226" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46128</v>
+        <v>46260</v>
       </c>
       <c r="C227" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C228" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4736,10 +4736,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46255</v>
+        <v>46083</v>
       </c>
       <c r="C229" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46076</v>
+        <v>46255</v>
       </c>
       <c r="C230" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46262</v>
+        <v>46076</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46084</v>
+        <v>46262</v>
       </c>
       <c r="C232" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,10 +4780,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46273</v>
+        <v>46084</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46099</v>
+        <v>46273</v>
       </c>
       <c r="C234" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,7 +4813,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46226</v>
+        <v>46154</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4824,7 +4824,7 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="C237" s="9">
         <v>1</v>
@@ -4835,7 +4835,7 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -4846,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="C239" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4857,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46237</v>
+        <v>46120</v>
       </c>
       <c r="C240" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46077</v>
+        <v>46237</v>
       </c>
       <c r="C241" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,10 +4890,10 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46216</v>
+        <v>46114</v>
       </c>
       <c r="C243" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,10 +4901,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46037</v>
+        <v>46216</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46289</v>
+        <v>46037</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4923,7 +4923,7 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="C246" s="6">
         <v>1</v>
@@ -4934,10 +4934,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46020</v>
+        <v>46276</v>
       </c>
       <c r="C247" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,10 +4956,10 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46287</v>
+        <v>46106</v>
       </c>
       <c r="C249" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46211</v>
+        <v>46287</v>
       </c>
       <c r="C250" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5000,10 +5000,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46210</v>
+        <v>46155</v>
       </c>
       <c r="C253" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5011,10 +5011,10 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46112</v>
+        <v>46210</v>
       </c>
       <c r="C254" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5022,7 +5022,7 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C255" s="9">
         <v>1</v>
@@ -5033,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5044,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5055,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5066,7 +5066,7 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C259" s="9">
         <v>1</v>
@@ -5077,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46181</v>
+        <v>46035</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
@@ -5088,7 +5088,7 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46290</v>
+        <v>46181</v>
       </c>
       <c r="C261" s="9">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46087</v>
+        <v>46290</v>
       </c>
       <c r="C262" s="6">
         <v>1</v>
@@ -5110,10 +5110,10 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C263" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5121,10 +5121,10 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C264" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46204</v>
+        <v>46031</v>
       </c>
       <c r="C265" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="C267" s="9">
         <v>1</v>
@@ -5165,7 +5165,7 @@
         <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46101</v>
+        <v>46286</v>
       </c>
       <c r="C268" s="6">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46213</v>
+        <v>46101</v>
       </c>
       <c r="C269" s="9">
         <v>1</v>
@@ -5187,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46142</v>
+        <v>46213</v>
       </c>
       <c r="C270" s="6">
         <v>1</v>
@@ -5195,13 +5195,13 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B271" s="8">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C271" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5209,10 +5209,10 @@
         <v>21</v>
       </c>
       <c r="B272" s="5">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C272" s="6">
-        <v>38</v>
+        <v>151</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -5220,10 +5220,10 @@
         <v>21</v>
       </c>
       <c r="B273" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C273" s="9">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -5231,10 +5231,10 @@
         <v>21</v>
       </c>
       <c r="B274" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C274" s="6">
-        <v>109</v>
+        <v>70</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5242,10 +5242,10 @@
         <v>21</v>
       </c>
       <c r="B275" s="8">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C275" s="9">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5253,10 +5253,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C276" s="6">
-        <v>45</v>
+        <v>145</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5264,10 +5264,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C277" s="9">
-        <v>127</v>
+        <v>44</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5275,10 +5275,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C278" s="6">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5286,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C279" s="9">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5297,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C280" s="6">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5308,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C281" s="9">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C282" s="6">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C283" s="9">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,10 +5341,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="C284" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5352,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46157</v>
+        <v>46014</v>
       </c>
       <c r="C285" s="9">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5363,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C286" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,10 +5374,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C287" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5385,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C288" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C289" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C290" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C291" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C292" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5440,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46192</v>
+        <v>46094</v>
       </c>
       <c r="C293" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5451,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46080</v>
+        <v>46192</v>
       </c>
       <c r="C294" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,7 +5506,7 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C299" s="9">
         <v>6</v>
@@ -5517,10 +5517,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46217</v>
+        <v>46015</v>
       </c>
       <c r="C300" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5528,10 +5528,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46078</v>
+        <v>46217</v>
       </c>
       <c r="C301" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5539,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46209</v>
+        <v>46078</v>
       </c>
       <c r="C302" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46237</v>
+        <v>46209</v>
       </c>
       <c r="C303" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5561,10 +5561,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46148</v>
+        <v>46237</v>
       </c>
       <c r="C304" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5572,7 +5572,7 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C305" s="9">
         <v>2</v>
@@ -5583,10 +5583,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C306" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5594,7 +5594,7 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C307" s="9">
         <v>3</v>
@@ -5605,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C308" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,10 +5616,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C309" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5627,10 +5627,10 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C310" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -5638,7 +5638,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C311" s="9">
         <v>3</v>
@@ -5649,10 +5649,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C312" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5660,7 +5660,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46231</v>
+        <v>46118</v>
       </c>
       <c r="C313" s="9">
         <v>1</v>
@@ -5671,10 +5671,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46076</v>
+        <v>46231</v>
       </c>
       <c r="C314" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5682,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C315" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="C316" s="6">
         <v>1</v>
@@ -5704,7 +5704,7 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C317" s="9">
         <v>1</v>
@@ -5715,10 +5715,10 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C318" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -5726,10 +5726,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C319" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5737,10 +5737,10 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C320" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -5748,10 +5748,10 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C321" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,10 +5759,10 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C322" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C323" s="9">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5792,7 +5792,7 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46210</v>
+        <v>46189</v>
       </c>
       <c r="C325" s="9">
         <v>1</v>
@@ -5803,7 +5803,7 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C326" s="6">
         <v>1</v>
@@ -5814,7 +5814,7 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C327" s="9">
         <v>1</v>
@@ -5825,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C328" s="6">
         <v>1</v>
@@ -5836,10 +5836,10 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C329" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -5847,10 +5847,10 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C330" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,10 +5858,10 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C331" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -5869,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C332" s="6">
         <v>3</v>
@@ -5880,10 +5880,10 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C333" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,10 +5902,10 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46098</v>
+        <v>46233</v>
       </c>
       <c r="C335" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -5913,10 +5913,10 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C336" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -5924,7 +5924,7 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C337" s="9">
         <v>1</v>
@@ -5935,7 +5935,7 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C338" s="6">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C339" s="9">
         <v>1</v>
@@ -5957,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C340" s="6">
         <v>1</v>
@@ -5968,7 +5968,7 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C341" s="9">
         <v>1</v>
@@ -5979,9 +5979,20 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C342" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>21</v>
+      </c>
+      <c r="B343">
         <v>46155</v>
       </c>
-      <c r="C342" s="6">
+      <c r="C343">
         <v>1</v>
       </c>
     </row>
@@ -6215,7 +6226,7 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -6300,7 +6311,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -6374,7 +6385,7 @@
         <v>25</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -6538,7 +6549,7 @@
         <v>17</v>
       </c>
       <c r="C32">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D32">
         <v>242</v>
@@ -6561,7 +6572,7 @@
         <v>7</v>
       </c>
       <c r="E33">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6623,7 +6634,7 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D37">
         <v>13</v>
@@ -6640,7 +6651,7 @@
         <v>19</v>
       </c>
       <c r="C38">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -7836,7 +7847,7 @@
         <v>119</v>
       </c>
       <c r="C105">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -8878,7 +8889,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C200">
         <v>9</v>
@@ -8900,10 +8911,10 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C202">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -8955,10 +8966,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8966,7 +8977,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -8977,7 +8988,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8988,10 +8999,10 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C210">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -8999,7 +9010,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -9021,7 +9032,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -9043,7 +9054,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -9054,7 +9065,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -9065,7 +9076,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -9076,7 +9087,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -9087,7 +9098,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -9098,7 +9109,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>285</v>
+        <v>68</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -9109,7 +9120,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -9131,7 +9142,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>194</v>
+        <v>59</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9142,7 +9153,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -9153,7 +9164,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -9164,7 +9175,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -9175,7 +9186,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>199</v>
+        <v>64</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -9197,7 +9208,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9208,7 +9219,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9219,7 +9230,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9230,7 +9241,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -10605,7 +10616,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10616,7 +10627,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10627,7 +10638,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10638,7 +10649,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10649,7 +10660,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10660,7 +10671,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10787,7 +10798,7 @@
         <v>272</v>
       </c>
       <c r="C9">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10820,7 +10831,7 @@
         <v>275</v>
       </c>
       <c r="C12">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -10842,7 +10853,7 @@
         <v>275</v>
       </c>
       <c r="C14">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -10996,7 +11007,7 @@
         <v>273</v>
       </c>
       <c r="C28">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -11062,7 +11073,7 @@
         <v>275</v>
       </c>
       <c r="C34">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="604" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D4D3B34-7D1C-44E4-BE81-97FCCD897D75}"/>
+  <xr:revisionPtr revIDLastSave="605" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{095AC658-36A1-4B03-A0EB-51A955B3B39C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="2" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -5986,13 +5986,13 @@
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A343" t="s">
-        <v>21</v>
-      </c>
-      <c r="B343">
+      <c r="A343" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B343" s="8">
         <v>46155</v>
       </c>
-      <c r="C343">
+      <c r="C343" s="9">
         <v>1</v>
       </c>
     </row>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="605" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{095AC658-36A1-4B03-A0EB-51A955B3B39C}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D65754DA-BFDE-405C-90CF-4A0C73527AF0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="2" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1638,10 +1638,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6">
-        <v>1.103</v>
+        <v>1.121</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1672,10 +1672,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E8">
-        <v>1.0269999999999999</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1689,10 +1689,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1774,10 +1774,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14">
-        <v>1.097</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1859,10 +1859,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19">
-        <v>1.0109999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1910,10 +1910,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E22">
-        <v>1.357</v>
+        <v>1.393</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1944,10 +1944,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E24">
-        <v>1.169</v>
+        <v>1.1379999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2029,10 +2029,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E29">
-        <v>1.07</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E32">
-        <v>1.071</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,10 +2114,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E34">
-        <v>0.94399999999999995</v>
+        <v>0.94099999999999995</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E38">
-        <v>1.0880000000000001</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C343"/>
+  <dimension ref="A1:C348"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2330,7 +2330,7 @@
         <v>46007</v>
       </c>
       <c r="C10" s="6">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2844,10 +2844,10 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="C57" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2855,7 +2855,7 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46090</v>
+        <v>46290</v>
       </c>
       <c r="C58" s="6">
         <v>3</v>
@@ -2866,10 +2866,10 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46210</v>
+        <v>46090</v>
       </c>
       <c r="C59" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2877,10 +2877,10 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C60" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2888,7 +2888,7 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="C61" s="9">
         <v>1</v>
@@ -2899,7 +2899,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46148</v>
+        <v>46289</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -2910,7 +2910,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2921,7 +2921,7 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -2932,7 +2932,7 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46295</v>
+        <v>46125</v>
       </c>
       <c r="C65" s="9">
         <v>1</v>
@@ -2943,7 +2943,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46093</v>
+        <v>46295</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2954,10 +2954,10 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C67" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2965,10 +2965,10 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C68" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2976,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -2998,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3031,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -3053,7 +3053,7 @@
         <v>16</v>
       </c>
       <c r="B76" s="5">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C76" s="6">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>16</v>
       </c>
       <c r="B77" s="8">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -3072,13 +3072,13 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B78" s="5">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C78" s="6">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3086,10 +3086,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C79" s="9">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3097,10 +3097,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C80" s="6">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3108,10 +3108,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C81" s="9">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3119,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C82" s="6">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3141,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C84" s="6">
-        <v>18</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C85" s="9">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C86" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C87" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C88" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C89" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C90" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C91" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C92" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3240,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C93" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3251,7 +3251,7 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C94" s="6">
         <v>2</v>
@@ -3262,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C95" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3273,7 +3273,7 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46105</v>
+        <v>46296</v>
       </c>
       <c r="C96" s="6">
         <v>1</v>
@@ -3284,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46210</v>
+        <v>46083</v>
       </c>
       <c r="C97" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3295,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46211</v>
+        <v>46105</v>
       </c>
       <c r="C98" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46269</v>
+        <v>46210</v>
       </c>
       <c r="C99" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3317,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46077</v>
+        <v>46211</v>
       </c>
       <c r="C100" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46118</v>
+        <v>46269</v>
       </c>
       <c r="C101" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3339,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C102" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3350,7 +3350,7 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46217</v>
+        <v>46118</v>
       </c>
       <c r="C103" s="9">
         <v>1</v>
@@ -3361,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46272</v>
+        <v>46078</v>
       </c>
       <c r="C104" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3372,7 +3372,7 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46099</v>
+        <v>46217</v>
       </c>
       <c r="C105" s="9">
         <v>1</v>
@@ -3383,7 +3383,7 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46104</v>
+        <v>46272</v>
       </c>
       <c r="C106" s="6">
         <v>3</v>
@@ -3394,7 +3394,7 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46267</v>
+        <v>46099</v>
       </c>
       <c r="C107" s="9">
         <v>1</v>
@@ -3405,7 +3405,7 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46273</v>
+        <v>46104</v>
       </c>
       <c r="C108" s="6">
         <v>3</v>
@@ -3416,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="C109" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3427,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46231</v>
+        <v>46273</v>
       </c>
       <c r="C110" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3438,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="C111" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3449,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46020</v>
+        <v>46231</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3460,10 +3460,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46076</v>
+        <v>46258</v>
       </c>
       <c r="C113" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3471,7 +3471,7 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46111</v>
+        <v>46020</v>
       </c>
       <c r="C114" s="6">
         <v>1</v>
@@ -3482,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46087</v>
+        <v>46076</v>
       </c>
       <c r="C115" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3493,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46140</v>
+        <v>46111</v>
       </c>
       <c r="C116" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3504,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46113</v>
+        <v>46087</v>
       </c>
       <c r="C117" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3515,7 +3515,7 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="C118" s="6">
         <v>2</v>
@@ -3526,10 +3526,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3537,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46274</v>
+        <v>46119</v>
       </c>
       <c r="C120" s="6">
         <v>2</v>
@@ -3548,7 +3548,7 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C121" s="9">
         <v>1</v>
@@ -3559,10 +3559,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46141</v>
+        <v>46274</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3570,7 +3570,7 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46287</v>
+        <v>46098</v>
       </c>
       <c r="C123" s="9">
         <v>1</v>
@@ -3581,10 +3581,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46079</v>
+        <v>46141</v>
       </c>
       <c r="C124" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3592,7 +3592,7 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46139</v>
+        <v>46287</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3603,10 +3603,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46148</v>
+        <v>46079</v>
       </c>
       <c r="C126" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46185</v>
+        <v>46139</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3625,10 +3625,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46174</v>
+        <v>46148</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3636,7 +3636,7 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46286</v>
+        <v>46185</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3647,7 +3647,7 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46092</v>
+        <v>46174</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3658,10 +3658,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46021</v>
+        <v>46286</v>
       </c>
       <c r="C131" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3669,7 +3669,7 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46177</v>
+        <v>46092</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3680,10 +3680,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46252</v>
+        <v>46021</v>
       </c>
       <c r="C133" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3691,10 +3691,10 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46212</v>
+        <v>46177</v>
       </c>
       <c r="C134" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3702,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46288</v>
+        <v>46252</v>
       </c>
       <c r="C135" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3713,10 +3713,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46086</v>
+        <v>46212</v>
       </c>
       <c r="C136" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3724,10 +3724,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46227</v>
+        <v>46288</v>
       </c>
       <c r="C137" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3735,10 +3735,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46289</v>
+        <v>46086</v>
       </c>
       <c r="C138" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3746,10 +3746,10 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46188</v>
+        <v>46227</v>
       </c>
       <c r="C139" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3757,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46147</v>
+        <v>46289</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3768,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46134</v>
+        <v>46188</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3779,7 +3779,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3790,7 +3790,7 @@
         <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46190</v>
+        <v>46134</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3801,7 +3801,7 @@
         <v>14</v>
       </c>
       <c r="B144" s="5">
-        <v>46225</v>
+        <v>46182</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3809,24 +3809,24 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B145" s="8">
-        <v>46003</v>
+        <v>46190</v>
       </c>
       <c r="C145" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B146" s="5">
-        <v>46002</v>
+        <v>46225</v>
       </c>
       <c r="C146" s="6">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3834,10 +3834,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C147" s="9">
-        <v>13</v>
+        <v>95</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3845,10 +3845,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C148" s="6">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3856,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C149" s="9">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3867,10 +3867,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C150" s="6">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3878,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C151" s="9">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3889,10 +3889,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C152" s="6">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3900,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C153" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C154" s="6">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3922,7 +3922,7 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C155" s="9">
         <v>2</v>
@@ -3933,10 +3933,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C156" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3944,7 +3944,7 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46212</v>
+        <v>46013</v>
       </c>
       <c r="C157" s="9">
         <v>2</v>
@@ -3955,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C158" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3966,10 +3966,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46167</v>
+        <v>46212</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3977,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46209</v>
+        <v>46077</v>
       </c>
       <c r="C160" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3988,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46189</v>
+        <v>46167</v>
       </c>
       <c r="C161" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3999,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46245</v>
+        <v>46209</v>
       </c>
       <c r="C162" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4021,7 +4021,7 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C164" s="6">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4043,10 +4043,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C166" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4054,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C167" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4065,10 +4065,10 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C168" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4076,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C169" s="9">
         <v>4</v>
@@ -4087,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C170" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4098,7 +4098,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C171" s="9">
         <v>4</v>
@@ -4109,7 +4109,7 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46262</v>
+        <v>46134</v>
       </c>
       <c r="C172" s="6">
         <v>2</v>
@@ -4120,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46022</v>
+        <v>46296</v>
       </c>
       <c r="C173" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4131,10 +4131,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46114</v>
+        <v>46083</v>
       </c>
       <c r="C174" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4142,10 +4142,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46135</v>
+        <v>46262</v>
       </c>
       <c r="C175" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46287</v>
+        <v>46022</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4164,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C177" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4175,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46087</v>
+        <v>46135</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4197,7 +4197,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46108</v>
+        <v>46127</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46267</v>
+        <v>46087</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4219,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46020</v>
+        <v>46286</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4230,10 +4230,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46168</v>
+        <v>46108</v>
       </c>
       <c r="C183" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46252</v>
+        <v>46020</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4263,10 +4263,10 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46097</v>
+        <v>46168</v>
       </c>
       <c r="C186" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4274,7 +4274,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46177</v>
+        <v>46248</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4285,10 +4285,10 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46161</v>
+        <v>46252</v>
       </c>
       <c r="C188" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4296,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46080</v>
+        <v>46177</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4318,10 +4318,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46120</v>
+        <v>46161</v>
       </c>
       <c r="C191" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4329,7 +4329,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46101</v>
+        <v>46129</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4340,7 +4340,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46155</v>
+        <v>46080</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46150</v>
+        <v>46120</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46141</v>
+        <v>46101</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46085</v>
+        <v>46155</v>
       </c>
       <c r="C196" s="6">
         <v>1</v>
@@ -4384,7 +4384,7 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4395,10 +4395,10 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46126</v>
+        <v>46141</v>
       </c>
       <c r="C198" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4406,10 +4406,10 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46118</v>
+        <v>46085</v>
       </c>
       <c r="C199" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46258</v>
+        <v>46295</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4428,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46192</v>
+        <v>46148</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4439,54 +4439,54 @@
         <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46079</v>
+        <v>46126</v>
       </c>
       <c r="C202" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B203" s="8">
-        <v>46003</v>
+        <v>46118</v>
       </c>
       <c r="C203" s="9">
-        <v>91</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B204" s="5">
-        <v>46000</v>
+        <v>46258</v>
       </c>
       <c r="C204" s="6">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B205" s="8">
-        <v>46006</v>
+        <v>46192</v>
       </c>
       <c r="C205" s="9">
-        <v>166</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B206" s="5">
-        <v>46001</v>
+        <v>46079</v>
       </c>
       <c r="C206" s="6">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4494,10 +4494,10 @@
         <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46014</v>
+        <v>46003</v>
       </c>
       <c r="C207" s="9">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4505,10 +4505,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="C208" s="6">
-        <v>168</v>
+        <v>132</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C209" s="9">
-        <v>16</v>
+        <v>166</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4527,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C210" s="6">
-        <v>18</v>
+        <v>173</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4538,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C211" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C212" s="6">
-        <v>43</v>
+        <v>168</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C213" s="9">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46258</v>
+        <v>46010</v>
       </c>
       <c r="C214" s="6">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46080</v>
+        <v>46008</v>
       </c>
       <c r="C215" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46209</v>
+        <v>46007</v>
       </c>
       <c r="C216" s="6">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46227</v>
+        <v>46013</v>
       </c>
       <c r="C217" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46090</v>
+        <v>46258</v>
       </c>
       <c r="C218" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46192</v>
+        <v>46080</v>
       </c>
       <c r="C219" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4637,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46079</v>
+        <v>46209</v>
       </c>
       <c r="C220" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4648,7 +4648,7 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46015</v>
+        <v>46227</v>
       </c>
       <c r="C221" s="9">
         <v>1</v>
@@ -4659,7 +4659,7 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C222" s="6">
         <v>5</v>
@@ -4670,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46098</v>
+        <v>46192</v>
       </c>
       <c r="C223" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,10 +4681,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46021</v>
+        <v>46079</v>
       </c>
       <c r="C224" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46265</v>
+        <v>46015</v>
       </c>
       <c r="C225" s="9">
         <v>1</v>
@@ -4703,10 +4703,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C226" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46260</v>
+        <v>46098</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46128</v>
+        <v>46021</v>
       </c>
       <c r="C228" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4736,10 +4736,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46083</v>
+        <v>46265</v>
       </c>
       <c r="C229" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46255</v>
+        <v>46078</v>
       </c>
       <c r="C230" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46076</v>
+        <v>46260</v>
       </c>
       <c r="C231" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46262</v>
+        <v>46128</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,7 +4780,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46084</v>
+        <v>46083</v>
       </c>
       <c r="C233" s="9">
         <v>6</v>
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46273</v>
+        <v>46255</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C235" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46154</v>
+        <v>46294</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4824,7 +4824,7 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46226</v>
+        <v>46262</v>
       </c>
       <c r="C237" s="9">
         <v>1</v>
@@ -4835,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46092</v>
+        <v>46084</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,7 +4846,7 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46022</v>
+        <v>46273</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
@@ -4857,7 +4857,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46120</v>
+        <v>46099</v>
       </c>
       <c r="C240" s="6">
         <v>2</v>
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46237</v>
+        <v>46154</v>
       </c>
       <c r="C241" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46077</v>
+        <v>46226</v>
       </c>
       <c r="C242" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,7 +4890,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46114</v>
+        <v>46092</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4901,10 +4901,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46216</v>
+        <v>46022</v>
       </c>
       <c r="C244" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,10 +4912,10 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46037</v>
+        <v>46120</v>
       </c>
       <c r="C245" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4923,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46289</v>
+        <v>46237</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,10 +4934,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46276</v>
+        <v>46077</v>
       </c>
       <c r="C247" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46020</v>
+        <v>46114</v>
       </c>
       <c r="C248" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,10 +4956,10 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46106</v>
+        <v>46216</v>
       </c>
       <c r="C249" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46287</v>
+        <v>46037</v>
       </c>
       <c r="C250" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46211</v>
+        <v>46289</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46239</v>
+        <v>46276</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5000,10 +5000,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46155</v>
+        <v>46020</v>
       </c>
       <c r="C253" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5011,10 +5011,10 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46210</v>
+        <v>46106</v>
       </c>
       <c r="C254" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5022,10 +5022,10 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46112</v>
+        <v>46287</v>
       </c>
       <c r="C255" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5033,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46132</v>
+        <v>46211</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5044,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46108</v>
+        <v>46239</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5055,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5066,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46118</v>
+        <v>46210</v>
       </c>
       <c r="C259" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5077,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46035</v>
+        <v>46132</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
@@ -5088,7 +5088,7 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46181</v>
+        <v>46108</v>
       </c>
       <c r="C261" s="9">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46290</v>
+        <v>46148</v>
       </c>
       <c r="C262" s="6">
         <v>1</v>
@@ -5110,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46087</v>
+        <v>46118</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5121,10 +5121,10 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46030</v>
+        <v>46035</v>
       </c>
       <c r="C264" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5132,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46031</v>
+        <v>46181</v>
       </c>
       <c r="C265" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46204</v>
+        <v>46290</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46176</v>
+        <v>46087</v>
       </c>
       <c r="C267" s="9">
         <v>1</v>
@@ -5165,10 +5165,10 @@
         <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46286</v>
+        <v>46030</v>
       </c>
       <c r="C268" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46101</v>
+        <v>46031</v>
       </c>
       <c r="C269" s="9">
         <v>1</v>
@@ -5187,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46213</v>
+        <v>46204</v>
       </c>
       <c r="C270" s="6">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         <v>15</v>
       </c>
       <c r="B271" s="8">
-        <v>46142</v>
+        <v>46176</v>
       </c>
       <c r="C271" s="9">
         <v>1</v>
@@ -5206,46 +5206,46 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B272" s="5">
-        <v>46001</v>
+        <v>46286</v>
       </c>
       <c r="C272" s="6">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B273" s="8">
-        <v>46008</v>
+        <v>46101</v>
       </c>
       <c r="C273" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B274" s="5">
-        <v>46003</v>
+        <v>46213</v>
       </c>
       <c r="C274" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B275" s="8">
-        <v>46002</v>
+        <v>46142</v>
       </c>
       <c r="C275" s="9">
-        <v>109</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5253,10 +5253,10 @@
         <v>21</v>
       </c>
       <c r="B276" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C276" s="6">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5264,10 +5264,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C277" s="9">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5275,10 +5275,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C278" s="6">
-        <v>127</v>
+        <v>70</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5286,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46084</v>
+        <v>46002</v>
       </c>
       <c r="C279" s="9">
-        <v>10</v>
+        <v>109</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5297,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46013</v>
+        <v>46006</v>
       </c>
       <c r="C280" s="6">
-        <v>25</v>
+        <v>145</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5308,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C281" s="9">
-        <v>19</v>
+        <v>44</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46021</v>
+        <v>46000</v>
       </c>
       <c r="C282" s="6">
-        <v>6</v>
+        <v>127</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46009</v>
+        <v>46084</v>
       </c>
       <c r="C283" s="9">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,10 +5341,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46083</v>
+        <v>46013</v>
       </c>
       <c r="C284" s="6">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5352,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C285" s="9">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5363,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46157</v>
+        <v>46021</v>
       </c>
       <c r="C286" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,10 +5374,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46079</v>
+        <v>46009</v>
       </c>
       <c r="C287" s="9">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5385,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46167</v>
+        <v>46083</v>
       </c>
       <c r="C288" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46035</v>
+        <v>46014</v>
       </c>
       <c r="C289" s="9">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46085</v>
+        <v>46157</v>
       </c>
       <c r="C290" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46120</v>
+        <v>46079</v>
       </c>
       <c r="C291" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,7 +5429,7 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46114</v>
+        <v>46167</v>
       </c>
       <c r="C292" s="6">
         <v>1</v>
@@ -5440,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46094</v>
+        <v>46035</v>
       </c>
       <c r="C293" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5451,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46192</v>
+        <v>46085</v>
       </c>
       <c r="C294" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,7 +5462,7 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C295" s="9">
         <v>2</v>
@@ -5473,10 +5473,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46091</v>
+        <v>46114</v>
       </c>
       <c r="C296" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5484,10 +5484,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="C297" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5495,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46020</v>
+        <v>46192</v>
       </c>
       <c r="C298" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46080</v>
+        <v>46127</v>
       </c>
       <c r="C299" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5517,10 +5517,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46015</v>
+        <v>46091</v>
       </c>
       <c r="C300" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5528,7 +5528,7 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46217</v>
+        <v>46090</v>
       </c>
       <c r="C301" s="9">
         <v>1</v>
@@ -5539,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46078</v>
+        <v>46020</v>
       </c>
       <c r="C302" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,7 +5550,7 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46209</v>
+        <v>46080</v>
       </c>
       <c r="C303" s="9">
         <v>6</v>
@@ -5561,10 +5561,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46237</v>
+        <v>46015</v>
       </c>
       <c r="C304" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5572,10 +5572,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46148</v>
+        <v>46217</v>
       </c>
       <c r="C305" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5583,10 +5583,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46105</v>
+        <v>46078</v>
       </c>
       <c r="C306" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5594,10 +5594,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46087</v>
+        <v>46209</v>
       </c>
       <c r="C307" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5605,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46107</v>
+        <v>46237</v>
       </c>
       <c r="C308" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,10 +5616,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46086</v>
+        <v>46148</v>
       </c>
       <c r="C309" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5627,10 +5627,10 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="C310" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -5638,7 +5638,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46150</v>
+        <v>46087</v>
       </c>
       <c r="C311" s="9">
         <v>3</v>
@@ -5649,7 +5649,7 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="C312" s="6">
         <v>3</v>
@@ -5660,10 +5660,10 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46118</v>
+        <v>46086</v>
       </c>
       <c r="C313" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -5671,7 +5671,7 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46231</v>
+        <v>46106</v>
       </c>
       <c r="C314" s="6">
         <v>1</v>
@@ -5682,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46076</v>
+        <v>46150</v>
       </c>
       <c r="C315" s="9">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5693,10 +5693,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46182</v>
+        <v>46104</v>
       </c>
       <c r="C316" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5704,7 +5704,7 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46188</v>
+        <v>46118</v>
       </c>
       <c r="C317" s="9">
         <v>1</v>
@@ -5715,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46154</v>
+        <v>46231</v>
       </c>
       <c r="C318" s="6">
         <v>1</v>
@@ -5726,10 +5726,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="C319" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5737,7 +5737,7 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46122</v>
+        <v>46182</v>
       </c>
       <c r="C320" s="6">
         <v>1</v>
@@ -5748,10 +5748,10 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46092</v>
+        <v>46188</v>
       </c>
       <c r="C321" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,10 +5759,10 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="C322" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,10 +5770,10 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46287</v>
+        <v>46093</v>
       </c>
       <c r="C323" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -5781,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5792,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46189</v>
+        <v>46092</v>
       </c>
       <c r="C325" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46210</v>
+        <v>46156</v>
       </c>
       <c r="C326" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46232</v>
+        <v>46287</v>
       </c>
       <c r="C327" s="9">
         <v>1</v>
@@ -5825,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="C328" s="6">
         <v>1</v>
@@ -5836,7 +5836,7 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46022</v>
+        <v>46189</v>
       </c>
       <c r="C329" s="9">
         <v>1</v>
@@ -5847,10 +5847,10 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46100</v>
+        <v>46295</v>
       </c>
       <c r="C330" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46101</v>
+        <v>46210</v>
       </c>
       <c r="C331" s="9">
         <v>1</v>
@@ -5869,10 +5869,10 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46097</v>
+        <v>46232</v>
       </c>
       <c r="C332" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -5880,10 +5880,10 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46077</v>
+        <v>46126</v>
       </c>
       <c r="C333" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46108</v>
+        <v>46022</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,10 +5902,10 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46233</v>
+        <v>46100</v>
       </c>
       <c r="C335" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -5913,10 +5913,10 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C336" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -5924,10 +5924,10 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="C337" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -5935,10 +5935,10 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46253</v>
+        <v>46077</v>
       </c>
       <c r="C338" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -5946,7 +5946,7 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C339" s="9">
         <v>1</v>
@@ -5957,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46244</v>
+        <v>46233</v>
       </c>
       <c r="C340" s="6">
         <v>1</v>
@@ -5968,10 +5968,10 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="C341" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -5979,7 +5979,7 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46031</v>
+        <v>46113</v>
       </c>
       <c r="C342" s="6">
         <v>1</v>
@@ -5990,9 +5990,64 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
+        <v>46253</v>
+      </c>
+      <c r="C343" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B344" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C344" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B345" s="8">
+        <v>46244</v>
+      </c>
+      <c r="C345" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B346" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C346" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B347" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C347" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B348" s="5">
         <v>46155</v>
       </c>
-      <c r="C343" s="9">
+      <c r="C348" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6113,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -6147,7 +6202,7 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -6164,7 +6219,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -6243,7 +6298,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -6277,13 +6332,13 @@
         <v>11</v>
       </c>
       <c r="C16">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -6334,7 +6389,7 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6385,7 +6440,7 @@
         <v>25</v>
       </c>
       <c r="E22">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -6419,7 +6474,7 @@
         <v>12</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -6504,7 +6559,7 @@
         <v>3</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6555,7 +6610,7 @@
         <v>242</v>
       </c>
       <c r="E32">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6583,7 +6638,7 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -6657,7 +6712,7 @@
         <v>10</v>
       </c>
       <c r="E38">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6788,7 +6843,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -6799,7 +6854,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -6810,7 +6865,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -6821,7 +6876,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6832,7 +6887,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6843,7 +6898,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -6865,7 +6920,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -6876,7 +6931,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -6887,10 +6942,10 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -6898,7 +6953,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -6909,7 +6964,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -6920,7 +6975,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -6931,7 +6986,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -6942,7 +6997,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -6953,7 +7008,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -6964,7 +7019,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -6975,7 +7030,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -6997,7 +7052,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -7008,7 +7063,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -7019,7 +7074,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -7030,7 +7085,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -7041,7 +7096,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -7052,7 +7107,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -7063,7 +7118,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -7074,7 +7129,7 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -7085,7 +7140,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -7096,7 +7151,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -7107,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -7118,7 +7173,7 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -7143,7 +7198,7 @@
         <v>43</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -7162,7 +7217,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -7173,7 +7228,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -7184,7 +7239,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -7217,7 +7272,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C48">
         <v>4</v>
@@ -7228,7 +7283,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -7250,7 +7305,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -7272,7 +7327,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -7283,7 +7338,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>236</v>
+        <v>86</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -7294,7 +7349,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -7305,7 +7360,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -7316,7 +7371,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -7327,7 +7382,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -7349,7 +7404,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -7360,7 +7415,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -7371,7 +7426,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -7382,7 +7437,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -7393,7 +7448,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -7404,7 +7459,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -7426,7 +7481,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -7437,7 +7492,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -7448,7 +7503,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -7459,7 +7514,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -7470,7 +7525,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -7481,7 +7536,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7492,7 +7547,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -7503,7 +7558,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -7514,7 +7569,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7525,7 +7580,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -7536,7 +7591,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7547,7 +7602,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7558,7 +7613,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7569,7 +7624,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -7580,7 +7635,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -7591,7 +7646,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -7602,7 +7657,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7613,7 +7668,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7624,7 +7679,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -7635,7 +7690,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7646,7 +7701,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7657,7 +7712,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7668,7 +7723,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -7679,7 +7734,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -7690,7 +7745,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -7701,7 +7756,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -7712,7 +7767,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -7723,7 +7778,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -7734,7 +7789,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -7745,7 +7800,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -7756,7 +7811,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -7767,7 +7822,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -7778,7 +7833,7 @@
         <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -7789,7 +7844,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s">
-        <v>104</v>
+        <v>66</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -7800,7 +7855,7 @@
         <v>14</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -7808,13 +7863,13 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B102" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C102">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -7833,10 +7888,10 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C104">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -7844,10 +7899,10 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -7855,10 +7910,10 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -7866,7 +7921,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C107">
         <v>6</v>
@@ -7877,7 +7932,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C108">
         <v>6</v>
@@ -7899,10 +7954,10 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C110">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -7910,10 +7965,10 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C111">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -7921,7 +7976,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -7943,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -7954,7 +8009,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -7965,7 +8020,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C116">
         <v>4</v>
@@ -7976,10 +8031,10 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="C117">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -7987,10 +8042,10 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -8009,7 +8064,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C120">
         <v>3</v>
@@ -8020,10 +8075,10 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -8031,10 +8086,10 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -8042,7 +8097,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -8053,7 +8108,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -8064,7 +8119,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -8086,7 +8141,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -8119,7 +8174,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -8130,7 +8185,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8141,10 +8196,10 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -8152,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -8163,7 +8218,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8174,7 +8229,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -8185,7 +8240,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -8196,7 +8251,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -8207,7 +8262,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -8218,7 +8273,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8229,7 +8284,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8240,7 +8295,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -8251,7 +8306,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8262,7 +8317,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -8273,7 +8328,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -8284,7 +8339,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -8295,7 +8350,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8306,7 +8361,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8317,7 +8372,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8328,7 +8383,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8339,7 +8394,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8350,7 +8405,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8361,7 +8416,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8372,7 +8427,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8383,7 +8438,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>67</v>
+        <v>155</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8394,7 +8449,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8405,7 +8460,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8416,7 +8471,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -8427,7 +8482,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -8438,7 +8493,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8449,7 +8504,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8460,7 +8515,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8471,7 +8526,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8482,7 +8537,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8493,7 +8548,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8504,7 +8559,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8515,7 +8570,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8526,7 +8581,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8537,7 +8592,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>267</v>
+        <v>96</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8548,7 +8603,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8559,7 +8614,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8570,7 +8625,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8581,7 +8636,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8592,7 +8647,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8603,7 +8658,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8614,7 +8669,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8625,7 +8680,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>140</v>
+        <v>234</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8636,7 +8691,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8647,7 +8702,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8658,7 +8713,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8669,7 +8724,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8680,7 +8735,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8691,7 +8746,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8702,7 +8757,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8713,7 +8768,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8724,7 +8779,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8743,13 +8798,13 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C187">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -8757,10 +8812,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C188">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8768,10 +8823,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C189">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8779,7 +8834,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C190">
         <v>16</v>
@@ -8790,10 +8845,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C191">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -8801,10 +8856,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="C192">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8812,10 +8867,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C193">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8823,10 +8878,10 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C194">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -8834,10 +8889,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="C195">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8845,7 +8900,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C196">
         <v>11</v>
@@ -8856,10 +8911,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C197">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -8867,7 +8922,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C198">
         <v>10</v>
@@ -8878,10 +8933,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C199">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8889,7 +8944,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>192</v>
+        <v>55</v>
       </c>
       <c r="C200">
         <v>9</v>
@@ -8900,7 +8955,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="C201">
         <v>9</v>
@@ -8911,7 +8966,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -8922,10 +8977,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C203">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8933,7 +8988,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C204">
         <v>8</v>
@@ -8944,10 +8999,10 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C205">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -8955,10 +9010,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C206">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -8969,7 +9024,7 @@
         <v>47</v>
       </c>
       <c r="C207">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8977,10 +9032,10 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -8988,7 +9043,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -8999,10 +9054,10 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C210">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -9010,7 +9065,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -9021,7 +9076,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -9032,7 +9087,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -9043,7 +9098,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -9054,7 +9109,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -9065,10 +9120,10 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C216">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -9076,7 +9131,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -9087,7 +9142,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -9098,7 +9153,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -9109,7 +9164,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -9120,7 +9175,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -9131,7 +9186,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -9142,7 +9197,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9153,7 +9208,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -9164,7 +9219,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -9175,10 +9230,10 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>199</v>
+        <v>285</v>
       </c>
       <c r="C226">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -9186,7 +9241,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>64</v>
+        <v>199</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -9197,7 +9252,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>195</v>
+        <v>64</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -9208,7 +9263,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9219,7 +9274,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9230,7 +9285,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9241,7 +9296,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -9252,7 +9307,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C233">
         <v>2</v>
@@ -9263,10 +9318,10 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -9274,7 +9329,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -9285,7 +9340,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9296,7 +9351,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9307,7 +9362,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9318,7 +9373,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9329,7 +9384,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9340,7 +9395,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9351,7 +9406,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9362,7 +9417,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>207</v>
+        <v>112</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9373,7 +9428,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9384,7 +9439,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9395,7 +9450,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9406,7 +9461,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9417,7 +9472,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9428,7 +9483,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9439,7 +9494,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9450,7 +9505,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9461,7 +9516,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9472,7 +9527,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9483,7 +9538,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9494,7 +9549,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9505,7 +9560,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9516,7 +9571,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9527,7 +9582,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9538,7 +9593,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9549,7 +9604,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9560,7 +9615,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9571,7 +9626,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9582,7 +9637,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9593,7 +9648,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9604,7 +9659,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9615,7 +9670,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>226</v>
+        <v>116</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9626,7 +9681,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9637,7 +9692,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9648,7 +9703,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9659,7 +9714,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9670,7 +9725,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9681,7 +9736,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9692,7 +9747,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9700,13 +9755,13 @@
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="C274">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -9714,10 +9769,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C275">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -9725,10 +9780,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C276">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -9736,10 +9791,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="C277">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -9747,10 +9802,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="C278">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -9758,10 +9813,10 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="C279">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -9769,7 +9824,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>117</v>
+        <v>231</v>
       </c>
       <c r="C280">
         <v>6</v>
@@ -9780,10 +9835,10 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="C281">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -9791,7 +9846,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9802,7 +9857,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>138</v>
+        <v>235</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9813,7 +9868,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9824,7 +9879,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -9835,7 +9890,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>234</v>
+        <v>125</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -9846,10 +9901,10 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C287">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -9857,7 +9912,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="C288">
         <v>4</v>
@@ -9868,10 +9923,10 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C289">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -9879,7 +9934,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9890,7 +9945,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9901,7 +9956,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9912,7 +9967,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9923,7 +9978,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9934,7 +9989,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9945,7 +10000,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9956,7 +10011,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9967,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9978,7 +10033,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9989,7 +10044,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="C300">
         <v>3</v>
@@ -10000,10 +10055,10 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="C301">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -10011,7 +10066,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>258</v>
+        <v>166</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -10022,7 +10077,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -10033,7 +10088,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -10044,7 +10099,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>190</v>
+        <v>84</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -10055,7 +10110,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>243</v>
+        <v>190</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -10066,7 +10121,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>54</v>
+        <v>243</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -10077,7 +10132,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>244</v>
+        <v>54</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -10088,7 +10143,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>122</v>
+        <v>244</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -10099,7 +10154,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>241</v>
+        <v>122</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -10110,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -10121,7 +10176,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>70</v>
+        <v>242</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -10132,7 +10187,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -10143,7 +10198,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -10154,7 +10209,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -10165,7 +10220,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -10176,10 +10231,10 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="C317">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -10187,7 +10242,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>248</v>
+        <v>112</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10198,7 +10253,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10209,7 +10264,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10220,7 +10275,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10231,7 +10286,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10242,7 +10297,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>259</v>
+        <v>134</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10253,7 +10308,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10264,7 +10319,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10275,7 +10330,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10286,7 +10341,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10297,7 +10352,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>250</v>
+        <v>159</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10308,7 +10363,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10319,7 +10374,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10330,7 +10385,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10341,7 +10396,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>204</v>
+        <v>256</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10352,7 +10407,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10363,7 +10418,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>254</v>
+        <v>63</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10374,7 +10429,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10385,7 +10440,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>116</v>
+        <v>267</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -10396,7 +10451,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10407,7 +10462,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10418,7 +10473,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10429,7 +10484,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>91</v>
+        <v>262</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10440,7 +10495,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>249</v>
+        <v>91</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10451,7 +10506,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10462,7 +10517,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>263</v>
+        <v>167</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10473,7 +10528,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10484,7 +10539,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>143</v>
+        <v>251</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10495,7 +10550,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10506,7 +10561,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>266</v>
+        <v>49</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10517,7 +10572,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10528,7 +10583,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10539,14 +10594,22 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
+        <v>261</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B351" t="s">
         <v>255</v>
       </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="12"/>
+      <c r="C351">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10583,7 +10646,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10594,7 +10657,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10605,7 +10668,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10616,7 +10679,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10627,7 +10690,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10638,7 +10701,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10649,7 +10712,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10660,7 +10723,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10671,7 +10734,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10732,7 +10795,7 @@
         <v>272</v>
       </c>
       <c r="C3">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10798,7 +10861,7 @@
         <v>272</v>
       </c>
       <c r="C9">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10963,7 +11026,7 @@
         <v>275</v>
       </c>
       <c r="C24">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -10974,7 +11037,7 @@
         <v>272</v>
       </c>
       <c r="C25">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -11007,7 +11070,7 @@
         <v>273</v>
       </c>
       <c r="C28">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -11073,7 +11136,7 @@
         <v>275</v>
       </c>
       <c r="C34">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D65754DA-BFDE-405C-90CF-4A0C73527AF0}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{857C6AD3-EB97-4639-B5A6-48600C793F71}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -2029,10 +2029,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E29">
-        <v>1.0780000000000001</v>
+        <v>1.0860000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E32">
-        <v>1.073</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C348"/>
+  <dimension ref="A1:C349"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2319,7 +2319,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46128</v>
+        <v>46296</v>
       </c>
       <c r="C232" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,10 +4780,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C233" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46255</v>
+        <v>46083</v>
       </c>
       <c r="C234" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46076</v>
+        <v>46255</v>
       </c>
       <c r="C235" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46294</v>
+        <v>46076</v>
       </c>
       <c r="C236" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4824,10 +4824,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46262</v>
+        <v>46294</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46084</v>
+        <v>46262</v>
       </c>
       <c r="C238" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46273</v>
+        <v>46084</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4857,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46099</v>
+        <v>46273</v>
       </c>
       <c r="C240" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C241" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,7 +4879,7 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46226</v>
+        <v>46154</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -4890,7 +4890,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4901,7 +4901,7 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C244" s="6">
         <v>1</v>
@@ -4912,10 +4912,10 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="C245" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4923,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46237</v>
+        <v>46120</v>
       </c>
       <c r="C246" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,10 +4934,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46077</v>
+        <v>46237</v>
       </c>
       <c r="C247" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,10 +4956,10 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46216</v>
+        <v>46114</v>
       </c>
       <c r="C249" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46037</v>
+        <v>46216</v>
       </c>
       <c r="C250" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46289</v>
+        <v>46037</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5000,10 +5000,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46020</v>
+        <v>46276</v>
       </c>
       <c r="C253" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5011,10 +5011,10 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C254" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5022,10 +5022,10 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46287</v>
+        <v>46106</v>
       </c>
       <c r="C255" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5033,10 +5033,10 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46211</v>
+        <v>46287</v>
       </c>
       <c r="C256" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5044,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5055,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5066,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46210</v>
+        <v>46155</v>
       </c>
       <c r="C259" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5077,10 +5077,10 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46132</v>
+        <v>46210</v>
       </c>
       <c r="C260" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5088,7 +5088,7 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C261" s="9">
         <v>1</v>
@@ -5099,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C262" s="6">
         <v>1</v>
@@ -5110,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5121,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5132,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46181</v>
+        <v>46035</v>
       </c>
       <c r="C265" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46290</v>
+        <v>46181</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46087</v>
+        <v>46290</v>
       </c>
       <c r="C267" s="9">
         <v>1</v>
@@ -5165,10 +5165,10 @@
         <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C268" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -5176,10 +5176,10 @@
         <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C269" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5187,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46204</v>
+        <v>46031</v>
       </c>
       <c r="C270" s="6">
         <v>1</v>
@@ -5198,7 +5198,7 @@
         <v>15</v>
       </c>
       <c r="B271" s="8">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="C271" s="9">
         <v>1</v>
@@ -5209,7 +5209,7 @@
         <v>15</v>
       </c>
       <c r="B272" s="5">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="C272" s="6">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="B273" s="8">
-        <v>46101</v>
+        <v>46286</v>
       </c>
       <c r="C273" s="9">
         <v>1</v>
@@ -5231,7 +5231,7 @@
         <v>15</v>
       </c>
       <c r="B274" s="5">
-        <v>46213</v>
+        <v>46101</v>
       </c>
       <c r="C274" s="6">
         <v>1</v>
@@ -5242,7 +5242,7 @@
         <v>15</v>
       </c>
       <c r="B275" s="8">
-        <v>46142</v>
+        <v>46213</v>
       </c>
       <c r="C275" s="9">
         <v>1</v>
@@ -5250,13 +5250,13 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B276" s="5">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C276" s="6">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -5264,10 +5264,10 @@
         <v>21</v>
       </c>
       <c r="B277" s="8">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C277" s="9">
-        <v>38</v>
+        <v>151</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5275,10 +5275,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C278" s="6">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5286,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C279" s="9">
-        <v>109</v>
+        <v>70</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5297,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C280" s="6">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5308,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C281" s="9">
-        <v>44</v>
+        <v>145</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C282" s="6">
-        <v>127</v>
+        <v>44</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C283" s="9">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,10 +5341,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C284" s="6">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5352,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C285" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5363,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C286" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,10 +5374,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C287" s="9">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5385,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C288" s="6">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="C289" s="9">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46157</v>
+        <v>46014</v>
       </c>
       <c r="C290" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C291" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C292" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5440,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C293" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5451,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C294" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C295" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5473,10 +5473,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C296" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5484,10 +5484,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C297" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5495,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46192</v>
+        <v>46094</v>
       </c>
       <c r="C298" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46127</v>
+        <v>46192</v>
       </c>
       <c r="C299" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5517,7 +5517,7 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C300" s="6">
         <v>2</v>
@@ -5528,10 +5528,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C301" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5539,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C302" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46080</v>
+        <v>46020</v>
       </c>
       <c r="C303" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5561,7 +5561,7 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C304" s="6">
         <v>6</v>
@@ -5572,10 +5572,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46217</v>
+        <v>46015</v>
       </c>
       <c r="C305" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5583,10 +5583,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46078</v>
+        <v>46217</v>
       </c>
       <c r="C306" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5594,10 +5594,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46209</v>
+        <v>46078</v>
       </c>
       <c r="C307" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5605,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46237</v>
+        <v>46209</v>
       </c>
       <c r="C308" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,10 +5616,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46148</v>
+        <v>46237</v>
       </c>
       <c r="C309" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5627,7 +5627,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C310" s="6">
         <v>2</v>
@@ -5638,10 +5638,10 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C311" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -5649,7 +5649,7 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C312" s="6">
         <v>3</v>
@@ -5660,10 +5660,10 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C313" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -5671,10 +5671,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C314" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5682,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C315" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C316" s="6">
         <v>3</v>
@@ -5704,10 +5704,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C317" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5715,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46231</v>
+        <v>46118</v>
       </c>
       <c r="C318" s="6">
         <v>1</v>
@@ -5726,10 +5726,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46076</v>
+        <v>46231</v>
       </c>
       <c r="C319" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5737,10 +5737,10 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C320" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -5748,7 +5748,7 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="C321" s="9">
         <v>1</v>
@@ -5759,7 +5759,7 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C322" s="6">
         <v>1</v>
@@ -5770,10 +5770,10 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C323" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -5781,10 +5781,10 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C324" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -5792,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C325" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C326" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,10 +5814,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C327" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5825,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C328" s="6">
         <v>1</v>
@@ -5836,7 +5836,7 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C329" s="9">
         <v>1</v>
@@ -5847,7 +5847,7 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46295</v>
+        <v>46189</v>
       </c>
       <c r="C330" s="6">
         <v>1</v>
@@ -5858,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46210</v>
+        <v>46295</v>
       </c>
       <c r="C331" s="9">
         <v>1</v>
@@ -5869,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C332" s="6">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,10 +5902,10 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C335" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -5913,10 +5913,10 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C336" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -5924,10 +5924,10 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C337" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -5935,7 +5935,7 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C338" s="6">
         <v>3</v>
@@ -5946,10 +5946,10 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C339" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -5957,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C340" s="6">
         <v>1</v>
@@ -5968,10 +5968,10 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46098</v>
+        <v>46233</v>
       </c>
       <c r="C341" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -5979,10 +5979,10 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C342" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -5990,7 +5990,7 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C343" s="9">
         <v>1</v>
@@ -6001,7 +6001,7 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C344" s="6">
         <v>1</v>
@@ -6012,7 +6012,7 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C345" s="9">
         <v>1</v>
@@ -6023,7 +6023,7 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C346" s="6">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6045,9 +6045,20 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C348" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B349" s="8">
         <v>46155</v>
       </c>
-      <c r="C348" s="6">
+      <c r="C349" s="9">
         <v>1</v>
       </c>
     </row>
@@ -10701,7 +10712,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10712,7 +10723,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10916,7 +10927,7 @@
         <v>275</v>
       </c>
       <c r="C14">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -11037,7 +11048,7 @@
         <v>272</v>
       </c>
       <c r="C25">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="619" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{857C6AD3-EB97-4639-B5A6-48600C793F71}"/>
+  <xr:revisionPtr revIDLastSave="625" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F346B7-8098-488D-81AD-E607D7F16559}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1604,10 +1604,10 @@
         <v>46</v>
       </c>
       <c r="D4">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4">
-        <v>1.1739999999999999</v>
+        <v>1.1519999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1621,10 +1621,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>1.2649999999999999</v>
+        <v>1.2350000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1638,10 +1638,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6">
-        <v>1.121</v>
+        <v>1.103</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1672,10 +1672,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8">
-        <v>1.0529999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1740,10 +1740,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E12">
-        <v>1.484</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2148,10 +2148,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E36">
-        <v>1.02</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2165,10 +2165,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C349"/>
+  <dimension ref="A1:C350"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2319,7 +2319,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2976,7 +2976,7 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46156</v>
+        <v>46300</v>
       </c>
       <c r="C69" s="9">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -2998,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3031,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -3053,7 +3053,7 @@
         <v>16</v>
       </c>
       <c r="B76" s="5">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C76" s="6">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>16</v>
       </c>
       <c r="B77" s="8">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -3075,7 +3075,7 @@
         <v>16</v>
       </c>
       <c r="B78" s="5">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
@@ -3083,13 +3083,13 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B79" s="8">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C79" s="9">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3097,10 +3097,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C80" s="6">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3108,10 +3108,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C81" s="9">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3119,7 +3119,7 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C82" s="6">
         <v>78</v>
@@ -3130,10 +3130,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C83" s="9">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3141,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C84" s="6">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C85" s="9">
-        <v>18</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C86" s="6">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C87" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C88" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C89" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C90" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C91" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C92" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3240,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C93" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3251,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C94" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3262,7 +3262,7 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C95" s="9">
         <v>2</v>
@@ -3273,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46296</v>
+        <v>46091</v>
       </c>
       <c r="C96" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3284,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C97" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3295,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C98" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3306,7 +3306,7 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C99" s="9">
         <v>1</v>
@@ -3317,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C100" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C101" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3339,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C102" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3350,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C103" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3361,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C104" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3372,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46217</v>
+        <v>46078</v>
       </c>
       <c r="C105" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3837,7 +3837,7 @@
         <v>46003</v>
       </c>
       <c r="C147" s="9">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3892,7 +3892,7 @@
         <v>46001</v>
       </c>
       <c r="C152" s="6">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>46009</v>
       </c>
       <c r="C155" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3936,7 +3936,7 @@
         <v>46014</v>
       </c>
       <c r="C156" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -5333,7 +5333,7 @@
         <v>46000</v>
       </c>
       <c r="C283" s="9">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46092</v>
+        <v>46300</v>
       </c>
       <c r="C326" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,10 +5814,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C327" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5825,10 +5825,10 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C328" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -5836,7 +5836,7 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C329" s="9">
         <v>1</v>
@@ -5847,7 +5847,7 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C330" s="6">
         <v>1</v>
@@ -5858,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46295</v>
+        <v>46189</v>
       </c>
       <c r="C331" s="9">
         <v>1</v>
@@ -5869,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46210</v>
+        <v>46295</v>
       </c>
       <c r="C332" s="6">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,7 +5902,7 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C335" s="9">
         <v>1</v>
@@ -5913,10 +5913,10 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C336" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -5924,10 +5924,10 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C337" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -5935,10 +5935,10 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C338" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -5946,7 +5946,7 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C339" s="9">
         <v>3</v>
@@ -5957,10 +5957,10 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C340" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -5968,7 +5968,7 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C341" s="9">
         <v>1</v>
@@ -5979,10 +5979,10 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46098</v>
+        <v>46233</v>
       </c>
       <c r="C342" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -5990,10 +5990,10 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C343" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -6001,7 +6001,7 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C344" s="6">
         <v>1</v>
@@ -6012,7 +6012,7 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C345" s="9">
         <v>1</v>
@@ -6023,7 +6023,7 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C346" s="6">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6045,7 +6045,7 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C348" s="6">
         <v>1</v>
@@ -6056,9 +6056,20 @@
         <v>21</v>
       </c>
       <c r="B349" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C349" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B350" s="5">
         <v>46155</v>
       </c>
-      <c r="C349" s="9">
+      <c r="C350" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6139,7 +6150,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4">
         <v>9</v>
@@ -6162,7 +6173,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6173,7 +6184,7 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -6207,7 +6218,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -6281,7 +6292,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6570,7 +6581,7 @@
         <v>3</v>
       </c>
       <c r="E29">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6615,13 +6626,13 @@
         <v>17</v>
       </c>
       <c r="C32">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D32">
         <v>242</v>
       </c>
       <c r="E32">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6689,7 +6700,7 @@
         <v>83</v>
       </c>
       <c r="E36">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6700,7 +6711,7 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D37">
         <v>13</v>
@@ -6802,7 +6813,7 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -8892,7 +8903,7 @@
         <v>187</v>
       </c>
       <c r="C194">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -9857,7 +9868,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9868,7 +9879,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9879,7 +9890,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9901,7 +9912,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -9912,7 +9923,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>234</v>
+        <v>125</v>
       </c>
       <c r="C287">
         <v>5</v>
@@ -9923,10 +9934,10 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C288">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -9978,7 +9989,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>239</v>
+        <v>123</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9989,7 +10000,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -10000,7 +10011,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -10011,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -10022,7 +10033,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>124</v>
+        <v>239</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -10657,7 +10668,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10668,7 +10679,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10690,7 +10701,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10806,7 +10817,7 @@
         <v>272</v>
       </c>
       <c r="C3">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10872,7 +10883,7 @@
         <v>272</v>
       </c>
       <c r="C9">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -11147,7 +11158,7 @@
         <v>275</v>
       </c>
       <c r="C34">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -11191,7 +11202,7 @@
         <v>276</v>
       </c>
       <c r="C38">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="625" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F346B7-8098-488D-81AD-E607D7F16559}"/>
+  <xr:revisionPtr revIDLastSave="633" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB240A74-5943-47C6-9BF4-C6638954D7EF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1978,10 +1978,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E26">
-        <v>0.98799999999999999</v>
+        <v>0.97599999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2114,10 +2114,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E34">
-        <v>0.94099999999999995</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2148,10 +2148,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E36">
-        <v>1.024</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C350"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2712,7 +2712,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46132</v>
+        <v>46304</v>
       </c>
       <c r="C45" s="9">
         <v>1</v>
@@ -2723,10 +2723,10 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46246</v>
+        <v>46132</v>
       </c>
       <c r="C46" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2734,7 +2734,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46127</v>
+        <v>46246</v>
       </c>
       <c r="C47" s="9">
         <v>2</v>
@@ -2745,10 +2745,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46225</v>
+        <v>46127</v>
       </c>
       <c r="C48" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2756,10 +2756,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46293</v>
+        <v>46225</v>
       </c>
       <c r="C49" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2767,10 +2767,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46212</v>
+        <v>46293</v>
       </c>
       <c r="C50" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2778,10 +2778,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46091</v>
+        <v>46212</v>
       </c>
       <c r="C51" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2789,10 +2789,10 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C52" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2800,7 +2800,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46276</v>
+        <v>46106</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46113</v>
+        <v>46276</v>
       </c>
       <c r="C56" s="6">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46296</v>
+        <v>46113</v>
       </c>
       <c r="C57" s="9">
         <v>1</v>
@@ -2855,10 +2855,10 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="C58" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2866,7 +2866,7 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46090</v>
+        <v>46290</v>
       </c>
       <c r="C59" s="9">
         <v>3</v>
@@ -2877,10 +2877,10 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46210</v>
+        <v>46090</v>
       </c>
       <c r="C60" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2888,10 +2888,10 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C61" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2899,7 +2899,7 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46289</v>
+        <v>46287</v>
       </c>
       <c r="C62" s="6">
         <v>1</v>
@@ -2910,7 +2910,7 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46148</v>
+        <v>46289</v>
       </c>
       <c r="C63" s="9">
         <v>1</v>
@@ -2921,7 +2921,7 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -2932,7 +2932,7 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C65" s="9">
         <v>1</v>
@@ -2943,7 +2943,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46295</v>
+        <v>46125</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2954,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46093</v>
+        <v>46295</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2965,10 +2965,10 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C68" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2976,10 +2976,10 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46300</v>
+        <v>46177</v>
       </c>
       <c r="C69" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2987,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46156</v>
+        <v>46300</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -2998,7 +2998,7 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C71" s="9">
         <v>1</v>
@@ -3009,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3031,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -3053,7 +3053,7 @@
         <v>16</v>
       </c>
       <c r="B76" s="5">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C76" s="6">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>16</v>
       </c>
       <c r="B77" s="8">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -3075,7 +3075,7 @@
         <v>16</v>
       </c>
       <c r="B78" s="5">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
@@ -3086,7 +3086,7 @@
         <v>16</v>
       </c>
       <c r="B79" s="8">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C79" s="9">
         <v>1</v>
@@ -3094,13 +3094,13 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B80" s="5">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C80" s="6">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3108,10 +3108,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C81" s="9">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3119,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C82" s="6">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3130,7 +3130,7 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C83" s="9">
         <v>78</v>
@@ -3141,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C84" s="6">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C85" s="9">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C86" s="6">
-        <v>18</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C87" s="9">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C88" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C89" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C90" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C91" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C92" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3240,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C93" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3251,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C94" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3262,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3273,7 +3273,7 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C96" s="6">
         <v>2</v>
@@ -3284,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46296</v>
+        <v>46091</v>
       </c>
       <c r="C97" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3295,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C98" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3317,7 +3317,7 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C100" s="6">
         <v>1</v>
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C101" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3339,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C102" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3350,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C103" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3361,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C104" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3372,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C105" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3383,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46272</v>
+        <v>46078</v>
       </c>
       <c r="C106" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3394,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C107" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3405,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C108" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3416,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C109" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3427,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C110" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3438,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C111" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3449,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3460,10 +3460,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C113" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3471,10 +3471,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3482,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C115" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3493,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3504,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3515,7 +3515,7 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C118" s="6">
         <v>2</v>
@@ -3526,10 +3526,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C119" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3537,10 +3537,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C120" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3548,10 +3548,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C121" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3559,10 +3559,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C122" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3570,10 +3570,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3581,7 +3581,7 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -3592,7 +3592,7 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3603,10 +3603,10 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C126" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3614,10 +3614,10 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C127" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3625,10 +3625,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C128" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3636,10 +3636,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C129" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3647,7 +3647,7 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3658,7 +3658,7 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3669,7 +3669,7 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3680,10 +3680,10 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C133" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3691,10 +3691,10 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3702,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C135" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3713,10 +3713,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C136" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3724,10 +3724,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46288</v>
+        <v>46212</v>
       </c>
       <c r="C137" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3735,10 +3735,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46086</v>
+        <v>46288</v>
       </c>
       <c r="C138" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3746,10 +3746,10 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46227</v>
+        <v>46086</v>
       </c>
       <c r="C139" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3757,10 +3757,10 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3768,7 +3768,7 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46188</v>
+        <v>46289</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3779,7 +3779,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46147</v>
+        <v>46188</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3790,7 +3790,7 @@
         <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3801,7 +3801,7 @@
         <v>14</v>
       </c>
       <c r="B144" s="5">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3812,7 +3812,7 @@
         <v>14</v>
       </c>
       <c r="B145" s="8">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="B146" s="5">
-        <v>46225</v>
+        <v>46190</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3831,13 +3831,13 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B147" s="8">
-        <v>46003</v>
+        <v>46225</v>
       </c>
       <c r="C147" s="9">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3845,10 +3845,10 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C148" s="6">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3856,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C149" s="9">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3867,10 +3867,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C150" s="6">
-        <v>96</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3878,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C151" s="9">
-        <v>38</v>
+        <v>96</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3889,10 +3889,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C152" s="6">
-        <v>90</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3900,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C153" s="9">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C154" s="6">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3922,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C155" s="9">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3933,10 +3933,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C156" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3944,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C157" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3955,7 +3955,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C158" s="6">
         <v>2</v>
@@ -3966,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46212</v>
+        <v>46021</v>
       </c>
       <c r="C159" s="9">
         <v>2</v>
@@ -3977,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46077</v>
+        <v>46212</v>
       </c>
       <c r="C160" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3988,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C161" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3999,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46209</v>
+        <v>46167</v>
       </c>
       <c r="C162" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="C163" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4021,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46245</v>
+        <v>46189</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4032,7 +4032,7 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46170</v>
+        <v>46245</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46210</v>
+        <v>46170</v>
       </c>
       <c r="C166" s="6">
         <v>1</v>
@@ -4054,7 +4054,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46093</v>
+        <v>46210</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4065,10 +4065,10 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46233</v>
+        <v>46093</v>
       </c>
       <c r="C168" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4076,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46090</v>
+        <v>46233</v>
       </c>
       <c r="C169" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4087,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C170" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4098,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C171" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4109,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C172" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4120,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46296</v>
+        <v>46134</v>
       </c>
       <c r="C173" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4131,10 +4131,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C174" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4142,10 +4142,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46262</v>
+        <v>46083</v>
       </c>
       <c r="C175" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4153,10 +4153,10 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46022</v>
+        <v>46262</v>
       </c>
       <c r="C176" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4164,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C177" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4175,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46287</v>
+        <v>46135</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4197,7 +4197,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46127</v>
+        <v>46287</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4219,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46286</v>
+        <v>46087</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4230,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46108</v>
+        <v>46286</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46267</v>
+        <v>46108</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46020</v>
+        <v>46267</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4263,10 +4263,10 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46168</v>
+        <v>46020</v>
       </c>
       <c r="C186" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4274,10 +4274,10 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46248</v>
+        <v>46168</v>
       </c>
       <c r="C187" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4285,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4296,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46097</v>
+        <v>46252</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4318,10 +4318,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C191" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4329,10 +4329,10 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C192" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4340,7 +4340,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46120</v>
+        <v>46080</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C196" s="6">
         <v>1</v>
@@ -4384,7 +4384,7 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4395,7 +4395,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4406,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46295</v>
+        <v>46085</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4428,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46148</v>
+        <v>46295</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4439,10 +4439,10 @@
         <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="C202" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4450,7 +4450,7 @@
         <v>3</v>
       </c>
       <c r="B203" s="8">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="C203" s="9">
         <v>2</v>
@@ -4461,10 +4461,10 @@
         <v>3</v>
       </c>
       <c r="B204" s="5">
-        <v>46258</v>
+        <v>46118</v>
       </c>
       <c r="C204" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4472,7 +4472,7 @@
         <v>3</v>
       </c>
       <c r="B205" s="8">
-        <v>46192</v>
+        <v>46258</v>
       </c>
       <c r="C205" s="9">
         <v>1</v>
@@ -4483,7 +4483,7 @@
         <v>3</v>
       </c>
       <c r="B206" s="5">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C206" s="6">
         <v>1</v>
@@ -4491,13 +4491,13 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B207" s="8">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C207" s="9">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4505,10 +4505,10 @@
         <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C208" s="6">
-        <v>132</v>
+        <v>91</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C209" s="9">
-        <v>166</v>
+        <v>132</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4527,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C210" s="6">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4538,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C211" s="9">
-        <v>15</v>
+        <v>173</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C212" s="6">
-        <v>168</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C213" s="9">
-        <v>16</v>
+        <v>168</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C214" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C215" s="9">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C216" s="6">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C217" s="9">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46258</v>
+        <v>46013</v>
       </c>
       <c r="C218" s="6">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46080</v>
+        <v>46258</v>
       </c>
       <c r="C219" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4637,7 +4637,7 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46209</v>
+        <v>46080</v>
       </c>
       <c r="C220" s="6">
         <v>2</v>
@@ -4648,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46227</v>
+        <v>46209</v>
       </c>
       <c r="C221" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46090</v>
+        <v>46227</v>
       </c>
       <c r="C222" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4703,10 +4703,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C226" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C227" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C228" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4736,10 +4736,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46265</v>
+        <v>46021</v>
       </c>
       <c r="C229" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46078</v>
+        <v>46265</v>
       </c>
       <c r="C230" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46260</v>
+        <v>46078</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,7 +4769,7 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46296</v>
+        <v>46260</v>
       </c>
       <c r="C232" s="6">
         <v>1</v>
@@ -4780,10 +4780,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46128</v>
+        <v>46296</v>
       </c>
       <c r="C233" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C234" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46255</v>
+        <v>46083</v>
       </c>
       <c r="C235" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46076</v>
+        <v>46255</v>
       </c>
       <c r="C236" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4824,10 +4824,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46294</v>
+        <v>46076</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46262</v>
+        <v>46294</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46084</v>
+        <v>46262</v>
       </c>
       <c r="C239" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4857,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46273</v>
+        <v>46084</v>
       </c>
       <c r="C240" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46099</v>
+        <v>46273</v>
       </c>
       <c r="C241" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,7 +4890,7 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46226</v>
+        <v>46154</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -4901,7 +4901,7 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="C244" s="6">
         <v>1</v>
@@ -4912,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4923,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,10 +4934,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46237</v>
+        <v>46120</v>
       </c>
       <c r="C247" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46077</v>
+        <v>46237</v>
       </c>
       <c r="C248" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,10 +4956,10 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C249" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46216</v>
+        <v>46114</v>
       </c>
       <c r="C250" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,10 +4978,10 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46037</v>
+        <v>46216</v>
       </c>
       <c r="C251" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46289</v>
+        <v>46037</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5000,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="C253" s="9">
         <v>1</v>
@@ -5011,10 +5011,10 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46020</v>
+        <v>46276</v>
       </c>
       <c r="C254" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5022,10 +5022,10 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C255" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5033,10 +5033,10 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46287</v>
+        <v>46106</v>
       </c>
       <c r="C256" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5044,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46211</v>
+        <v>46287</v>
       </c>
       <c r="C257" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5055,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5066,7 +5066,7 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="C259" s="9">
         <v>1</v>
@@ -5077,10 +5077,10 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46210</v>
+        <v>46155</v>
       </c>
       <c r="C260" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5088,10 +5088,10 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46132</v>
+        <v>46210</v>
       </c>
       <c r="C261" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5099,7 +5099,7 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C262" s="6">
         <v>1</v>
@@ -5110,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5121,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5132,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C265" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46181</v>
+        <v>46035</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46290</v>
+        <v>46181</v>
       </c>
       <c r="C267" s="9">
         <v>1</v>
@@ -5165,7 +5165,7 @@
         <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46087</v>
+        <v>46290</v>
       </c>
       <c r="C268" s="6">
         <v>1</v>
@@ -5176,10 +5176,10 @@
         <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C269" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -5187,10 +5187,10 @@
         <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C270" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5198,7 +5198,7 @@
         <v>15</v>
       </c>
       <c r="B271" s="8">
-        <v>46204</v>
+        <v>46031</v>
       </c>
       <c r="C271" s="9">
         <v>1</v>
@@ -5209,7 +5209,7 @@
         <v>15</v>
       </c>
       <c r="B272" s="5">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="C272" s="6">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="B273" s="8">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="C273" s="9">
         <v>1</v>
@@ -5231,7 +5231,7 @@
         <v>15</v>
       </c>
       <c r="B274" s="5">
-        <v>46101</v>
+        <v>46286</v>
       </c>
       <c r="C274" s="6">
         <v>1</v>
@@ -5242,7 +5242,7 @@
         <v>15</v>
       </c>
       <c r="B275" s="8">
-        <v>46213</v>
+        <v>46101</v>
       </c>
       <c r="C275" s="9">
         <v>1</v>
@@ -5253,7 +5253,7 @@
         <v>15</v>
       </c>
       <c r="B276" s="5">
-        <v>46142</v>
+        <v>46213</v>
       </c>
       <c r="C276" s="6">
         <v>1</v>
@@ -5261,13 +5261,13 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B277" s="8">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C277" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -5275,10 +5275,10 @@
         <v>21</v>
       </c>
       <c r="B278" s="5">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C278" s="6">
-        <v>38</v>
+        <v>151</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5286,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C279" s="9">
-        <v>70</v>
+        <v>37</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5297,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C280" s="6">
-        <v>109</v>
+        <v>70</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5308,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C281" s="9">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C282" s="6">
-        <v>44</v>
+        <v>145</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C283" s="9">
-        <v>126</v>
+        <v>44</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,10 +5341,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C284" s="6">
-        <v>10</v>
+        <v>126</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5352,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C285" s="9">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5363,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C286" s="6">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,10 +5374,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C287" s="9">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5385,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C288" s="6">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C289" s="9">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="C290" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46157</v>
+        <v>46014</v>
       </c>
       <c r="C291" s="9">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C292" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5440,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C293" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5451,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C294" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C295" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5473,10 +5473,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C296" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5484,10 +5484,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C297" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5495,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C298" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46192</v>
+        <v>46094</v>
       </c>
       <c r="C299" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5517,10 +5517,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46127</v>
+        <v>46192</v>
       </c>
       <c r="C300" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5528,7 +5528,7 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C301" s="9">
         <v>2</v>
@@ -5539,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C302" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C303" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5561,10 +5561,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46080</v>
+        <v>46020</v>
       </c>
       <c r="C304" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5572,7 +5572,7 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C305" s="9">
         <v>6</v>
@@ -5583,10 +5583,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46217</v>
+        <v>46015</v>
       </c>
       <c r="C306" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5594,10 +5594,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46078</v>
+        <v>46217</v>
       </c>
       <c r="C307" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5605,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46209</v>
+        <v>46078</v>
       </c>
       <c r="C308" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,10 +5616,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46237</v>
+        <v>46209</v>
       </c>
       <c r="C309" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5627,10 +5627,10 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46148</v>
+        <v>46237</v>
       </c>
       <c r="C310" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -5638,7 +5638,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C311" s="9">
         <v>2</v>
@@ -5649,10 +5649,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C312" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5660,7 +5660,7 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C313" s="9">
         <v>3</v>
@@ -5671,10 +5671,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C314" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5682,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C315" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5693,10 +5693,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C316" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5704,7 +5704,7 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C317" s="9">
         <v>3</v>
@@ -5715,10 +5715,10 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C318" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -5726,7 +5726,7 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46231</v>
+        <v>46118</v>
       </c>
       <c r="C319" s="9">
         <v>1</v>
@@ -5737,10 +5737,10 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46076</v>
+        <v>46231</v>
       </c>
       <c r="C320" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -5748,10 +5748,10 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C321" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,7 +5759,7 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="C322" s="6">
         <v>1</v>
@@ -5770,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C323" s="9">
         <v>1</v>
@@ -5781,10 +5781,10 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C324" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
@@ -5792,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C325" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,7 +5803,7 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46300</v>
+        <v>46122</v>
       </c>
       <c r="C326" s="6">
         <v>1</v>
@@ -5814,10 +5814,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46092</v>
+        <v>46300</v>
       </c>
       <c r="C327" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5825,10 +5825,10 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C328" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -5836,10 +5836,10 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C329" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -5847,7 +5847,7 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C330" s="6">
         <v>1</v>
@@ -5858,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C331" s="9">
         <v>1</v>
@@ -5869,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46295</v>
+        <v>46189</v>
       </c>
       <c r="C332" s="6">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46210</v>
+        <v>46295</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,7 +5902,7 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C335" s="9">
         <v>1</v>
@@ -5913,7 +5913,7 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C336" s="6">
         <v>1</v>
@@ -5924,10 +5924,10 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C337" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -5935,10 +5935,10 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C338" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -5946,10 +5946,10 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C339" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -5957,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C340" s="6">
         <v>3</v>
@@ -5968,10 +5968,10 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C341" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -5979,7 +5979,7 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C342" s="6">
         <v>1</v>
@@ -5990,10 +5990,10 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46098</v>
+        <v>46233</v>
       </c>
       <c r="C343" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -6001,10 +6001,10 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C344" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -6012,7 +6012,7 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C345" s="9">
         <v>1</v>
@@ -6023,7 +6023,7 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C346" s="6">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6045,7 +6045,7 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C348" s="6">
         <v>1</v>
@@ -6056,7 +6056,7 @@
         <v>21</v>
       </c>
       <c r="B349" s="8">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C349" s="9">
         <v>1</v>
@@ -6067,9 +6067,20 @@
         <v>21</v>
       </c>
       <c r="B350" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C350" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B351" s="8">
         <v>46155</v>
       </c>
-      <c r="C350" s="6">
+      <c r="C351" s="9">
         <v>1</v>
       </c>
     </row>
@@ -6527,7 +6538,7 @@
         <v>72</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -6666,7 +6677,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -6697,7 +6708,7 @@
         <v>107</v>
       </c>
       <c r="D36">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E36">
         <v>66</v>
@@ -6745,13 +6756,13 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8075,7 +8086,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="C119">
         <v>3</v>
@@ -8097,7 +8108,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="C121">
         <v>3</v>
@@ -8108,10 +8119,10 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -8119,7 +8130,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -8130,7 +8141,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -8141,7 +8152,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -8152,7 +8163,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -8163,7 +8174,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -8174,7 +8185,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -8185,7 +8196,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -8196,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -8207,7 +8218,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8218,7 +8229,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="C132">
         <v>2</v>
@@ -8306,7 +8317,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8416,7 +8427,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8482,7 +8493,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8493,7 +8504,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>67</v>
+        <v>234</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -8548,7 +8559,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8680,7 +8691,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8702,7 +8713,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8801,7 +8812,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>178</v>
+        <v>67</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8812,7 +8823,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -8944,7 +8955,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C198">
         <v>10</v>
@@ -8955,7 +8966,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C199">
         <v>10</v>
@@ -8966,10 +8977,10 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="C200">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -8977,7 +8988,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="C201">
         <v>9</v>
@@ -8988,7 +8999,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>72</v>
+        <v>192</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -8999,7 +9010,7 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>188</v>
+        <v>55</v>
       </c>
       <c r="C203">
         <v>9</v>
@@ -10088,7 +10099,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -10099,7 +10110,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -10110,7 +10121,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -10132,7 +10143,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -10154,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -10176,7 +10187,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>122</v>
+        <v>258</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -10187,7 +10198,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>241</v>
+        <v>70</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -10198,7 +10209,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -10209,7 +10220,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -10220,7 +10231,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -10231,7 +10242,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -10242,7 +10253,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -10253,10 +10264,10 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C317">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -10264,7 +10275,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>112</v>
+        <v>267</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10275,7 +10286,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10286,7 +10297,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>246</v>
+        <v>143</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10297,7 +10308,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10308,7 +10319,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10319,7 +10330,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10330,7 +10341,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10341,7 +10352,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>247</v>
+        <v>63</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10352,7 +10363,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10363,7 +10374,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10374,7 +10385,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10385,7 +10396,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>250</v>
+        <v>135</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10396,7 +10407,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10407,7 +10418,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>265</v>
+        <v>112</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10418,7 +10429,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10429,7 +10440,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>204</v>
+        <v>91</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10440,7 +10451,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10451,7 +10462,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10462,7 +10473,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -10473,7 +10484,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>116</v>
+        <v>252</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10484,7 +10495,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10495,7 +10506,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10506,7 +10517,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10517,7 +10528,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10528,7 +10539,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>249</v>
+        <v>116</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10539,7 +10550,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10550,7 +10561,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>263</v>
+        <v>167</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10561,7 +10572,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10572,7 +10583,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>143</v>
+        <v>251</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10712,7 +10723,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10734,7 +10745,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -10767,7 +10778,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -10938,7 +10949,7 @@
         <v>275</v>
       </c>
       <c r="C14">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -11059,7 +11070,7 @@
         <v>272</v>
       </c>
       <c r="C25">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -11180,7 +11191,7 @@
         <v>279</v>
       </c>
       <c r="C36">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="633" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB240A74-5943-47C6-9BF4-C6638954D7EF}"/>
+  <xr:revisionPtr revIDLastSave="638" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BFFAE97-560A-4882-9FFE-A0E0FA7478D2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1672,10 +1672,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8">
-        <v>1.04</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1774,10 +1774,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14">
-        <v>1.081</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1791,10 +1791,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15">
-        <v>1.125</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E20">
-        <v>1.0469999999999999</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C351"/>
+  <dimension ref="A1:C352"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3122,7 +3122,7 @@
         <v>46009</v>
       </c>
       <c r="C82" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3177,7 +3177,7 @@
         <v>46014</v>
       </c>
       <c r="C87" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3944,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46014</v>
+        <v>46304</v>
       </c>
       <c r="C157" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3955,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C158" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3966,7 +3966,7 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C159" s="9">
         <v>2</v>
@@ -3977,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46212</v>
+        <v>46021</v>
       </c>
       <c r="C160" s="6">
         <v>2</v>
@@ -3988,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46077</v>
+        <v>46212</v>
       </c>
       <c r="C161" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3999,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C162" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46209</v>
+        <v>46167</v>
       </c>
       <c r="C163" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4021,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="C164" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4032,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46245</v>
+        <v>46189</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4043,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46170</v>
+        <v>46245</v>
       </c>
       <c r="C166" s="6">
         <v>1</v>
@@ -4054,7 +4054,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46210</v>
+        <v>46170</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4065,7 +4065,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46093</v>
+        <v>46210</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4076,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46233</v>
+        <v>46093</v>
       </c>
       <c r="C169" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4087,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46090</v>
+        <v>46233</v>
       </c>
       <c r="C170" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4098,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C171" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4109,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C172" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4120,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C173" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4131,10 +4131,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46296</v>
+        <v>46134</v>
       </c>
       <c r="C174" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4142,10 +4142,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C175" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4153,10 +4153,10 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46262</v>
+        <v>46083</v>
       </c>
       <c r="C176" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4164,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46022</v>
+        <v>46262</v>
       </c>
       <c r="C177" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4175,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C178" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4186,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C179" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4197,7 +4197,7 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46287</v>
+        <v>46135</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46127</v>
+        <v>46287</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4219,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4230,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46286</v>
+        <v>46087</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46108</v>
+        <v>46286</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46267</v>
+        <v>46108</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4263,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46020</v>
+        <v>46267</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4274,10 +4274,10 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46168</v>
+        <v>46020</v>
       </c>
       <c r="C187" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4285,10 +4285,10 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46248</v>
+        <v>46168</v>
       </c>
       <c r="C188" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4296,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46097</v>
+        <v>46252</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4318,7 +4318,7 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4329,10 +4329,10 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C192" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4340,10 +4340,10 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C193" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46120</v>
+        <v>46080</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4373,7 +4373,7 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="C196" s="6">
         <v>1</v>
@@ -4384,7 +4384,7 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4395,7 +4395,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4406,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4428,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46295</v>
+        <v>46085</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4439,7 +4439,7 @@
         <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46148</v>
+        <v>46295</v>
       </c>
       <c r="C202" s="6">
         <v>1</v>
@@ -4450,10 +4450,10 @@
         <v>3</v>
       </c>
       <c r="B203" s="8">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="C203" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4461,7 +4461,7 @@
         <v>3</v>
       </c>
       <c r="B204" s="5">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="C204" s="6">
         <v>2</v>
@@ -4472,10 +4472,10 @@
         <v>3</v>
       </c>
       <c r="B205" s="8">
-        <v>46258</v>
+        <v>46118</v>
       </c>
       <c r="C205" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4483,7 +4483,7 @@
         <v>3</v>
       </c>
       <c r="B206" s="5">
-        <v>46192</v>
+        <v>46258</v>
       </c>
       <c r="C206" s="6">
         <v>1</v>
@@ -4494,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="B207" s="8">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C207" s="9">
         <v>1</v>
@@ -4502,13 +4502,13 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B208" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C208" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4516,10 +4516,10 @@
         <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C209" s="9">
-        <v>132</v>
+        <v>91</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4527,10 +4527,10 @@
         <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C210" s="6">
-        <v>166</v>
+        <v>132</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4538,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C211" s="9">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C212" s="6">
-        <v>15</v>
+        <v>173</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C213" s="9">
-        <v>168</v>
+        <v>15</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C214" s="6">
-        <v>16</v>
+        <v>168</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C215" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C216" s="6">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C217" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C218" s="6">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46258</v>
+        <v>46013</v>
       </c>
       <c r="C219" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4637,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46080</v>
+        <v>46258</v>
       </c>
       <c r="C220" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4648,7 +4648,7 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46209</v>
+        <v>46080</v>
       </c>
       <c r="C221" s="9">
         <v>2</v>
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46227</v>
+        <v>46209</v>
       </c>
       <c r="C222" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4670,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="C223" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,7 +4681,7 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C224" s="6">
         <v>4</v>
@@ -4692,10 +4692,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4703,10 +4703,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46090</v>
+        <v>46015</v>
       </c>
       <c r="C226" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C227" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C228" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4736,10 +4736,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C229" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46265</v>
+        <v>46021</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46078</v>
+        <v>46265</v>
       </c>
       <c r="C231" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46260</v>
+        <v>46078</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,7 +4780,7 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46296</v>
+        <v>46260</v>
       </c>
       <c r="C233" s="9">
         <v>1</v>
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46128</v>
+        <v>46296</v>
       </c>
       <c r="C234" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C235" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46255</v>
+        <v>46083</v>
       </c>
       <c r="C236" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4824,10 +4824,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46076</v>
+        <v>46255</v>
       </c>
       <c r="C237" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46294</v>
+        <v>46076</v>
       </c>
       <c r="C238" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46262</v>
+        <v>46294</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4857,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46084</v>
+        <v>46262</v>
       </c>
       <c r="C240" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46273</v>
+        <v>46084</v>
       </c>
       <c r="C241" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46099</v>
+        <v>46273</v>
       </c>
       <c r="C242" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,10 +4890,10 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C243" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,7 +4901,7 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46226</v>
+        <v>46154</v>
       </c>
       <c r="C244" s="6">
         <v>1</v>
@@ -4912,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4923,7 +4923,7 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C246" s="6">
         <v>1</v>
@@ -4934,10 +4934,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="C247" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46237</v>
+        <v>46120</v>
       </c>
       <c r="C248" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,10 +4956,10 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46077</v>
+        <v>46237</v>
       </c>
       <c r="C249" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C250" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,10 +4978,10 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46216</v>
+        <v>46114</v>
       </c>
       <c r="C251" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4989,10 +4989,10 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46037</v>
+        <v>46216</v>
       </c>
       <c r="C252" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5000,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46289</v>
+        <v>46037</v>
       </c>
       <c r="C253" s="9">
         <v>1</v>
@@ -5011,7 +5011,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5022,10 +5022,10 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46020</v>
+        <v>46276</v>
       </c>
       <c r="C255" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5033,10 +5033,10 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C256" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5044,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46287</v>
+        <v>46106</v>
       </c>
       <c r="C257" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5055,10 +5055,10 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46211</v>
+        <v>46287</v>
       </c>
       <c r="C258" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5066,7 +5066,7 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="C259" s="9">
         <v>1</v>
@@ -5077,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
@@ -5088,10 +5088,10 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46210</v>
+        <v>46155</v>
       </c>
       <c r="C261" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5099,10 +5099,10 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46132</v>
+        <v>46210</v>
       </c>
       <c r="C262" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5110,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5121,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5132,7 +5132,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C265" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46181</v>
+        <v>46035</v>
       </c>
       <c r="C267" s="9">
         <v>1</v>
@@ -5165,7 +5165,7 @@
         <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46290</v>
+        <v>46181</v>
       </c>
       <c r="C268" s="6">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46087</v>
+        <v>46290</v>
       </c>
       <c r="C269" s="9">
         <v>1</v>
@@ -5187,10 +5187,10 @@
         <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C270" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -5198,10 +5198,10 @@
         <v>15</v>
       </c>
       <c r="B271" s="8">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C271" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5209,7 +5209,7 @@
         <v>15</v>
       </c>
       <c r="B272" s="5">
-        <v>46204</v>
+        <v>46031</v>
       </c>
       <c r="C272" s="6">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="B273" s="8">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="C273" s="9">
         <v>1</v>
@@ -5231,7 +5231,7 @@
         <v>15</v>
       </c>
       <c r="B274" s="5">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="C274" s="6">
         <v>1</v>
@@ -5242,7 +5242,7 @@
         <v>15</v>
       </c>
       <c r="B275" s="8">
-        <v>46101</v>
+        <v>46286</v>
       </c>
       <c r="C275" s="9">
         <v>1</v>
@@ -5253,7 +5253,7 @@
         <v>15</v>
       </c>
       <c r="B276" s="5">
-        <v>46213</v>
+        <v>46101</v>
       </c>
       <c r="C276" s="6">
         <v>1</v>
@@ -5264,7 +5264,7 @@
         <v>15</v>
       </c>
       <c r="B277" s="8">
-        <v>46142</v>
+        <v>46213</v>
       </c>
       <c r="C277" s="9">
         <v>1</v>
@@ -5272,13 +5272,13 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B278" s="5">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C278" s="6">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -5286,10 +5286,10 @@
         <v>21</v>
       </c>
       <c r="B279" s="8">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C279" s="9">
-        <v>37</v>
+        <v>151</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -5297,10 +5297,10 @@
         <v>21</v>
       </c>
       <c r="B280" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C280" s="6">
-        <v>70</v>
+        <v>37</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -5308,10 +5308,10 @@
         <v>21</v>
       </c>
       <c r="B281" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C281" s="9">
-        <v>109</v>
+        <v>70</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C282" s="6">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C283" s="9">
-        <v>44</v>
+        <v>145</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,10 +5341,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C284" s="6">
-        <v>126</v>
+        <v>44</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5352,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C285" s="9">
-        <v>10</v>
+        <v>126</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5363,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C286" s="6">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,10 +5374,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C287" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5385,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C288" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C289" s="9">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C290" s="6">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="C291" s="9">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46157</v>
+        <v>46014</v>
       </c>
       <c r="C292" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5440,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C293" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5451,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C294" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C295" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5473,10 +5473,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C296" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5484,10 +5484,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C297" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5495,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C298" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C299" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5517,10 +5517,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46192</v>
+        <v>46094</v>
       </c>
       <c r="C300" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5528,10 +5528,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46127</v>
+        <v>46192</v>
       </c>
       <c r="C301" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5539,7 +5539,7 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C302" s="6">
         <v>2</v>
@@ -5550,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C303" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5561,10 +5561,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C304" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5572,10 +5572,10 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46080</v>
+        <v>46020</v>
       </c>
       <c r="C305" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -5583,7 +5583,7 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C306" s="6">
         <v>6</v>
@@ -5594,10 +5594,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46217</v>
+        <v>46015</v>
       </c>
       <c r="C307" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5605,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46078</v>
+        <v>46217</v>
       </c>
       <c r="C308" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,10 +5616,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46209</v>
+        <v>46078</v>
       </c>
       <c r="C309" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5627,10 +5627,10 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46237</v>
+        <v>46209</v>
       </c>
       <c r="C310" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
@@ -5638,10 +5638,10 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46148</v>
+        <v>46237</v>
       </c>
       <c r="C311" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -5649,7 +5649,7 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C312" s="6">
         <v>2</v>
@@ -5660,10 +5660,10 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C313" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -5671,7 +5671,7 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C314" s="6">
         <v>3</v>
@@ -5682,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C315" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5693,10 +5693,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C316" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5704,10 +5704,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C317" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5715,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C318" s="6">
         <v>3</v>
@@ -5726,10 +5726,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C319" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5737,7 +5737,7 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46231</v>
+        <v>46118</v>
       </c>
       <c r="C320" s="6">
         <v>1</v>
@@ -5748,10 +5748,10 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46076</v>
+        <v>46231</v>
       </c>
       <c r="C321" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,10 +5759,10 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C322" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="C323" s="9">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5792,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C325" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C326" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46300</v>
+        <v>46122</v>
       </c>
       <c r="C327" s="9">
         <v>1</v>
@@ -5825,10 +5825,10 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46092</v>
+        <v>46300</v>
       </c>
       <c r="C328" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -5836,10 +5836,10 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C329" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -5847,10 +5847,10 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C330" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C331" s="9">
         <v>1</v>
@@ -5869,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C332" s="6">
         <v>1</v>
@@ -5880,7 +5880,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46295</v>
+        <v>46189</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46210</v>
+        <v>46295</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,7 +5902,7 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C335" s="9">
         <v>1</v>
@@ -5913,7 +5913,7 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C336" s="6">
         <v>1</v>
@@ -5924,7 +5924,7 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C337" s="9">
         <v>1</v>
@@ -5935,10 +5935,10 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C338" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
@@ -5946,10 +5946,10 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C339" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -5957,10 +5957,10 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C340" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -5968,7 +5968,7 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C341" s="9">
         <v>3</v>
@@ -5979,10 +5979,10 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C342" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -5990,7 +5990,7 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C343" s="9">
         <v>1</v>
@@ -6001,10 +6001,10 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46098</v>
+        <v>46233</v>
       </c>
       <c r="C344" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -6012,10 +6012,10 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C345" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -6023,7 +6023,7 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C346" s="6">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6045,7 +6045,7 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C348" s="6">
         <v>1</v>
@@ -6056,7 +6056,7 @@
         <v>21</v>
       </c>
       <c r="B349" s="8">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C349" s="9">
         <v>1</v>
@@ -6067,7 +6067,7 @@
         <v>21</v>
       </c>
       <c r="B350" s="5">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C350" s="6">
         <v>1</v>
@@ -6078,9 +6078,20 @@
         <v>21</v>
       </c>
       <c r="B351" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C351" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B352" s="5">
         <v>46155</v>
       </c>
-      <c r="C351" s="9">
+      <c r="C352" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6229,7 +6240,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -6331,7 +6342,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -6348,7 +6359,7 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -6433,7 +6444,7 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -10679,7 +10690,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10712,7 +10723,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10828,7 +10839,7 @@
         <v>272</v>
       </c>
       <c r="C3">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10894,7 +10905,7 @@
         <v>272</v>
       </c>
       <c r="C9">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10905,7 +10916,7 @@
         <v>274</v>
       </c>
       <c r="C10">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="638" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BFFAE97-560A-4882-9FFE-A0E0FA7478D2}"/>
+  <xr:revisionPtr revIDLastSave="644" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2D732A-E50E-417B-8B3E-0AC4C672A919}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -1910,10 +1910,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22">
-        <v>1.393</v>
+        <v>1.357</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -4530,7 +4530,7 @@
         <v>46000</v>
       </c>
       <c r="C210" s="6">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -6481,7 +6481,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22">
         <v>14</v>
@@ -7954,10 +7954,10 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -7965,7 +7965,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C107">
         <v>6</v>
@@ -10734,7 +10734,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10960,7 +10960,7 @@
         <v>275</v>
       </c>
       <c r="C14">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="644" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2D732A-E50E-417B-8B3E-0AC4C672A919}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="644" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2D732A-E50E-417B-8B3E-0AC4C672A919}"/>
+  <xr:revisionPtr revIDLastSave="657" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74D78442-D354-408F-A427-B187103EC43D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1570,10 +1570,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>1.3160000000000001</v>
+        <v>1.3680000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1689,10 +1689,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9">
-        <v>1.0089999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1723,10 +1723,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11">
-        <v>1.0680000000000001</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20">
-        <v>1.0349999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E32">
-        <v>1.071</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C352"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3086,7 +3086,7 @@
         <v>16</v>
       </c>
       <c r="B79" s="8">
-        <v>46261</v>
+        <v>46316</v>
       </c>
       <c r="C79" s="9">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="5">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C80" s="6">
         <v>1</v>
@@ -3105,13 +3105,13 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B81" s="8">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C81" s="9">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3119,10 +3119,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C82" s="6">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3130,10 +3130,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C83" s="9">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3141,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C84" s="6">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C85" s="9">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C86" s="6">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C87" s="9">
-        <v>16</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C88" s="6">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C89" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C90" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C91" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C92" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3240,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C93" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3251,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C94" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3262,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C95" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3273,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C96" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3284,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C97" s="9">
         <v>2</v>
@@ -3295,10 +3295,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46296</v>
+        <v>46091</v>
       </c>
       <c r="C98" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C99" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3317,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3328,7 +3328,7 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C101" s="9">
         <v>1</v>
@@ -3339,10 +3339,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C102" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3350,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C103" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3361,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C104" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3372,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C105" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3383,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C106" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3394,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46272</v>
+        <v>46078</v>
       </c>
       <c r="C107" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3405,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C108" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3416,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C109" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3427,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C110" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3438,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C111" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3449,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3460,10 +3460,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3471,10 +3471,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C114" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3482,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3493,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C116" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3504,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3515,10 +3515,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C118" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3526,7 +3526,7 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C119" s="9">
         <v>2</v>
@@ -3537,10 +3537,10 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C120" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3548,10 +3548,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C121" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3559,10 +3559,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3570,10 +3570,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C123" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3581,10 +3581,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3592,7 +3592,7 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3614,10 +3614,10 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C127" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3625,10 +3625,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3636,10 +3636,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C129" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3647,10 +3647,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3669,7 +3669,7 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3680,7 +3680,7 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3691,10 +3691,10 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C134" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3702,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C135" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3713,10 +3713,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C136" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3724,10 +3724,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C137" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3735,10 +3735,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46288</v>
+        <v>46212</v>
       </c>
       <c r="C138" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3746,10 +3746,10 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46086</v>
+        <v>46288</v>
       </c>
       <c r="C139" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3757,10 +3757,10 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46227</v>
+        <v>46086</v>
       </c>
       <c r="C140" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3768,10 +3768,10 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="C141" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3779,7 +3779,7 @@
         <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46188</v>
+        <v>46289</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3790,7 +3790,7 @@
         <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46147</v>
+        <v>46188</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3801,7 +3801,7 @@
         <v>14</v>
       </c>
       <c r="B144" s="5">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3812,7 +3812,7 @@
         <v>14</v>
       </c>
       <c r="B145" s="8">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="B146" s="5">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3834,7 +3834,7 @@
         <v>14</v>
       </c>
       <c r="B147" s="8">
-        <v>46225</v>
+        <v>46190</v>
       </c>
       <c r="C147" s="9">
         <v>1</v>
@@ -3842,13 +3842,13 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B148" s="5">
-        <v>46003</v>
+        <v>46225</v>
       </c>
       <c r="C148" s="6">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3856,10 +3856,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C149" s="9">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3867,10 +3867,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C150" s="6">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3878,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C151" s="9">
-        <v>96</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3889,10 +3889,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C152" s="6">
-        <v>38</v>
+        <v>96</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3900,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C153" s="9">
-        <v>90</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C154" s="6">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3922,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C155" s="9">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3933,10 +3933,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C156" s="6">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3944,7 +3944,7 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46304</v>
+        <v>46009</v>
       </c>
       <c r="C157" s="9">
         <v>1</v>
@@ -3955,10 +3955,10 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46014</v>
+        <v>46304</v>
       </c>
       <c r="C158" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3966,10 +3966,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C159" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3977,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C160" s="6">
         <v>2</v>
@@ -3988,7 +3988,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46212</v>
+        <v>46021</v>
       </c>
       <c r="C161" s="9">
         <v>2</v>
@@ -3999,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46077</v>
+        <v>46212</v>
       </c>
       <c r="C162" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4021,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46209</v>
+        <v>46167</v>
       </c>
       <c r="C164" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4032,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="C165" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4043,10 +4043,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46245</v>
+        <v>46189</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4054,7 +4054,7 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46170</v>
+        <v>46315</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4065,7 +4065,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4076,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4087,10 +4087,10 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46233</v>
+        <v>46210</v>
       </c>
       <c r="C170" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4098,10 +4098,10 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="C171" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4109,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46078</v>
+        <v>46233</v>
       </c>
       <c r="C172" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4120,7 +4120,7 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C173" s="9">
         <v>4</v>
@@ -4131,10 +4131,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C174" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4142,10 +4142,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46296</v>
+        <v>46084</v>
       </c>
       <c r="C175" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4153,10 +4153,10 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C176" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4164,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46262</v>
+        <v>46296</v>
       </c>
       <c r="C177" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4175,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4186,7 +4186,7 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46114</v>
+        <v>46316</v>
       </c>
       <c r="C179" s="9">
         <v>2</v>
@@ -4197,10 +4197,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46135</v>
+        <v>46262</v>
       </c>
       <c r="C180" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4208,7 +4208,7 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46287</v>
+        <v>46022</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4219,10 +4219,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C182" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4230,7 +4230,7 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46087</v>
+        <v>46135</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46108</v>
+        <v>46127</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4263,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46267</v>
+        <v>46087</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4274,7 +4274,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46020</v>
+        <v>46286</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4285,10 +4285,10 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46168</v>
+        <v>46108</v>
       </c>
       <c r="C188" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4296,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46252</v>
+        <v>46020</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4318,10 +4318,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46097</v>
+        <v>46168</v>
       </c>
       <c r="C191" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4329,7 +4329,7 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46177</v>
+        <v>46248</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4340,10 +4340,10 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46161</v>
+        <v>46252</v>
       </c>
       <c r="C193" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46080</v>
+        <v>46177</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4373,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46120</v>
+        <v>46161</v>
       </c>
       <c r="C196" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4384,7 +4384,7 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46101</v>
+        <v>46129</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4395,7 +4395,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46155</v>
+        <v>46080</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4406,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46150</v>
+        <v>46120</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46141</v>
+        <v>46101</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4428,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46085</v>
+        <v>46155</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4439,7 +4439,7 @@
         <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46295</v>
+        <v>46150</v>
       </c>
       <c r="C202" s="6">
         <v>1</v>
@@ -4450,7 +4450,7 @@
         <v>3</v>
       </c>
       <c r="B203" s="8">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C203" s="9">
         <v>1</v>
@@ -4461,10 +4461,10 @@
         <v>3</v>
       </c>
       <c r="B204" s="5">
-        <v>46126</v>
+        <v>46085</v>
       </c>
       <c r="C204" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4472,10 +4472,10 @@
         <v>3</v>
       </c>
       <c r="B205" s="8">
-        <v>46118</v>
+        <v>46295</v>
       </c>
       <c r="C205" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4483,7 +4483,7 @@
         <v>3</v>
       </c>
       <c r="B206" s="5">
-        <v>46258</v>
+        <v>46148</v>
       </c>
       <c r="C206" s="6">
         <v>1</v>
@@ -4494,10 +4494,10 @@
         <v>3</v>
       </c>
       <c r="B207" s="8">
-        <v>46192</v>
+        <v>46126</v>
       </c>
       <c r="C207" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4505,43 +4505,43 @@
         <v>3</v>
       </c>
       <c r="B208" s="5">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C208" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B209" s="8">
-        <v>46003</v>
+        <v>46258</v>
       </c>
       <c r="C209" s="9">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B210" s="5">
-        <v>46000</v>
+        <v>46192</v>
       </c>
       <c r="C210" s="6">
-        <v>131</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B211" s="8">
-        <v>46006</v>
+        <v>46079</v>
       </c>
       <c r="C211" s="9">
-        <v>166</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4549,10 +4549,10 @@
         <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C212" s="6">
-        <v>173</v>
+        <v>91</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C213" s="9">
-        <v>15</v>
+        <v>131</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C214" s="6">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="C215" s="9">
-        <v>16</v>
+        <v>173</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C216" s="6">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C217" s="9">
-        <v>25</v>
+        <v>168</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C218" s="6">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C219" s="9">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4637,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46258</v>
+        <v>46008</v>
       </c>
       <c r="C220" s="6">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4648,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46080</v>
+        <v>46007</v>
       </c>
       <c r="C221" s="9">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46209</v>
+        <v>46013</v>
       </c>
       <c r="C222" s="6">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4670,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,10 +4681,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46192</v>
+        <v>46080</v>
       </c>
       <c r="C224" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4692,10 +4692,10 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46079</v>
+        <v>46209</v>
       </c>
       <c r="C225" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4703,7 +4703,7 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46015</v>
+        <v>46227</v>
       </c>
       <c r="C226" s="6">
         <v>1</v>
@@ -4714,7 +4714,7 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46090</v>
+        <v>46192</v>
       </c>
       <c r="C227" s="9">
         <v>4</v>
@@ -4725,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C228" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4736,10 +4736,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C229" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46021</v>
+        <v>46090</v>
       </c>
       <c r="C230" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46265</v>
+        <v>46085</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="C232" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,10 +4780,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46260</v>
+        <v>46021</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4791,7 +4791,7 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46296</v>
+        <v>46265</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4802,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C235" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46083</v>
+        <v>46260</v>
       </c>
       <c r="C236" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4824,10 +4824,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46255</v>
+        <v>46296</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46076</v>
+        <v>46128</v>
       </c>
       <c r="C238" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46294</v>
+        <v>46083</v>
       </c>
       <c r="C239" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4857,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="C240" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46084</v>
+        <v>46076</v>
       </c>
       <c r="C241" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,10 +4890,10 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46099</v>
+        <v>46262</v>
       </c>
       <c r="C243" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,10 +4901,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46154</v>
+        <v>46084</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,7 +4912,7 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46226</v>
+        <v>46273</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -4923,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,7 +4934,7 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46022</v>
+        <v>46154</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -4945,10 +4945,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46120</v>
+        <v>46226</v>
       </c>
       <c r="C248" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4956,10 +4956,10 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46237</v>
+        <v>46092</v>
       </c>
       <c r="C249" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4967,10 +4967,10 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46077</v>
+        <v>46022</v>
       </c>
       <c r="C250" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4978,10 +4978,10 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C251" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4989,10 +4989,10 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="C252" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5000,10 +5000,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46037</v>
+        <v>46077</v>
       </c>
       <c r="C253" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5011,7 +5011,7 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46289</v>
+        <v>46114</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5022,10 +5022,10 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46276</v>
+        <v>46216</v>
       </c>
       <c r="C255" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5033,10 +5033,10 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C256" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5044,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46106</v>
+        <v>46289</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5055,10 +5055,10 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46287</v>
+        <v>46276</v>
       </c>
       <c r="C258" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5066,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46211</v>
+        <v>46020</v>
       </c>
       <c r="C259" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5077,7 +5077,7 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46239</v>
+        <v>46106</v>
       </c>
       <c r="C260" s="6">
         <v>1</v>
@@ -5088,10 +5088,10 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46155</v>
+        <v>46287</v>
       </c>
       <c r="C261" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5099,10 +5099,10 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C262" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5110,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46132</v>
+        <v>46239</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5121,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46108</v>
+        <v>46155</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5132,10 +5132,10 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46148</v>
+        <v>46210</v>
       </c>
       <c r="C265" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5143,7 +5143,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46035</v>
+        <v>46108</v>
       </c>
       <c r="C267" s="9">
         <v>1</v>
@@ -5165,7 +5165,7 @@
         <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46181</v>
+        <v>46148</v>
       </c>
       <c r="C268" s="6">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46290</v>
+        <v>46118</v>
       </c>
       <c r="C269" s="9">
         <v>1</v>
@@ -5187,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46087</v>
+        <v>46035</v>
       </c>
       <c r="C270" s="6">
         <v>1</v>
@@ -5198,10 +5198,10 @@
         <v>15</v>
       </c>
       <c r="B271" s="8">
-        <v>46030</v>
+        <v>46181</v>
       </c>
       <c r="C271" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -5209,7 +5209,7 @@
         <v>15</v>
       </c>
       <c r="B272" s="5">
-        <v>46031</v>
+        <v>46290</v>
       </c>
       <c r="C272" s="6">
         <v>1</v>
@@ -5220,7 +5220,7 @@
         <v>15</v>
       </c>
       <c r="B273" s="8">
-        <v>46204</v>
+        <v>46087</v>
       </c>
       <c r="C273" s="9">
         <v>1</v>
@@ -5231,10 +5231,10 @@
         <v>15</v>
       </c>
       <c r="B274" s="5">
-        <v>46176</v>
+        <v>46030</v>
       </c>
       <c r="C274" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5242,7 +5242,7 @@
         <v>15</v>
       </c>
       <c r="B275" s="8">
-        <v>46286</v>
+        <v>46031</v>
       </c>
       <c r="C275" s="9">
         <v>1</v>
@@ -5253,7 +5253,7 @@
         <v>15</v>
       </c>
       <c r="B276" s="5">
-        <v>46101</v>
+        <v>46204</v>
       </c>
       <c r="C276" s="6">
         <v>1</v>
@@ -5264,7 +5264,7 @@
         <v>15</v>
       </c>
       <c r="B277" s="8">
-        <v>46213</v>
+        <v>46176</v>
       </c>
       <c r="C277" s="9">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         <v>15</v>
       </c>
       <c r="B278" s="5">
-        <v>46142</v>
+        <v>46286</v>
       </c>
       <c r="C278" s="6">
         <v>1</v>
@@ -5283,35 +5283,35 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B279" s="8">
-        <v>46001</v>
+        <v>46101</v>
       </c>
       <c r="C279" s="9">
-        <v>151</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B280" s="5">
-        <v>46008</v>
+        <v>46213</v>
       </c>
       <c r="C280" s="6">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B281" s="8">
-        <v>46003</v>
+        <v>46142</v>
       </c>
       <c r="C281" s="9">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>21</v>
       </c>
       <c r="B282" s="5">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C282" s="6">
-        <v>109</v>
+        <v>151</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5330,10 +5330,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C283" s="9">
-        <v>145</v>
+        <v>37</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5341,10 +5341,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C284" s="6">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5352,10 +5352,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C285" s="9">
-        <v>126</v>
+        <v>109</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5363,10 +5363,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46084</v>
+        <v>46006</v>
       </c>
       <c r="C286" s="6">
-        <v>10</v>
+        <v>145</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5374,10 +5374,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C287" s="9">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5385,10 +5385,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="C288" s="6">
-        <v>19</v>
+        <v>126</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5396,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46021</v>
+        <v>46084</v>
       </c>
       <c r="C289" s="9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5407,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C290" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5418,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46083</v>
+        <v>46010</v>
       </c>
       <c r="C291" s="9">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,10 +5429,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="C292" s="6">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5440,10 +5440,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46157</v>
+        <v>46009</v>
       </c>
       <c r="C293" s="9">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5451,10 +5451,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="C294" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46167</v>
+        <v>46014</v>
       </c>
       <c r="C295" s="9">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5473,7 +5473,7 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46035</v>
+        <v>46157</v>
       </c>
       <c r="C296" s="6">
         <v>2</v>
@@ -5484,7 +5484,7 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C297" s="9">
         <v>3</v>
@@ -5495,10 +5495,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46120</v>
+        <v>46167</v>
       </c>
       <c r="C298" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,10 +5506,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46114</v>
+        <v>46035</v>
       </c>
       <c r="C299" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5517,7 +5517,7 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="C300" s="6">
         <v>3</v>
@@ -5528,10 +5528,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46192</v>
+        <v>46120</v>
       </c>
       <c r="C301" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5539,10 +5539,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C302" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,10 +5550,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C303" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5561,7 +5561,7 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46090</v>
+        <v>46192</v>
       </c>
       <c r="C304" s="6">
         <v>1</v>
@@ -5572,7 +5572,7 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C305" s="9">
         <v>2</v>
@@ -5583,10 +5583,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46080</v>
+        <v>46091</v>
       </c>
       <c r="C306" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5594,10 +5594,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C307" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5605,10 +5605,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46217</v>
+        <v>46020</v>
       </c>
       <c r="C308" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5616,10 +5616,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="C309" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5627,7 +5627,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46209</v>
+        <v>46015</v>
       </c>
       <c r="C310" s="6">
         <v>6</v>
@@ -5638,7 +5638,7 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46237</v>
+        <v>46217</v>
       </c>
       <c r="C311" s="9">
         <v>1</v>
@@ -5649,10 +5649,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C312" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5660,10 +5660,10 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46105</v>
+        <v>46209</v>
       </c>
       <c r="C313" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -5671,10 +5671,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46087</v>
+        <v>46237</v>
       </c>
       <c r="C314" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5682,10 +5682,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46107</v>
+        <v>46148</v>
       </c>
       <c r="C315" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5693,10 +5693,10 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46086</v>
+        <v>46105</v>
       </c>
       <c r="C316" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -5704,10 +5704,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46106</v>
+        <v>46087</v>
       </c>
       <c r="C317" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5715,7 +5715,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46150</v>
+        <v>46107</v>
       </c>
       <c r="C318" s="6">
         <v>3</v>
@@ -5726,10 +5726,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46104</v>
+        <v>46086</v>
       </c>
       <c r="C319" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5737,7 +5737,7 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46118</v>
+        <v>46106</v>
       </c>
       <c r="C320" s="6">
         <v>1</v>
@@ -5748,10 +5748,10 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46231</v>
+        <v>46150</v>
       </c>
       <c r="C321" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -5759,10 +5759,10 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="C322" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46182</v>
+        <v>46118</v>
       </c>
       <c r="C323" s="9">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46188</v>
+        <v>46231</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5792,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C325" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46093</v>
+        <v>46182</v>
       </c>
       <c r="C326" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46122</v>
+        <v>46188</v>
       </c>
       <c r="C327" s="9">
         <v>1</v>
@@ -5825,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46300</v>
+        <v>46154</v>
       </c>
       <c r="C328" s="6">
         <v>1</v>
@@ -5836,7 +5836,7 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C329" s="9">
         <v>3</v>
@@ -5847,10 +5847,10 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C330" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46287</v>
+        <v>46300</v>
       </c>
       <c r="C331" s="9">
         <v>1</v>
@@ -5869,10 +5869,10 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46133</v>
+        <v>46092</v>
       </c>
       <c r="C332" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -5880,10 +5880,10 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46189</v>
+        <v>46156</v>
       </c>
       <c r="C333" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -5891,7 +5891,7 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="C334" s="6">
         <v>1</v>
@@ -5902,7 +5902,7 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46210</v>
+        <v>46133</v>
       </c>
       <c r="C335" s="9">
         <v>1</v>
@@ -5913,7 +5913,7 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46232</v>
+        <v>46189</v>
       </c>
       <c r="C336" s="6">
         <v>1</v>
@@ -5924,7 +5924,7 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46126</v>
+        <v>46295</v>
       </c>
       <c r="C337" s="9">
         <v>1</v>
@@ -5935,7 +5935,7 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46022</v>
+        <v>46210</v>
       </c>
       <c r="C338" s="6">
         <v>1</v>
@@ -5946,10 +5946,10 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46100</v>
+        <v>46232</v>
       </c>
       <c r="C339" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
@@ -5957,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46101</v>
+        <v>46126</v>
       </c>
       <c r="C340" s="6">
         <v>1</v>
@@ -5968,10 +5968,10 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46097</v>
+        <v>46022</v>
       </c>
       <c r="C341" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
@@ -5979,10 +5979,10 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46077</v>
+        <v>46100</v>
       </c>
       <c r="C342" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -5990,7 +5990,7 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="C343" s="9">
         <v>1</v>
@@ -6001,10 +6001,10 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46233</v>
+        <v>46097</v>
       </c>
       <c r="C344" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -6012,10 +6012,10 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46098</v>
+        <v>46077</v>
       </c>
       <c r="C345" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -6023,7 +6023,7 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="C346" s="6">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46253</v>
+        <v>46233</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6045,10 +6045,10 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46142</v>
+        <v>46098</v>
       </c>
       <c r="C348" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -6056,7 +6056,7 @@
         <v>21</v>
       </c>
       <c r="B349" s="8">
-        <v>46244</v>
+        <v>46113</v>
       </c>
       <c r="C349" s="9">
         <v>1</v>
@@ -6067,7 +6067,7 @@
         <v>21</v>
       </c>
       <c r="B350" s="5">
-        <v>46153</v>
+        <v>46253</v>
       </c>
       <c r="C350" s="6">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         <v>21</v>
       </c>
       <c r="B351" s="8">
-        <v>46031</v>
+        <v>46142</v>
       </c>
       <c r="C351" s="9">
         <v>1</v>
@@ -6089,9 +6089,42 @@
         <v>21</v>
       </c>
       <c r="B352" s="5">
+        <v>46244</v>
+      </c>
+      <c r="C352" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B353" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C353" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B354" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C354" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B355" s="8">
         <v>46155</v>
       </c>
-      <c r="C352" s="6">
+      <c r="C355" s="9">
         <v>1</v>
       </c>
     </row>
@@ -6144,7 +6177,7 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6263,7 +6296,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -6297,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -6444,7 +6477,7 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -6654,7 +6687,7 @@
         <v>242</v>
       </c>
       <c r="E32">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -8900,7 +8933,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>66</v>
+        <v>187</v>
       </c>
       <c r="C192">
         <v>15</v>
@@ -8911,10 +8944,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="C193">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8922,7 +8955,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C194">
         <v>14</v>
@@ -10690,7 +10723,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10701,7 +10734,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10723,7 +10756,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10767,7 +10800,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10839,7 +10872,7 @@
         <v>272</v>
       </c>
       <c r="C3">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10894,7 +10927,7 @@
         <v>271</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -11081,7 +11114,7 @@
         <v>272</v>
       </c>
       <c r="C25">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="657" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74D78442-D354-408F-A427-B187103EC43D}"/>
+  <xr:revisionPtr revIDLastSave="667" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6597354-80E8-4B32-8967-D2D6C866E6D9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="4" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1621,10 +1621,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5">
-        <v>1.2350000000000001</v>
+        <v>1.2649999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1961,10 +1961,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25">
-        <v>1.0109999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2046,10 +2046,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E30">
-        <v>0.98299999999999998</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E32">
-        <v>1.073</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2182,10 +2182,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E38">
-        <v>1.093</v>
+        <v>1.0880000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C355"/>
+  <dimension ref="A1:C356"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2448,10 +2448,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="8">
-        <v>46021</v>
+        <v>46316</v>
       </c>
       <c r="C21" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2459,10 +2459,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="5">
-        <v>46080</v>
+        <v>46021</v>
       </c>
       <c r="C22" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2470,10 +2470,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="8">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="C23" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2481,7 +2481,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46273</v>
+        <v>46087</v>
       </c>
       <c r="C24" s="6">
         <v>3</v>
@@ -2492,10 +2492,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46254</v>
+        <v>46273</v>
       </c>
       <c r="C25" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2503,10 +2503,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46022</v>
+        <v>46254</v>
       </c>
       <c r="C26" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2514,10 +2514,10 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46161</v>
+        <v>46022</v>
       </c>
       <c r="C27" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2525,10 +2525,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46086</v>
+        <v>46161</v>
       </c>
       <c r="C28" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2536,7 +2536,7 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46211</v>
+        <v>46086</v>
       </c>
       <c r="C29" s="9">
         <v>3</v>
@@ -2547,10 +2547,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46020</v>
+        <v>46211</v>
       </c>
       <c r="C30" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2558,10 +2558,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C31" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2569,10 +2569,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46136</v>
+        <v>46076</v>
       </c>
       <c r="C32" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2580,10 +2580,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46078</v>
+        <v>46136</v>
       </c>
       <c r="C33" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2591,10 +2591,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46176</v>
+        <v>46078</v>
       </c>
       <c r="C34" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2602,10 +2602,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="C35" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2613,7 +2613,7 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46262</v>
+        <v>46182</v>
       </c>
       <c r="C36" s="6">
         <v>1</v>
@@ -2624,10 +2624,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46098</v>
+        <v>46262</v>
       </c>
       <c r="C37" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2635,7 +2635,7 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46181</v>
+        <v>46098</v>
       </c>
       <c r="C38" s="6">
         <v>3</v>
@@ -2646,10 +2646,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46084</v>
+        <v>46181</v>
       </c>
       <c r="C39" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2657,10 +2657,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C40" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2668,10 +2668,10 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C41" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2679,7 +2679,7 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C42" s="6">
         <v>2</v>
@@ -2690,10 +2690,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C43" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2701,10 +2701,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C44" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2712,10 +2712,10 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46304</v>
+        <v>46141</v>
       </c>
       <c r="C45" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2723,7 +2723,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46132</v>
+        <v>46304</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -2734,10 +2734,10 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46246</v>
+        <v>46132</v>
       </c>
       <c r="C47" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2745,7 +2745,7 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46127</v>
+        <v>46246</v>
       </c>
       <c r="C48" s="6">
         <v>2</v>
@@ -2756,10 +2756,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46225</v>
+        <v>46127</v>
       </c>
       <c r="C49" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2767,10 +2767,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46293</v>
+        <v>46225</v>
       </c>
       <c r="C50" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2778,10 +2778,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46212</v>
+        <v>46293</v>
       </c>
       <c r="C51" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2789,10 +2789,10 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46091</v>
+        <v>46212</v>
       </c>
       <c r="C52" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2800,10 +2800,10 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C53" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2811,7 +2811,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46276</v>
+        <v>46106</v>
       </c>
       <c r="C56" s="6">
         <v>1</v>
@@ -2844,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46113</v>
+        <v>46276</v>
       </c>
       <c r="C57" s="9">
         <v>1</v>
@@ -2855,7 +2855,7 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46296</v>
+        <v>46113</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
@@ -2866,10 +2866,10 @@
         <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46290</v>
+        <v>46317</v>
       </c>
       <c r="C59" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2877,10 +2877,10 @@
         <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46090</v>
+        <v>46296</v>
       </c>
       <c r="C60" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2888,10 +2888,10 @@
         <v>16</v>
       </c>
       <c r="B61" s="8">
-        <v>46210</v>
+        <v>46290</v>
       </c>
       <c r="C61" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2899,10 +2899,10 @@
         <v>16</v>
       </c>
       <c r="B62" s="5">
-        <v>46287</v>
+        <v>46090</v>
       </c>
       <c r="C62" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2910,10 +2910,10 @@
         <v>16</v>
       </c>
       <c r="B63" s="8">
-        <v>46289</v>
+        <v>46210</v>
       </c>
       <c r="C63" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2921,7 +2921,7 @@
         <v>16</v>
       </c>
       <c r="B64" s="5">
-        <v>46148</v>
+        <v>46287</v>
       </c>
       <c r="C64" s="6">
         <v>1</v>
@@ -2932,7 +2932,7 @@
         <v>16</v>
       </c>
       <c r="B65" s="8">
-        <v>46175</v>
+        <v>46289</v>
       </c>
       <c r="C65" s="9">
         <v>1</v>
@@ -2943,7 +2943,7 @@
         <v>16</v>
       </c>
       <c r="B66" s="5">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="C66" s="6">
         <v>1</v>
@@ -2954,7 +2954,7 @@
         <v>16</v>
       </c>
       <c r="B67" s="8">
-        <v>46295</v>
+        <v>46175</v>
       </c>
       <c r="C67" s="9">
         <v>1</v>
@@ -2965,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="5">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -2976,10 +2976,10 @@
         <v>16</v>
       </c>
       <c r="B69" s="8">
-        <v>46177</v>
+        <v>46295</v>
       </c>
       <c r="C69" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2987,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B70" s="5">
-        <v>46300</v>
+        <v>46093</v>
       </c>
       <c r="C70" s="6">
         <v>1</v>
@@ -2998,10 +2998,10 @@
         <v>16</v>
       </c>
       <c r="B71" s="8">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C71" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3009,7 +3009,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46245</v>
+        <v>46300</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46213</v>
+        <v>46156</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3031,7 +3031,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46092</v>
+        <v>46245</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3042,7 +3042,7 @@
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46226</v>
+        <v>46213</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -3053,7 +3053,7 @@
         <v>16</v>
       </c>
       <c r="B76" s="5">
-        <v>46238</v>
+        <v>46092</v>
       </c>
       <c r="C76" s="6">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>16</v>
       </c>
       <c r="B77" s="8">
-        <v>46188</v>
+        <v>46226</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -3075,7 +3075,7 @@
         <v>16</v>
       </c>
       <c r="B78" s="5">
-        <v>46101</v>
+        <v>46238</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
@@ -3086,7 +3086,7 @@
         <v>16</v>
       </c>
       <c r="B79" s="8">
-        <v>46316</v>
+        <v>46188</v>
       </c>
       <c r="C79" s="9">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="5">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C80" s="6">
         <v>1</v>
@@ -3108,7 +3108,7 @@
         <v>16</v>
       </c>
       <c r="B81" s="8">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C81" s="9">
         <v>1</v>
@@ -3116,13 +3116,13 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B82" s="5">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C82" s="6">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3130,10 +3130,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C83" s="9">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3141,10 +3141,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C84" s="6">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,10 +3152,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C85" s="9">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3163,10 +3163,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C86" s="6">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3174,10 +3174,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C87" s="9">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C88" s="6">
-        <v>16</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C89" s="9">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3207,10 +3207,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C90" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3218,10 +3218,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C91" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3229,10 +3229,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C92" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3240,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C93" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3251,10 +3251,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C94" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3262,10 +3262,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C95" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3273,10 +3273,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C96" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3284,10 +3284,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C97" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3295,7 +3295,7 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C98" s="6">
         <v>2</v>
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46296</v>
+        <v>46091</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3317,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C100" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3328,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C101" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3339,7 +3339,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46210</v>
+        <v>46105</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -3350,10 +3350,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C103" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3361,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C104" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3372,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C105" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3383,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3394,10 +3394,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C107" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3405,10 +3405,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46272</v>
+        <v>46078</v>
       </c>
       <c r="C108" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3416,10 +3416,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C109" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3427,10 +3427,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C110" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3438,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C111" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3449,10 +3449,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C112" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3460,10 +3460,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C113" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3471,10 +3471,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3482,10 +3482,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C115" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3493,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3504,10 +3504,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C117" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3515,10 +3515,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3526,10 +3526,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C119" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3537,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C120" s="6">
         <v>2</v>
@@ -3548,10 +3548,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3559,10 +3559,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C122" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3570,10 +3570,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3581,10 +3581,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C124" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3592,10 +3592,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C125" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3603,7 +3603,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3625,10 +3625,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C128" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3636,10 +3636,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C129" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3647,10 +3647,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C130" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3658,10 +3658,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C131" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3669,7 +3669,7 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3680,7 +3680,7 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3691,7 +3691,7 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3702,10 +3702,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C135" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3713,10 +3713,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C136" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3724,10 +3724,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C137" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3735,10 +3735,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C138" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3746,10 +3746,10 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46288</v>
+        <v>46212</v>
       </c>
       <c r="C139" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3757,10 +3757,10 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46086</v>
+        <v>46288</v>
       </c>
       <c r="C140" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3768,10 +3768,10 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46227</v>
+        <v>46086</v>
       </c>
       <c r="C141" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3779,10 +3779,10 @@
         <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="C142" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3790,7 +3790,7 @@
         <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46188</v>
+        <v>46289</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3801,7 +3801,7 @@
         <v>14</v>
       </c>
       <c r="B144" s="5">
-        <v>46147</v>
+        <v>46188</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3812,7 +3812,7 @@
         <v>14</v>
       </c>
       <c r="B145" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="B146" s="5">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3834,7 +3834,7 @@
         <v>14</v>
       </c>
       <c r="B147" s="8">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="C147" s="9">
         <v>1</v>
@@ -3845,7 +3845,7 @@
         <v>14</v>
       </c>
       <c r="B148" s="5">
-        <v>46225</v>
+        <v>46190</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -3853,13 +3853,13 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B149" s="8">
-        <v>46003</v>
+        <v>46225</v>
       </c>
       <c r="C149" s="9">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3867,10 +3867,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C150" s="6">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3878,10 +3878,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C151" s="9">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3889,10 +3889,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C152" s="6">
-        <v>96</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3900,10 +3900,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C153" s="9">
-        <v>38</v>
+        <v>96</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,10 +3911,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C154" s="6">
-        <v>90</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3922,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C155" s="9">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3933,10 +3933,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C156" s="6">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3944,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3955,7 +3955,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46304</v>
+        <v>46009</v>
       </c>
       <c r="C158" s="6">
         <v>1</v>
@@ -3966,10 +3966,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46014</v>
+        <v>46304</v>
       </c>
       <c r="C159" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3977,10 +3977,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C160" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3988,7 +3988,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C161" s="9">
         <v>2</v>
@@ -3999,7 +3999,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46212</v>
+        <v>46021</v>
       </c>
       <c r="C162" s="6">
         <v>2</v>
@@ -4010,10 +4010,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46077</v>
+        <v>46212</v>
       </c>
       <c r="C163" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4021,10 +4021,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4032,10 +4032,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46209</v>
+        <v>46167</v>
       </c>
       <c r="C165" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4043,10 +4043,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="C166" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4054,10 +4054,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46315</v>
+        <v>46189</v>
       </c>
       <c r="C167" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4065,7 +4065,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46245</v>
+        <v>46315</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4076,7 +4076,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46170</v>
+        <v>46245</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4087,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46210</v>
+        <v>46170</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4098,7 +4098,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46093</v>
+        <v>46210</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4109,10 +4109,10 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46233</v>
+        <v>46093</v>
       </c>
       <c r="C172" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4120,10 +4120,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46090</v>
+        <v>46233</v>
       </c>
       <c r="C173" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4131,10 +4131,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C174" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4142,10 +4142,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C175" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4153,10 +4153,10 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C176" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4164,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46296</v>
+        <v>46134</v>
       </c>
       <c r="C177" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4175,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C178" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4186,10 +4186,10 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46316</v>
+        <v>46083</v>
       </c>
       <c r="C179" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4197,10 +4197,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46262</v>
+        <v>46316</v>
       </c>
       <c r="C180" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4208,10 +4208,10 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46022</v>
+        <v>46262</v>
       </c>
       <c r="C181" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4219,10 +4219,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C182" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4230,10 +4230,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4241,7 +4241,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46287</v>
+        <v>46135</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46127</v>
+        <v>46287</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4263,7 +4263,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4274,7 +4274,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46286</v>
+        <v>46087</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4285,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46108</v>
+        <v>46286</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4296,7 +4296,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46267</v>
+        <v>46108</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46020</v>
+        <v>46267</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4318,10 +4318,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46168</v>
+        <v>46020</v>
       </c>
       <c r="C191" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4329,10 +4329,10 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46248</v>
+        <v>46168</v>
       </c>
       <c r="C192" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4340,7 +4340,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4351,7 +4351,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46097</v>
+        <v>46252</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4362,7 +4362,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4373,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C196" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4384,10 +4384,10 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C197" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4395,7 +4395,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4406,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46120</v>
+        <v>46080</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4417,7 +4417,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4428,7 +4428,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4439,7 +4439,7 @@
         <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C202" s="6">
         <v>1</v>
@@ -4450,7 +4450,7 @@
         <v>3</v>
       </c>
       <c r="B203" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C203" s="9">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>3</v>
       </c>
       <c r="B204" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C204" s="6">
         <v>1</v>
@@ -4472,7 +4472,7 @@
         <v>3</v>
       </c>
       <c r="B205" s="8">
-        <v>46295</v>
+        <v>46085</v>
       </c>
       <c r="C205" s="9">
         <v>1</v>
@@ -4483,7 +4483,7 @@
         <v>3</v>
       </c>
       <c r="B206" s="5">
-        <v>46148</v>
+        <v>46295</v>
       </c>
       <c r="C206" s="6">
         <v>1</v>
@@ -4494,10 +4494,10 @@
         <v>3</v>
       </c>
       <c r="B207" s="8">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="C207" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4505,7 +4505,7 @@
         <v>3</v>
       </c>
       <c r="B208" s="5">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="C208" s="6">
         <v>2</v>
@@ -4516,10 +4516,10 @@
         <v>3</v>
       </c>
       <c r="B209" s="8">
-        <v>46258</v>
+        <v>46118</v>
       </c>
       <c r="C209" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4527,7 +4527,7 @@
         <v>3</v>
       </c>
       <c r="B210" s="5">
-        <v>46192</v>
+        <v>46258</v>
       </c>
       <c r="C210" s="6">
         <v>1</v>
@@ -4538,7 +4538,7 @@
         <v>3</v>
       </c>
       <c r="B211" s="8">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C211" s="9">
         <v>1</v>
@@ -4546,13 +4546,13 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B212" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C212" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4560,10 +4560,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C213" s="9">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C214" s="6">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4582,10 +4582,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C215" s="9">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4593,10 +4593,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C216" s="6">
-        <v>15</v>
+        <v>173</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4604,10 +4604,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C217" s="9">
-        <v>168</v>
+        <v>15</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4615,10 +4615,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C218" s="6">
-        <v>16</v>
+        <v>168</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4626,10 +4626,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C219" s="9">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4637,10 +4637,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C220" s="6">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4648,10 +4648,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C221" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4659,10 +4659,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C222" s="6">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4670,10 +4670,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46258</v>
+        <v>46013</v>
       </c>
       <c r="C223" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4681,10 +4681,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46080</v>
+        <v>46258</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4692,7 +4692,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46209</v>
+        <v>46080</v>
       </c>
       <c r="C225" s="9">
         <v>2</v>
@@ -4703,10 +4703,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46227</v>
+        <v>46209</v>
       </c>
       <c r="C226" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="C227" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4725,7 +4725,7 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C228" s="6">
         <v>4</v>
@@ -4736,10 +4736,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C229" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4747,10 +4747,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46090</v>
+        <v>46015</v>
       </c>
       <c r="C230" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C231" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4769,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C232" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,10 +4780,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C233" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4791,10 +4791,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46265</v>
+        <v>46021</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,10 +4802,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46078</v>
+        <v>46265</v>
       </c>
       <c r="C235" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,10 +4813,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46260</v>
+        <v>46078</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4824,7 +4824,7 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46296</v>
+        <v>46260</v>
       </c>
       <c r="C237" s="9">
         <v>1</v>
@@ -4835,10 +4835,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46128</v>
+        <v>46296</v>
       </c>
       <c r="C238" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4846,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C239" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4857,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46255</v>
+        <v>46083</v>
       </c>
       <c r="C240" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4868,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46076</v>
+        <v>46255</v>
       </c>
       <c r="C241" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4879,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46294</v>
+        <v>46076</v>
       </c>
       <c r="C242" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,10 +4890,10 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46262</v>
+        <v>46294</v>
       </c>
       <c r="C243" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,10 +4901,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46084</v>
+        <v>46262</v>
       </c>
       <c r="C244" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,10 +4912,10 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46273</v>
+        <v>46084</v>
       </c>
       <c r="C245" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4923,10 +4923,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46099</v>
+        <v>46273</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4934,10 +4934,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C247" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4945,7 +4945,7 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46226</v>
+        <v>46154</v>
       </c>
       <c r="C248" s="6">
         <v>1</v>
@@ -4956,7 +4956,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4967,7 +4967,7 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C250" s="6">
         <v>1</v>
@@ -4978,10 +4978,10 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="C251" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4989,10 +4989,10 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46237</v>
+        <v>46120</v>
       </c>
       <c r="C252" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5000,10 +5000,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46077</v>
+        <v>46237</v>
       </c>
       <c r="C253" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5011,10 +5011,10 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C254" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5022,10 +5022,10 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46216</v>
+        <v>46114</v>
       </c>
       <c r="C255" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5033,10 +5033,10 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46037</v>
+        <v>46216</v>
       </c>
       <c r="C256" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5044,7 +5044,7 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46289</v>
+        <v>46037</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5055,7 +5055,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5066,10 +5066,10 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46020</v>
+        <v>46276</v>
       </c>
       <c r="C259" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5077,10 +5077,10 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C260" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5088,10 +5088,10 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46287</v>
+        <v>46106</v>
       </c>
       <c r="C261" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5099,10 +5099,10 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46211</v>
+        <v>46287</v>
       </c>
       <c r="C262" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5110,7 +5110,7 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="C263" s="9">
         <v>1</v>
@@ -5121,7 +5121,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5132,10 +5132,10 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46210</v>
+        <v>46155</v>
       </c>
       <c r="C265" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5322,7 +5322,7 @@
         <v>46001</v>
       </c>
       <c r="C282" s="6">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
         <v>46003</v>
       </c>
       <c r="C284" s="6">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5770,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46118</v>
+        <v>46316</v>
       </c>
       <c r="C323" s="9">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46231</v>
+        <v>46118</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5792,10 +5792,10 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46076</v>
+        <v>46231</v>
       </c>
       <c r="C325" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
@@ -5803,10 +5803,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C326" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5814,7 +5814,7 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="C327" s="9">
         <v>1</v>
@@ -5825,7 +5825,7 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C328" s="6">
         <v>1</v>
@@ -5836,10 +5836,10 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C329" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
@@ -5847,10 +5847,10 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C330" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46300</v>
+        <v>46122</v>
       </c>
       <c r="C331" s="9">
         <v>1</v>
@@ -5869,10 +5869,10 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46092</v>
+        <v>46300</v>
       </c>
       <c r="C332" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -5880,10 +5880,10 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C333" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -5891,10 +5891,10 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C334" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -5902,7 +5902,7 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C335" s="9">
         <v>1</v>
@@ -5913,7 +5913,7 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C336" s="6">
         <v>1</v>
@@ -5924,7 +5924,7 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46295</v>
+        <v>46189</v>
       </c>
       <c r="C337" s="9">
         <v>1</v>
@@ -5935,7 +5935,7 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46210</v>
+        <v>46295</v>
       </c>
       <c r="C338" s="6">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C339" s="9">
         <v>1</v>
@@ -5957,7 +5957,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C340" s="6">
         <v>1</v>
@@ -5968,7 +5968,7 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C341" s="9">
         <v>1</v>
@@ -5979,10 +5979,10 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C342" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
@@ -5990,10 +5990,10 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C343" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -6001,10 +6001,10 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C344" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -6012,7 +6012,7 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C345" s="9">
         <v>3</v>
@@ -6023,10 +6023,10 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C346" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -6034,7 +6034,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6045,10 +6045,10 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46098</v>
+        <v>46233</v>
       </c>
       <c r="C348" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
@@ -6056,10 +6056,10 @@
         <v>21</v>
       </c>
       <c r="B349" s="8">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C349" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -6067,7 +6067,7 @@
         <v>21</v>
       </c>
       <c r="B350" s="5">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C350" s="6">
         <v>1</v>
@@ -6078,7 +6078,7 @@
         <v>21</v>
       </c>
       <c r="B351" s="8">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C351" s="9">
         <v>1</v>
@@ -6089,7 +6089,7 @@
         <v>21</v>
       </c>
       <c r="B352" s="5">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C352" s="6">
         <v>1</v>
@@ -6100,7 +6100,7 @@
         <v>21</v>
       </c>
       <c r="B353" s="8">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C353" s="9">
         <v>1</v>
@@ -6111,7 +6111,7 @@
         <v>21</v>
       </c>
       <c r="B354" s="5">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C354" s="6">
         <v>1</v>
@@ -6122,9 +6122,20 @@
         <v>21</v>
       </c>
       <c r="B355" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C355" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B356" s="5">
         <v>46155</v>
       </c>
-      <c r="C355" s="9">
+      <c r="C356" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6228,7 +6239,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -6568,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -6653,7 +6664,7 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -6681,13 +6692,13 @@
         <v>17</v>
       </c>
       <c r="C32">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D32">
         <v>242</v>
       </c>
       <c r="E32">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6752,10 +6763,10 @@
         <v>107</v>
       </c>
       <c r="D36">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E36">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6766,13 +6777,13 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D37">
         <v>13</v>
       </c>
       <c r="E37">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6783,7 +6794,7 @@
         <v>19</v>
       </c>
       <c r="C38">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -6843,10 +6854,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -6854,7 +6865,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -6920,7 +6931,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -6986,7 +6997,7 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -6997,7 +7008,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -7954,7 +7965,7 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C103">
         <v>15</v>
@@ -7965,7 +7976,7 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C104">
         <v>15</v>
@@ -8020,7 +8031,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C109">
         <v>6</v>
@@ -8031,7 +8042,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C110">
         <v>6</v>
@@ -8053,7 +8064,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -8064,7 +8075,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C113">
         <v>4</v>
@@ -8075,7 +8086,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C114">
         <v>4</v>
@@ -8086,7 +8097,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C115">
         <v>4</v>
@@ -8097,7 +8108,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C116">
         <v>4</v>
@@ -8108,7 +8119,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C117">
         <v>4</v>
@@ -8119,10 +8130,10 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C118">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -8152,10 +8163,10 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C121">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -8163,7 +8174,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -8174,7 +8185,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -8185,7 +8196,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -8196,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -8218,7 +8229,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -8229,7 +8240,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -8240,7 +8251,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -8251,7 +8262,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>49</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -8262,7 +8273,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8295,7 +8306,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8328,7 +8339,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -8438,7 +8449,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8636,7 +8647,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8680,7 +8691,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8691,7 +8702,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8735,7 +8746,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8790,7 +8801,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8812,7 +8823,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8823,7 +8834,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8856,7 +8867,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8878,7 +8889,7 @@
         <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -8911,7 +8922,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="C190">
         <v>16</v>
@@ -8922,7 +8933,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C191">
         <v>16</v>
@@ -8933,10 +8944,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="C192">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -9901,10 +9912,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>231</v>
+        <v>117</v>
       </c>
       <c r="C280">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -9912,7 +9923,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>117</v>
+        <v>231</v>
       </c>
       <c r="C281">
         <v>6</v>
@@ -9923,7 +9934,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>236</v>
+        <v>125</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -9934,7 +9945,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>138</v>
+        <v>236</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9956,7 +9967,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -9967,7 +9978,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -9978,7 +9989,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="C287">
         <v>5</v>
@@ -9989,10 +10000,10 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C288">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -10011,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -10022,7 +10033,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -10033,7 +10044,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -10044,7 +10055,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -10066,7 +10077,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -10077,7 +10088,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -10088,7 +10099,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -10099,7 +10110,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -10110,7 +10121,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -10121,7 +10132,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C300">
         <v>3</v>
@@ -10723,7 +10734,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10778,7 +10789,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10800,7 +10811,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10811,7 +10822,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10872,7 +10883,7 @@
         <v>272</v>
       </c>
       <c r="C3">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10993,7 +11004,7 @@
         <v>275</v>
       </c>
       <c r="C14">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -11114,7 +11125,7 @@
         <v>272</v>
       </c>
       <c r="C25">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -11147,7 +11158,7 @@
         <v>273</v>
       </c>
       <c r="C28">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -11158,7 +11169,7 @@
         <v>274</v>
       </c>
       <c r="C29">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -11213,7 +11224,7 @@
         <v>275</v>
       </c>
       <c r="C34">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -11246,7 +11257,7 @@
         <v>278</v>
       </c>
       <c r="C37">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -11257,7 +11268,7 @@
         <v>276</v>
       </c>
       <c r="C38">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="667" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6597354-80E8-4B32-8967-D2D6C866E6D9}"/>
+  <xr:revisionPtr revIDLastSave="678" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99F34AC9-9DE1-4191-83DA-714EE6BE16CA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="4" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="285">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -809,9 +809,6 @@
   </si>
   <si>
     <t>Colegio Polivalente Francisco Ramírez</t>
-  </si>
-  <si>
-    <t>Colegio Verdoyham School</t>
   </si>
   <si>
     <t>Escuela Ema Lobos Reyes</t>
@@ -2012,10 +2009,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E28">
-        <v>1.036</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2029,10 +2026,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E29">
-        <v>1.0860000000000001</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,10 +2094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E33">
-        <v>1.0429999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2148,10 +2145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E36">
-        <v>1.02</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2165,10 +2162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E37">
-        <v>0.995</v>
+        <v>0.98599999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2363,7 +2360,7 @@
         <v>46010</v>
       </c>
       <c r="C13" s="9">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -4629,7 +4626,7 @@
         <v>46009</v>
       </c>
       <c r="C219" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4758,10 +4755,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46090</v>
+        <v>46085</v>
       </c>
       <c r="C231" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4769,10 +4766,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="C232" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4780,10 +4777,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46098</v>
+        <v>46021</v>
       </c>
       <c r="C233" s="9">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4791,10 +4788,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46021</v>
+        <v>46265</v>
       </c>
       <c r="C234" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4802,10 +4799,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46265</v>
+        <v>46078</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4813,10 +4810,10 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46078</v>
+        <v>46260</v>
       </c>
       <c r="C236" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4824,7 +4821,7 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46260</v>
+        <v>46296</v>
       </c>
       <c r="C237" s="9">
         <v>1</v>
@@ -4835,10 +4832,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46296</v>
+        <v>46128</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4846,10 +4843,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46128</v>
+        <v>46083</v>
       </c>
       <c r="C239" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4857,10 +4854,10 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46083</v>
+        <v>46255</v>
       </c>
       <c r="C240" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4868,10 +4865,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46255</v>
+        <v>46076</v>
       </c>
       <c r="C241" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4879,10 +4876,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46076</v>
+        <v>46294</v>
       </c>
       <c r="C242" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4890,10 +4887,10 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46294</v>
+        <v>46262</v>
       </c>
       <c r="C243" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4901,10 +4898,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46262</v>
+        <v>46084</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4912,10 +4909,10 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C245" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -5396,10 +5393,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46084</v>
+        <v>46013</v>
       </c>
       <c r="C289" s="9">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5407,10 +5404,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C290" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5418,10 +5415,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46010</v>
+        <v>46021</v>
       </c>
       <c r="C291" s="9">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5429,10 +5426,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46021</v>
+        <v>46009</v>
       </c>
       <c r="C292" s="6">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5440,10 +5437,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46009</v>
+        <v>46083</v>
       </c>
       <c r="C293" s="9">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5451,10 +5448,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46083</v>
+        <v>46014</v>
       </c>
       <c r="C294" s="6">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5462,10 +5459,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46014</v>
+        <v>46157</v>
       </c>
       <c r="C295" s="9">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5473,10 +5470,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46157</v>
+        <v>46079</v>
       </c>
       <c r="C296" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5484,10 +5481,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46079</v>
+        <v>46167</v>
       </c>
       <c r="C297" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5495,10 +5492,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46167</v>
+        <v>46035</v>
       </c>
       <c r="C298" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,10 +5503,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46035</v>
+        <v>46085</v>
       </c>
       <c r="C299" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5517,10 +5514,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46085</v>
+        <v>46120</v>
       </c>
       <c r="C300" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5528,10 +5525,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="C301" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5539,10 +5536,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46114</v>
+        <v>46094</v>
       </c>
       <c r="C302" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5550,10 +5547,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46094</v>
+        <v>46192</v>
       </c>
       <c r="C303" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5561,10 +5558,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46192</v>
+        <v>46127</v>
       </c>
       <c r="C304" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5572,7 +5569,7 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46127</v>
+        <v>46091</v>
       </c>
       <c r="C305" s="9">
         <v>2</v>
@@ -5583,10 +5580,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46091</v>
+        <v>46090</v>
       </c>
       <c r="C306" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5594,10 +5591,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46090</v>
+        <v>46084</v>
       </c>
       <c r="C307" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5990,10 +5987,10 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="C343" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
@@ -6001,10 +5998,10 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46101</v>
+        <v>46097</v>
       </c>
       <c r="C344" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -6012,7 +6009,7 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46097</v>
+        <v>46077</v>
       </c>
       <c r="C345" s="9">
         <v>3</v>
@@ -6023,10 +6020,10 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46077</v>
+        <v>46108</v>
       </c>
       <c r="C346" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -6034,7 +6031,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46108</v>
+        <v>46233</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6045,7 +6042,7 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46233</v>
+        <v>46100</v>
       </c>
       <c r="C348" s="6">
         <v>1</v>
@@ -6624,7 +6621,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -6644,7 +6641,7 @@
         <v>117</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29">
         <v>19</v>
@@ -6709,7 +6706,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D33">
         <v>7</v>
@@ -6763,7 +6760,7 @@
         <v>107</v>
       </c>
       <c r="D36">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E36">
         <v>67</v>
@@ -6777,13 +6774,13 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37">
         <v>13</v>
       </c>
       <c r="E37">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6843,7 +6840,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -7272,7 +7269,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C40">
         <v>11</v>
@@ -8163,7 +8160,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -8174,7 +8171,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -8207,7 +8204,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -8218,7 +8215,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -8229,7 +8226,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -8240,7 +8237,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -8251,7 +8248,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C129">
         <v>2</v>
@@ -8262,7 +8259,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -8273,7 +8270,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -8284,10 +8281,10 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -8295,7 +8292,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -8306,7 +8303,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8317,7 +8314,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -8328,7 +8325,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -8339,7 +8336,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -8350,7 +8347,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -8361,7 +8358,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -8372,7 +8369,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8383,7 +8380,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -8394,7 +8391,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8405,7 +8402,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -8416,7 +8413,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -8427,7 +8424,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -8438,7 +8435,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8449,7 +8446,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -8460,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8471,7 +8468,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -8482,7 +8479,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8493,7 +8490,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -8504,7 +8501,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8515,7 +8512,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -8526,7 +8523,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8537,7 +8534,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -8548,7 +8545,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8559,7 +8556,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>234</v>
+        <v>161</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -8570,7 +8567,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -8581,7 +8578,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -8592,7 +8589,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8603,7 +8600,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -8614,7 +8611,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8625,7 +8622,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -8636,7 +8633,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8647,7 +8644,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -8658,7 +8655,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8669,7 +8666,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -8680,7 +8677,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8691,7 +8688,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -8702,7 +8699,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8713,7 +8710,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8724,7 +8721,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8735,7 +8732,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8746,7 +8743,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8757,7 +8754,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>267</v>
+        <v>68</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8768,7 +8765,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8779,7 +8776,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -8790,7 +8787,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8801,7 +8798,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -8812,7 +8809,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8823,7 +8820,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -8834,7 +8831,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8845,7 +8842,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -8856,7 +8853,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -8867,7 +8864,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -8878,7 +8875,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -8889,7 +8886,7 @@
         <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -9318,7 +9315,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C226">
         <v>3</v>
@@ -10165,7 +10162,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -10176,7 +10173,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>122</v>
+        <v>257</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -10198,7 +10195,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -10220,7 +10217,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -10242,7 +10239,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -10264,7 +10261,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -10286,7 +10283,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>166</v>
+        <v>237</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -10308,10 +10305,10 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C316">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -10319,7 +10316,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -10330,7 +10327,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10341,7 +10338,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10352,7 +10349,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>143</v>
+        <v>249</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10363,7 +10360,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10374,7 +10371,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10385,7 +10382,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10396,7 +10393,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10407,7 +10404,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>63</v>
+        <v>247</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10418,7 +10415,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10429,7 +10426,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10440,7 +10437,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10451,7 +10448,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10462,7 +10459,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>250</v>
+        <v>112</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10473,7 +10470,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>112</v>
+        <v>204</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10484,7 +10481,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>265</v>
+        <v>91</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10495,7 +10492,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>91</v>
+        <v>264</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10506,7 +10503,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>134</v>
+        <v>246</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10517,7 +10514,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>246</v>
+        <v>135</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10528,7 +10525,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -10539,7 +10536,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>252</v>
+        <v>116</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10550,7 +10547,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10561,7 +10558,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10572,7 +10569,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>264</v>
+        <v>159</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10583,7 +10580,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10594,7 +10591,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>116</v>
+        <v>245</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10605,7 +10602,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10616,7 +10613,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>167</v>
+        <v>241</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10627,7 +10624,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10638,7 +10635,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>251</v>
+        <v>49</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10649,7 +10646,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>49</v>
+        <v>259</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10660,7 +10657,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10671,7 +10668,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>260</v>
+        <v>63</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10682,22 +10679,14 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C350">
         <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B351" t="s">
-        <v>255</v>
-      </c>
-      <c r="C351">
-        <v>1</v>
-      </c>
+      <c r="A351" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10789,7 +10778,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -10811,7 +10800,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10822,7 +10811,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10858,10 +10847,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" t="s">
         <v>269</v>
-      </c>
-      <c r="C1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10869,10 +10858,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10880,10 +10869,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C3">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -10891,7 +10880,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -10902,7 +10891,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C5">
         <v>13</v>
@@ -10913,7 +10902,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -10924,7 +10913,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -10935,7 +10924,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C8">
         <v>27</v>
@@ -10946,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C9">
         <v>568</v>
@@ -10957,7 +10946,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C10">
         <v>26</v>
@@ -10968,7 +10957,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C11">
         <v>29</v>
@@ -10979,7 +10968,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C12">
         <v>27</v>
@@ -10990,7 +10979,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -11001,10 +10990,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C14">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -11012,7 +11001,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -11023,7 +11012,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C16">
         <v>15</v>
@@ -11034,7 +11023,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C17">
         <v>25</v>
@@ -11045,7 +11034,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C18">
         <v>35</v>
@@ -11056,7 +11045,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -11067,7 +11056,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -11078,7 +11067,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -11089,7 +11078,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -11100,7 +11089,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -11111,7 +11100,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C24">
         <v>39</v>
@@ -11122,7 +11111,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C25">
         <v>865</v>
@@ -11133,7 +11122,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -11144,7 +11133,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C27">
         <v>115</v>
@@ -11155,7 +11144,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C28">
         <v>145</v>
@@ -11166,7 +11155,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C29">
         <v>82</v>
@@ -11177,10 +11166,10 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -11188,7 +11177,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -11199,7 +11188,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -11210,7 +11199,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -11221,7 +11210,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C34">
         <v>703</v>
@@ -11232,7 +11221,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -11243,7 +11232,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C36">
         <v>21</v>
@@ -11254,10 +11243,10 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C37">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -11265,10 +11254,10 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C38">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -11276,10 +11265,10 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C39">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -11287,7 +11276,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -11298,7 +11287,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -11309,7 +11298,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -11320,7 +11309,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -11352,7 +11341,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -11459,7 +11448,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -11569,7 +11558,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -11679,7 +11668,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="678" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99F34AC9-9DE1-4191-83DA-714EE6BE16CA}"/>
+  <xr:revisionPtr revIDLastSave="686" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A96C5AA-BD71-410F-A775-BF6DC3BA6D7C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1422" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="285">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1771,10 +1771,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14">
-        <v>1.0649999999999999</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1839,10 +1839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18">
-        <v>1.133</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1924,10 +1924,10 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E23">
-        <v>1.105</v>
+        <v>1.1319999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2009,10 +2009,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28">
-        <v>1.0289999999999999</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2094,10 +2094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.04</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2162,10 +2162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E37">
-        <v>0.98599999999999999</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C356"/>
+  <dimension ref="A1:C357"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2250,7 +2250,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -3152,7 +3152,7 @@
         <v>46000</v>
       </c>
       <c r="C85" s="9">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3336,7 +3336,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46105</v>
+        <v>46210</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -3347,10 +3347,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C103" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3358,10 +3358,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46211</v>
+        <v>46269</v>
       </c>
       <c r="C104" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46269</v>
+        <v>46077</v>
       </c>
       <c r="C105" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3380,10 +3380,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46077</v>
+        <v>46118</v>
       </c>
       <c r="C106" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3391,10 +3391,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46118</v>
+        <v>46078</v>
       </c>
       <c r="C107" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3402,10 +3402,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46078</v>
+        <v>46272</v>
       </c>
       <c r="C108" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3413,10 +3413,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46272</v>
+        <v>46099</v>
       </c>
       <c r="C109" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3424,10 +3424,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="C110" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3435,10 +3435,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46104</v>
+        <v>46267</v>
       </c>
       <c r="C111" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3446,10 +3446,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3457,10 +3457,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46273</v>
+        <v>46248</v>
       </c>
       <c r="C113" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3468,10 +3468,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46248</v>
+        <v>46231</v>
       </c>
       <c r="C114" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3479,10 +3479,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46231</v>
+        <v>46258</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3490,10 +3490,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46258</v>
+        <v>46020</v>
       </c>
       <c r="C116" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3501,10 +3501,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46020</v>
+        <v>46076</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3512,10 +3512,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46076</v>
+        <v>46111</v>
       </c>
       <c r="C118" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3523,10 +3523,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46111</v>
+        <v>46087</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46087</v>
+        <v>46140</v>
       </c>
       <c r="C120" s="6">
         <v>2</v>
@@ -3545,10 +3545,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46140</v>
+        <v>46113</v>
       </c>
       <c r="C121" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3556,10 +3556,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="C122" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3567,10 +3567,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46119</v>
+        <v>46108</v>
       </c>
       <c r="C123" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3578,10 +3578,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46108</v>
+        <v>46274</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3589,10 +3589,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46274</v>
+        <v>46098</v>
       </c>
       <c r="C125" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3600,7 +3600,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46098</v>
+        <v>46141</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3611,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46141</v>
+        <v>46287</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3622,10 +3622,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46287</v>
+        <v>46079</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3633,10 +3633,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46079</v>
+        <v>46139</v>
       </c>
       <c r="C129" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3644,10 +3644,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3655,10 +3655,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46148</v>
+        <v>46185</v>
       </c>
       <c r="C131" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3666,7 +3666,7 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46185</v>
+        <v>46174</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3677,7 +3677,7 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46174</v>
+        <v>46286</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3688,7 +3688,7 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46286</v>
+        <v>46092</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3699,10 +3699,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46092</v>
+        <v>46021</v>
       </c>
       <c r="C135" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3710,10 +3710,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46021</v>
+        <v>46177</v>
       </c>
       <c r="C136" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3721,10 +3721,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46177</v>
+        <v>46252</v>
       </c>
       <c r="C137" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3732,10 +3732,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46252</v>
+        <v>46212</v>
       </c>
       <c r="C138" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3743,10 +3743,10 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46212</v>
+        <v>46288</v>
       </c>
       <c r="C139" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3754,10 +3754,10 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46288</v>
+        <v>46086</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3765,10 +3765,10 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46086</v>
+        <v>46227</v>
       </c>
       <c r="C141" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3776,10 +3776,10 @@
         <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46227</v>
+        <v>46289</v>
       </c>
       <c r="C142" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3787,7 +3787,7 @@
         <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46289</v>
+        <v>46188</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>14</v>
       </c>
       <c r="B144" s="5">
-        <v>46188</v>
+        <v>46147</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3809,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="B145" s="8">
-        <v>46147</v>
+        <v>46134</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3820,7 +3820,7 @@
         <v>14</v>
       </c>
       <c r="B146" s="5">
-        <v>46134</v>
+        <v>46182</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="B147" s="8">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="C147" s="9">
         <v>1</v>
@@ -3842,7 +3842,7 @@
         <v>14</v>
       </c>
       <c r="B148" s="5">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -3850,13 +3850,13 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46225</v>
+        <v>46003</v>
       </c>
       <c r="C149" s="9">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3864,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C150" s="6">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3875,10 +3875,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C151" s="9">
-        <v>113</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3886,10 +3886,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46008</v>
+        <v>46000</v>
       </c>
       <c r="C152" s="6">
-        <v>13</v>
+        <v>96</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3897,10 +3897,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C153" s="9">
-        <v>96</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3908,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46007</v>
+        <v>46001</v>
       </c>
       <c r="C154" s="6">
-        <v>38</v>
+        <v>90</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3919,10 +3919,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46001</v>
+        <v>46010</v>
       </c>
       <c r="C155" s="9">
-        <v>90</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3930,10 +3930,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C156" s="6">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3941,10 +3941,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="C157" s="9">
-        <v>83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46009</v>
+        <v>46304</v>
       </c>
       <c r="C158" s="6">
         <v>1</v>
@@ -3963,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46304</v>
+        <v>46014</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3974,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="C160" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46013</v>
+        <v>46021</v>
       </c>
       <c r="C161" s="9">
         <v>2</v>
@@ -3996,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46021</v>
+        <v>46212</v>
       </c>
       <c r="C162" s="6">
         <v>2</v>
@@ -4007,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46212</v>
+        <v>46077</v>
       </c>
       <c r="C163" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4018,10 +4018,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="C164" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4029,10 +4029,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46167</v>
+        <v>46209</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4040,10 +4040,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46209</v>
+        <v>46189</v>
       </c>
       <c r="C166" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4051,10 +4051,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46189</v>
+        <v>46315</v>
       </c>
       <c r="C167" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4062,7 +4062,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46315</v>
+        <v>46245</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4073,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46245</v>
+        <v>46170</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4084,7 +4084,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46170</v>
+        <v>46210</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4095,7 +4095,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46210</v>
+        <v>46093</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4106,10 +4106,10 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46093</v>
+        <v>46233</v>
       </c>
       <c r="C172" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4117,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46233</v>
+        <v>46090</v>
       </c>
       <c r="C173" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4128,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46090</v>
+        <v>46078</v>
       </c>
       <c r="C174" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4139,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46078</v>
+        <v>46084</v>
       </c>
       <c r="C175" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4150,10 +4150,10 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46084</v>
+        <v>46134</v>
       </c>
       <c r="C176" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4161,10 +4161,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46134</v>
+        <v>46296</v>
       </c>
       <c r="C177" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4172,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46296</v>
+        <v>46083</v>
       </c>
       <c r="C178" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4183,10 +4183,10 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46083</v>
+        <v>46316</v>
       </c>
       <c r="C179" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4194,10 +4194,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46316</v>
+        <v>46262</v>
       </c>
       <c r="C180" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4205,10 +4205,10 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46262</v>
+        <v>46022</v>
       </c>
       <c r="C181" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4216,10 +4216,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46022</v>
+        <v>46114</v>
       </c>
       <c r="C182" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4227,10 +4227,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46114</v>
+        <v>46135</v>
       </c>
       <c r="C183" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4238,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46135</v>
+        <v>46287</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46287</v>
+        <v>46127</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4260,7 +4260,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46127</v>
+        <v>46087</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4271,7 +4271,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46087</v>
+        <v>46286</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4282,7 +4282,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46286</v>
+        <v>46108</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46108</v>
+        <v>46267</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4304,7 +4304,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46267</v>
+        <v>46020</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4315,10 +4315,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46020</v>
+        <v>46168</v>
       </c>
       <c r="C191" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4326,10 +4326,10 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46168</v>
+        <v>46248</v>
       </c>
       <c r="C192" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4337,7 +4337,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4348,7 +4348,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46252</v>
+        <v>46097</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4359,7 +4359,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46097</v>
+        <v>46177</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4370,10 +4370,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46177</v>
+        <v>46161</v>
       </c>
       <c r="C196" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4381,10 +4381,10 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46161</v>
+        <v>46129</v>
       </c>
       <c r="C197" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4392,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46129</v>
+        <v>46080</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4403,7 +4403,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46080</v>
+        <v>46120</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4414,7 +4414,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46120</v>
+        <v>46101</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4425,7 +4425,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46101</v>
+        <v>46155</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4436,7 +4436,7 @@
         <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46155</v>
+        <v>46150</v>
       </c>
       <c r="C202" s="6">
         <v>1</v>
@@ -4447,7 +4447,7 @@
         <v>3</v>
       </c>
       <c r="B203" s="8">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="C203" s="9">
         <v>1</v>
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="B204" s="5">
-        <v>46141</v>
+        <v>46085</v>
       </c>
       <c r="C204" s="6">
         <v>1</v>
@@ -4469,7 +4469,7 @@
         <v>3</v>
       </c>
       <c r="B205" s="8">
-        <v>46085</v>
+        <v>46295</v>
       </c>
       <c r="C205" s="9">
         <v>1</v>
@@ -4480,7 +4480,7 @@
         <v>3</v>
       </c>
       <c r="B206" s="5">
-        <v>46295</v>
+        <v>46148</v>
       </c>
       <c r="C206" s="6">
         <v>1</v>
@@ -4491,10 +4491,10 @@
         <v>3</v>
       </c>
       <c r="B207" s="8">
-        <v>46148</v>
+        <v>46126</v>
       </c>
       <c r="C207" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4502,7 +4502,7 @@
         <v>3</v>
       </c>
       <c r="B208" s="5">
-        <v>46126</v>
+        <v>46118</v>
       </c>
       <c r="C208" s="6">
         <v>2</v>
@@ -4513,10 +4513,10 @@
         <v>3</v>
       </c>
       <c r="B209" s="8">
-        <v>46118</v>
+        <v>46258</v>
       </c>
       <c r="C209" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4524,7 +4524,7 @@
         <v>3</v>
       </c>
       <c r="B210" s="5">
-        <v>46258</v>
+        <v>46192</v>
       </c>
       <c r="C210" s="6">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         <v>3</v>
       </c>
       <c r="B211" s="8">
-        <v>46192</v>
+        <v>46079</v>
       </c>
       <c r="C211" s="9">
         <v>1</v>
@@ -4543,13 +4543,13 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46079</v>
+        <v>46003</v>
       </c>
       <c r="C212" s="6">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4557,10 +4557,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46003</v>
+        <v>46000</v>
       </c>
       <c r="C213" s="9">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4568,10 +4568,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C214" s="6">
-        <v>131</v>
+        <v>166</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4579,10 +4579,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C215" s="9">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4590,10 +4590,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46001</v>
+        <v>46014</v>
       </c>
       <c r="C216" s="6">
-        <v>173</v>
+        <v>15</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4601,10 +4601,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46014</v>
+        <v>46002</v>
       </c>
       <c r="C217" s="9">
-        <v>15</v>
+        <v>168</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4612,10 +4612,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="C218" s="6">
-        <v>168</v>
+        <v>15</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4623,10 +4623,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C219" s="9">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4634,10 +4634,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="C220" s="6">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4645,10 +4645,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="C221" s="9">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4656,10 +4656,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46007</v>
+        <v>46013</v>
       </c>
       <c r="C222" s="6">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4667,10 +4667,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46013</v>
+        <v>46258</v>
       </c>
       <c r="C223" s="9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4678,10 +4678,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46258</v>
+        <v>46080</v>
       </c>
       <c r="C224" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4689,7 +4689,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46080</v>
+        <v>46209</v>
       </c>
       <c r="C225" s="9">
         <v>2</v>
@@ -4700,10 +4700,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46209</v>
+        <v>46227</v>
       </c>
       <c r="C226" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4711,10 +4711,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46227</v>
+        <v>46192</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46192</v>
+        <v>46079</v>
       </c>
       <c r="C228" s="6">
         <v>4</v>
@@ -4733,10 +4733,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46079</v>
+        <v>46015</v>
       </c>
       <c r="C229" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4744,10 +4744,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46015</v>
+        <v>46085</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4755,10 +4755,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46085</v>
+        <v>46098</v>
       </c>
       <c r="C231" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4766,10 +4766,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46098</v>
+        <v>46021</v>
       </c>
       <c r="C232" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4777,10 +4777,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46021</v>
+        <v>46265</v>
       </c>
       <c r="C233" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4788,10 +4788,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46265</v>
+        <v>46078</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4799,10 +4799,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46078</v>
+        <v>46260</v>
       </c>
       <c r="C235" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4810,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46260</v>
+        <v>46296</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4821,10 +4821,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46296</v>
+        <v>46128</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4832,10 +4832,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46128</v>
+        <v>46083</v>
       </c>
       <c r="C238" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4843,10 +4843,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46083</v>
+        <v>46322</v>
       </c>
       <c r="C239" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5811,10 +5811,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46182</v>
+        <v>46322</v>
       </c>
       <c r="C327" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5822,7 +5822,7 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="C328" s="6">
         <v>1</v>
@@ -5833,7 +5833,7 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C329" s="9">
         <v>1</v>
@@ -5844,10 +5844,10 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C330" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
@@ -5855,10 +5855,10 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C331" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -5866,7 +5866,7 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46300</v>
+        <v>46122</v>
       </c>
       <c r="C332" s="6">
         <v>1</v>
@@ -5877,10 +5877,10 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46092</v>
+        <v>46300</v>
       </c>
       <c r="C333" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
@@ -5888,10 +5888,10 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C334" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -5899,10 +5899,10 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C335" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -5910,7 +5910,7 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C336" s="6">
         <v>1</v>
@@ -5921,7 +5921,7 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C337" s="9">
         <v>1</v>
@@ -5932,7 +5932,7 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46295</v>
+        <v>46189</v>
       </c>
       <c r="C338" s="6">
         <v>1</v>
@@ -5943,7 +5943,7 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46210</v>
+        <v>46295</v>
       </c>
       <c r="C339" s="9">
         <v>1</v>
@@ -5954,7 +5954,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C340" s="6">
         <v>1</v>
@@ -5965,7 +5965,7 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C341" s="9">
         <v>1</v>
@@ -5976,7 +5976,7 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C342" s="6">
         <v>1</v>
@@ -5987,7 +5987,7 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C343" s="9">
         <v>1</v>
@@ -5998,10 +5998,10 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C344" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
@@ -6009,7 +6009,7 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C345" s="9">
         <v>3</v>
@@ -6020,10 +6020,10 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C346" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
@@ -6031,7 +6031,7 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C347" s="9">
         <v>1</v>
@@ -6042,7 +6042,7 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46100</v>
+        <v>46233</v>
       </c>
       <c r="C348" s="6">
         <v>1</v>
@@ -6053,10 +6053,10 @@
         <v>21</v>
       </c>
       <c r="B349" s="8">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="C349" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
@@ -6064,10 +6064,10 @@
         <v>21</v>
       </c>
       <c r="B350" s="5">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C350" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -6075,7 +6075,7 @@
         <v>21</v>
       </c>
       <c r="B351" s="8">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C351" s="9">
         <v>1</v>
@@ -6086,7 +6086,7 @@
         <v>21</v>
       </c>
       <c r="B352" s="5">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C352" s="6">
         <v>1</v>
@@ -6097,7 +6097,7 @@
         <v>21</v>
       </c>
       <c r="B353" s="8">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C353" s="9">
         <v>1</v>
@@ -6108,7 +6108,7 @@
         <v>21</v>
       </c>
       <c r="B354" s="5">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C354" s="6">
         <v>1</v>
@@ -6119,7 +6119,7 @@
         <v>21</v>
       </c>
       <c r="B355" s="8">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C355" s="9">
         <v>1</v>
@@ -6130,9 +6130,20 @@
         <v>21</v>
       </c>
       <c r="B356" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C356" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B357" s="8">
         <v>46155</v>
       </c>
-      <c r="C356" s="6">
+      <c r="C357" s="9">
         <v>1</v>
       </c>
     </row>
@@ -6383,7 +6394,7 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -6457,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -6542,7 +6553,7 @@
         <v>5</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -6627,7 +6638,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6706,7 +6717,7 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D33">
         <v>7</v>
@@ -6780,7 +6791,7 @@
         <v>13</v>
       </c>
       <c r="E37">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -8281,7 +8292,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -8292,7 +8303,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -8303,7 +8314,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -8347,7 +8358,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -8369,7 +8380,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -8391,7 +8402,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>266</v>
+        <v>87</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -8435,7 +8446,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -8457,7 +8468,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -8479,7 +8490,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -8501,7 +8512,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -8523,7 +8534,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -8545,7 +8556,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -8589,7 +8600,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>149</v>
+        <v>237</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -8611,7 +8622,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -8633,7 +8644,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -8655,7 +8666,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -8677,7 +8688,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -8699,7 +8710,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -8710,7 +8721,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>234</v>
+        <v>138</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -8721,7 +8732,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -8732,7 +8743,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -8743,7 +8754,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -8754,7 +8765,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -8765,7 +8776,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -8787,7 +8798,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>176</v>
+        <v>140</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -8809,7 +8820,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -8831,7 +8842,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>160</v>
+        <v>266</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -8875,7 +8886,7 @@
         <v>15</v>
       </c>
       <c r="B186" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -8894,13 +8905,13 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B188" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C188">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -8908,10 +8919,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C189">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -8919,10 +8930,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>187</v>
+        <v>43</v>
       </c>
       <c r="C190">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -8930,7 +8941,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="C191">
         <v>16</v>
@@ -8941,7 +8952,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C192">
         <v>16</v>
@@ -8952,10 +8963,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C193">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -8963,10 +8974,10 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="C194">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -8974,10 +8985,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C195">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8985,10 +8996,10 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="C196">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -8996,7 +9007,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C197">
         <v>11</v>
@@ -9007,10 +9018,10 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C198">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -9018,7 +9029,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C199">
         <v>10</v>
@@ -9029,7 +9040,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>188</v>
+        <v>52</v>
       </c>
       <c r="C200">
         <v>10</v>
@@ -9040,10 +9051,10 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="C201">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -9051,7 +9062,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>192</v>
+        <v>72</v>
       </c>
       <c r="C202">
         <v>9</v>
@@ -9062,7 +9073,7 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="C203">
         <v>9</v>
@@ -9073,10 +9084,10 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="C204">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -9084,7 +9095,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C205">
         <v>8</v>
@@ -9095,10 +9106,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C206">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -9106,7 +9117,7 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C207">
         <v>7</v>
@@ -9117,10 +9128,10 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C208">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -9128,10 +9139,10 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C209">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -9139,7 +9150,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C210">
         <v>5</v>
@@ -9150,10 +9161,10 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C211">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -9161,7 +9172,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -9172,7 +9183,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -9183,7 +9194,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="C214">
         <v>4</v>
@@ -9194,7 +9205,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="C215">
         <v>4</v>
@@ -9205,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C216">
         <v>4</v>
@@ -9216,10 +9227,10 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C217">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -9227,7 +9238,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -9238,7 +9249,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -9249,7 +9260,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -9260,7 +9271,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -9271,7 +9282,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -9282,7 +9293,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="C223">
         <v>3</v>
@@ -9293,7 +9304,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -9304,7 +9315,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -9315,7 +9326,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>284</v>
+        <v>74</v>
       </c>
       <c r="C226">
         <v>3</v>
@@ -9326,10 +9337,10 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>199</v>
+        <v>284</v>
       </c>
       <c r="C227">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -9337,7 +9348,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>64</v>
+        <v>199</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -9348,7 +9359,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>195</v>
+        <v>64</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9359,7 +9370,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -9370,7 +9381,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C231">
         <v>2</v>
@@ -9381,7 +9392,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -9392,7 +9403,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="C233">
         <v>2</v>
@@ -9403,7 +9414,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C234">
         <v>2</v>
@@ -9414,10 +9425,10 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="C235">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -9425,7 +9436,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -9436,7 +9447,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -9447,7 +9458,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -9458,7 +9469,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -9469,7 +9480,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -9480,7 +9491,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>230</v>
+        <v>118</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -9491,7 +9502,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -9502,7 +9513,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -9513,7 +9524,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>207</v>
+        <v>112</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -9524,7 +9535,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -9535,7 +9546,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -9546,7 +9557,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -9557,7 +9568,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -9568,7 +9579,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -9579,7 +9590,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -9590,7 +9601,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -9601,7 +9612,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -9612,7 +9623,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -9623,7 +9634,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -9634,7 +9645,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -9645,7 +9656,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -9656,7 +9667,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -9667,7 +9678,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -9678,7 +9689,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -9689,7 +9700,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -9700,7 +9711,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -9711,7 +9722,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -9722,7 +9733,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -9733,7 +9744,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -9744,7 +9755,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -9755,7 +9766,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -9766,7 +9777,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>226</v>
+        <v>116</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -9777,7 +9788,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -9788,7 +9799,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -9799,7 +9810,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -9810,7 +9821,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -9821,7 +9832,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -9832,7 +9843,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -9843,7 +9854,7 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -9851,13 +9862,13 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="C275">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -9865,10 +9876,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C276">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -9876,10 +9887,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="C277">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -9887,10 +9898,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="C278">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -9898,10 +9909,10 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="C279">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -9909,10 +9920,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="C280">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -9920,10 +9931,10 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>231</v>
+        <v>117</v>
       </c>
       <c r="C281">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -9931,10 +9942,10 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -9942,7 +9953,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>236</v>
+        <v>125</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -9953,7 +9964,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -9964,7 +9975,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>138</v>
+        <v>233</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -9975,7 +9986,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -9986,7 +9997,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C287">
         <v>5</v>
@@ -9997,10 +10008,10 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C288">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -10008,7 +10019,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>133</v>
+        <v>235</v>
       </c>
       <c r="C289">
         <v>4</v>
@@ -10019,10 +10030,10 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C290">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -10030,10 +10041,10 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="C291">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -10052,7 +10063,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -10063,7 +10074,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -10096,7 +10107,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -10118,7 +10129,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -10129,7 +10140,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C300">
         <v>3</v>
@@ -10140,7 +10151,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="C301">
         <v>3</v>
@@ -10151,10 +10162,10 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="C302">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -10162,7 +10173,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>190</v>
+        <v>54</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -10173,7 +10184,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>257</v>
+        <v>190</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -10184,7 +10195,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>84</v>
+        <v>257</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -10195,7 +10206,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -10206,7 +10217,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>243</v>
+        <v>166</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -10217,7 +10228,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -10228,7 +10239,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>244</v>
+        <v>122</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -10239,7 +10250,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -10250,7 +10261,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>70</v>
+        <v>242</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -10261,7 +10272,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -10272,7 +10283,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -10283,7 +10294,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -10294,7 +10305,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -10305,10 +10316,10 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>253</v>
+        <v>191</v>
       </c>
       <c r="C316">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -10316,7 +10327,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -10327,7 +10338,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -10338,7 +10349,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>143</v>
+        <v>265</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -10349,7 +10360,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -10360,7 +10371,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -10371,7 +10382,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -10382,7 +10393,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -10393,7 +10404,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -10404,7 +10415,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -10415,7 +10426,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -10426,7 +10437,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>177</v>
+        <v>261</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -10437,7 +10448,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -10448,7 +10459,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -10459,7 +10470,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>112</v>
+        <v>250</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -10470,7 +10481,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -10481,7 +10492,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -10492,7 +10503,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -10503,7 +10514,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -10514,7 +10525,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -10525,7 +10536,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -10536,7 +10547,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>116</v>
+        <v>252</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -10547,7 +10558,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>248</v>
+        <v>116</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -10558,7 +10569,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -10569,7 +10580,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>159</v>
+        <v>263</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -10580,7 +10591,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -10591,7 +10602,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>245</v>
+        <v>164</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -10602,7 +10613,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -10613,7 +10624,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>241</v>
+        <v>167</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -10624,7 +10635,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -10635,7 +10646,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>49</v>
+        <v>251</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -10646,7 +10657,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>259</v>
+        <v>49</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -10657,7 +10668,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -10668,7 +10679,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>63</v>
+        <v>260</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -10679,14 +10690,22 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
+        <v>63</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B351" t="s">
         <v>254</v>
       </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" s="12"/>
+      <c r="C351">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10745,7 +10764,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10756,7 +10775,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -10767,7 +10786,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -10800,7 +10819,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10811,7 +10830,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -10938,7 +10957,7 @@
         <v>271</v>
       </c>
       <c r="C9">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10993,7 +11012,7 @@
         <v>274</v>
       </c>
       <c r="C14">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -11114,7 +11133,7 @@
         <v>271</v>
       </c>
       <c r="C25">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -11213,7 +11232,7 @@
         <v>274</v>
       </c>
       <c r="C34">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -11290,7 +11309,7 @@
         <v>276</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="686" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A96C5AA-BD71-410F-A775-BF6DC3BA6D7C}"/>
+  <xr:revisionPtr revIDLastSave="696" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26D9016F-8702-4297-BB72-5A8B971AF671}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="820" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="285">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1737,10 +1737,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12">
-        <v>1.452</v>
+        <v>1.419</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1822,10 +1822,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17">
-        <v>1.0589999999999999</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1890,10 +1890,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21">
-        <v>1.0229999999999999</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2077,10 +2077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E32">
-        <v>1.0780000000000001</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:C357"/>
+  <dimension ref="A1:C358"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3006,7 +3006,7 @@
         <v>16</v>
       </c>
       <c r="B72" s="5">
-        <v>46300</v>
+        <v>46323</v>
       </c>
       <c r="C72" s="6">
         <v>1</v>
@@ -3017,7 +3017,7 @@
         <v>16</v>
       </c>
       <c r="B73" s="8">
-        <v>46156</v>
+        <v>46300</v>
       </c>
       <c r="C73" s="9">
         <v>1</v>
@@ -3028,7 +3028,7 @@
         <v>16</v>
       </c>
       <c r="B74" s="5">
-        <v>46245</v>
+        <v>46156</v>
       </c>
       <c r="C74" s="6">
         <v>1</v>
@@ -3039,7 +3039,7 @@
         <v>16</v>
       </c>
       <c r="B75" s="8">
-        <v>46213</v>
+        <v>46245</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -3050,7 +3050,7 @@
         <v>16</v>
       </c>
       <c r="B76" s="5">
-        <v>46092</v>
+        <v>46213</v>
       </c>
       <c r="C76" s="6">
         <v>1</v>
@@ -3061,7 +3061,7 @@
         <v>16</v>
       </c>
       <c r="B77" s="8">
-        <v>46226</v>
+        <v>46092</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -3072,7 +3072,7 @@
         <v>16</v>
       </c>
       <c r="B78" s="5">
-        <v>46238</v>
+        <v>46226</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
@@ -3083,7 +3083,7 @@
         <v>16</v>
       </c>
       <c r="B79" s="8">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="C79" s="9">
         <v>1</v>
@@ -3094,7 +3094,7 @@
         <v>16</v>
       </c>
       <c r="B80" s="5">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C80" s="6">
         <v>1</v>
@@ -3105,7 +3105,7 @@
         <v>16</v>
       </c>
       <c r="B81" s="8">
-        <v>46261</v>
+        <v>46101</v>
       </c>
       <c r="C81" s="9">
         <v>1</v>
@@ -3116,7 +3116,7 @@
         <v>16</v>
       </c>
       <c r="B82" s="5">
-        <v>46286</v>
+        <v>46261</v>
       </c>
       <c r="C82" s="6">
         <v>1</v>
@@ -3124,13 +3124,13 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B83" s="8">
-        <v>46007</v>
+        <v>46286</v>
       </c>
       <c r="C83" s="9">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3138,10 +3138,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C84" s="6">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3149,10 +3149,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C85" s="9">
-        <v>76</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3160,10 +3160,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C86" s="6">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3171,10 +3171,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C87" s="9">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3182,10 +3182,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C88" s="6">
-        <v>77</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3193,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C89" s="9">
-        <v>16</v>
+        <v>76</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3204,10 +3204,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C90" s="6">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3215,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C91" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3226,10 +3226,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C92" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3237,10 +3237,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C93" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3248,10 +3248,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C94" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3259,10 +3259,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C95" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3270,10 +3270,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C96" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3281,10 +3281,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C97" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3292,10 +3292,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="C98" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3303,7 +3303,7 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46091</v>
+        <v>46209</v>
       </c>
       <c r="C99" s="9">
         <v>2</v>
@@ -3314,10 +3314,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46296</v>
+        <v>46091</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3325,10 +3325,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C101" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3336,10 +3336,10 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46210</v>
+        <v>46083</v>
       </c>
       <c r="C102" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3347,10 +3347,10 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="C103" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3358,10 +3358,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46269</v>
+        <v>46211</v>
       </c>
       <c r="C104" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46077</v>
+        <v>46269</v>
       </c>
       <c r="C105" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3380,10 +3380,10 @@
         <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3391,10 +3391,10 @@
         <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C107" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3402,10 +3402,10 @@
         <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46272</v>
+        <v>46078</v>
       </c>
       <c r="C108" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3413,10 +3413,10 @@
         <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46099</v>
+        <v>46272</v>
       </c>
       <c r="C109" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3424,10 +3424,10 @@
         <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C110" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3435,10 +3435,10 @@
         <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46267</v>
+        <v>46104</v>
       </c>
       <c r="C111" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3446,10 +3446,10 @@
         <v>14</v>
       </c>
       <c r="B112" s="5">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="C112" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3457,10 +3457,10 @@
         <v>14</v>
       </c>
       <c r="B113" s="8">
-        <v>46248</v>
+        <v>46273</v>
       </c>
       <c r="C113" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3468,10 +3468,10 @@
         <v>14</v>
       </c>
       <c r="B114" s="5">
-        <v>46231</v>
+        <v>46248</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3479,10 +3479,10 @@
         <v>14</v>
       </c>
       <c r="B115" s="8">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="C115" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3490,10 +3490,10 @@
         <v>14</v>
       </c>
       <c r="B116" s="5">
-        <v>46020</v>
+        <v>46258</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3501,10 +3501,10 @@
         <v>14</v>
       </c>
       <c r="B117" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C117" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3512,10 +3512,10 @@
         <v>14</v>
       </c>
       <c r="B118" s="5">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3523,10 +3523,10 @@
         <v>14</v>
       </c>
       <c r="B119" s="8">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C119" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3534,7 +3534,7 @@
         <v>14</v>
       </c>
       <c r="B120" s="5">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C120" s="6">
         <v>2</v>
@@ -3545,10 +3545,10 @@
         <v>14</v>
       </c>
       <c r="B121" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3556,10 +3556,10 @@
         <v>14</v>
       </c>
       <c r="B122" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C122" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3567,10 +3567,10 @@
         <v>14</v>
       </c>
       <c r="B123" s="8">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3578,10 +3578,10 @@
         <v>14</v>
       </c>
       <c r="B124" s="5">
-        <v>46274</v>
+        <v>46108</v>
       </c>
       <c r="C124" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3589,10 +3589,10 @@
         <v>14</v>
       </c>
       <c r="B125" s="8">
-        <v>46098</v>
+        <v>46274</v>
       </c>
       <c r="C125" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3600,7 +3600,7 @@
         <v>14</v>
       </c>
       <c r="B126" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3611,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="B127" s="8">
-        <v>46287</v>
+        <v>46141</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3622,10 +3622,10 @@
         <v>14</v>
       </c>
       <c r="B128" s="5">
-        <v>46079</v>
+        <v>46287</v>
       </c>
       <c r="C128" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3633,10 +3633,10 @@
         <v>14</v>
       </c>
       <c r="B129" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C129" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3644,10 +3644,10 @@
         <v>14</v>
       </c>
       <c r="B130" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C130" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3655,10 +3655,10 @@
         <v>14</v>
       </c>
       <c r="B131" s="8">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C131" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3666,7 +3666,7 @@
         <v>14</v>
       </c>
       <c r="B132" s="5">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3677,7 +3677,7 @@
         <v>14</v>
       </c>
       <c r="B133" s="8">
-        <v>46286</v>
+        <v>46174</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3688,7 +3688,7 @@
         <v>14</v>
       </c>
       <c r="B134" s="5">
-        <v>46092</v>
+        <v>46286</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3699,10 +3699,10 @@
         <v>14</v>
       </c>
       <c r="B135" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C135" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3710,10 +3710,10 @@
         <v>14</v>
       </c>
       <c r="B136" s="5">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C136" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3721,10 +3721,10 @@
         <v>14</v>
       </c>
       <c r="B137" s="8">
-        <v>46252</v>
+        <v>46177</v>
       </c>
       <c r="C137" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3732,10 +3732,10 @@
         <v>14</v>
       </c>
       <c r="B138" s="5">
-        <v>46212</v>
+        <v>46252</v>
       </c>
       <c r="C138" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3743,10 +3743,10 @@
         <v>14</v>
       </c>
       <c r="B139" s="8">
-        <v>46288</v>
+        <v>46212</v>
       </c>
       <c r="C139" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3754,10 +3754,10 @@
         <v>14</v>
       </c>
       <c r="B140" s="5">
-        <v>46086</v>
+        <v>46288</v>
       </c>
       <c r="C140" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3765,10 +3765,10 @@
         <v>14</v>
       </c>
       <c r="B141" s="8">
-        <v>46227</v>
+        <v>46086</v>
       </c>
       <c r="C141" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3776,10 +3776,10 @@
         <v>14</v>
       </c>
       <c r="B142" s="5">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="C142" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3787,7 +3787,7 @@
         <v>14</v>
       </c>
       <c r="B143" s="8">
-        <v>46188</v>
+        <v>46289</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>14</v>
       </c>
       <c r="B144" s="5">
-        <v>46147</v>
+        <v>46188</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3809,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="B145" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3820,7 +3820,7 @@
         <v>14</v>
       </c>
       <c r="B146" s="5">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3831,7 +3831,7 @@
         <v>14</v>
       </c>
       <c r="B147" s="8">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="C147" s="9">
         <v>1</v>
@@ -3842,7 +3842,7 @@
         <v>14</v>
       </c>
       <c r="B148" s="5">
-        <v>46225</v>
+        <v>46190</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -3850,13 +3850,13 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B149" s="8">
-        <v>46003</v>
+        <v>46225</v>
       </c>
       <c r="C149" s="9">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3864,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C150" s="6">
-        <v>113</v>
+        <v>94</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3875,10 +3875,10 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C151" s="9">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3886,10 +3886,10 @@
         <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C152" s="6">
-        <v>96</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3897,10 +3897,10 @@
         <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C153" s="9">
-        <v>38</v>
+        <v>96</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3908,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C154" s="6">
-        <v>90</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3919,10 +3919,10 @@
         <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C155" s="9">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3930,10 +3930,10 @@
         <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C156" s="6">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3941,10 +3941,10 @@
         <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3952,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46304</v>
+        <v>46009</v>
       </c>
       <c r="C158" s="6">
         <v>1</v>
@@ -3963,10 +3963,10 @@
         <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46014</v>
+        <v>46304</v>
       </c>
       <c r="C159" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3974,10 +3974,10 @@
         <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C160" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3985,7 +3985,7 @@
         <v>3</v>
       </c>
       <c r="B161" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C161" s="9">
         <v>2</v>
@@ -3996,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="B162" s="5">
-        <v>46212</v>
+        <v>46021</v>
       </c>
       <c r="C162" s="6">
         <v>2</v>
@@ -4007,10 +4007,10 @@
         <v>3</v>
       </c>
       <c r="B163" s="8">
-        <v>46077</v>
+        <v>46212</v>
       </c>
       <c r="C163" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4018,10 +4018,10 @@
         <v>3</v>
       </c>
       <c r="B164" s="5">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4029,10 +4029,10 @@
         <v>3</v>
       </c>
       <c r="B165" s="8">
-        <v>46209</v>
+        <v>46167</v>
       </c>
       <c r="C165" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4040,10 +4040,10 @@
         <v>3</v>
       </c>
       <c r="B166" s="5">
-        <v>46189</v>
+        <v>46209</v>
       </c>
       <c r="C166" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4051,10 +4051,10 @@
         <v>3</v>
       </c>
       <c r="B167" s="8">
-        <v>46315</v>
+        <v>46189</v>
       </c>
       <c r="C167" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4062,7 +4062,7 @@
         <v>3</v>
       </c>
       <c r="B168" s="5">
-        <v>46245</v>
+        <v>46315</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4073,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="B169" s="8">
-        <v>46170</v>
+        <v>46245</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4084,7 +4084,7 @@
         <v>3</v>
       </c>
       <c r="B170" s="5">
-        <v>46210</v>
+        <v>46170</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4095,7 +4095,7 @@
         <v>3</v>
       </c>
       <c r="B171" s="8">
-        <v>46093</v>
+        <v>46210</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4106,10 +4106,10 @@
         <v>3</v>
       </c>
       <c r="B172" s="5">
-        <v>46233</v>
+        <v>46093</v>
       </c>
       <c r="C172" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4117,10 +4117,10 @@
         <v>3</v>
       </c>
       <c r="B173" s="8">
-        <v>46090</v>
+        <v>46233</v>
       </c>
       <c r="C173" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4128,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="B174" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C174" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4139,10 +4139,10 @@
         <v>3</v>
       </c>
       <c r="B175" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C175" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4150,10 +4150,10 @@
         <v>3</v>
       </c>
       <c r="B176" s="5">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C176" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4161,10 +4161,10 @@
         <v>3</v>
       </c>
       <c r="B177" s="8">
-        <v>46296</v>
+        <v>46134</v>
       </c>
       <c r="C177" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4172,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="B178" s="5">
-        <v>46083</v>
+        <v>46296</v>
       </c>
       <c r="C178" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4183,10 +4183,10 @@
         <v>3</v>
       </c>
       <c r="B179" s="8">
-        <v>46316</v>
+        <v>46083</v>
       </c>
       <c r="C179" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4194,10 +4194,10 @@
         <v>3</v>
       </c>
       <c r="B180" s="5">
-        <v>46262</v>
+        <v>46316</v>
       </c>
       <c r="C180" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4205,10 +4205,10 @@
         <v>3</v>
       </c>
       <c r="B181" s="8">
-        <v>46022</v>
+        <v>46262</v>
       </c>
       <c r="C181" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4216,10 +4216,10 @@
         <v>3</v>
       </c>
       <c r="B182" s="5">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C182" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4227,10 +4227,10 @@
         <v>3</v>
       </c>
       <c r="B183" s="8">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4238,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="B184" s="5">
-        <v>46287</v>
+        <v>46135</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         <v>3</v>
       </c>
       <c r="B185" s="8">
-        <v>46127</v>
+        <v>46287</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4260,7 +4260,7 @@
         <v>3</v>
       </c>
       <c r="B186" s="5">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4271,7 +4271,7 @@
         <v>3</v>
       </c>
       <c r="B187" s="8">
-        <v>46286</v>
+        <v>46087</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4282,7 +4282,7 @@
         <v>3</v>
       </c>
       <c r="B188" s="5">
-        <v>46108</v>
+        <v>46286</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="B189" s="8">
-        <v>46267</v>
+        <v>46108</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4304,7 +4304,7 @@
         <v>3</v>
       </c>
       <c r="B190" s="5">
-        <v>46020</v>
+        <v>46267</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4315,10 +4315,10 @@
         <v>3</v>
       </c>
       <c r="B191" s="8">
-        <v>46168</v>
+        <v>46020</v>
       </c>
       <c r="C191" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4326,10 +4326,10 @@
         <v>3</v>
       </c>
       <c r="B192" s="5">
-        <v>46248</v>
+        <v>46168</v>
       </c>
       <c r="C192" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4337,7 +4337,7 @@
         <v>3</v>
       </c>
       <c r="B193" s="8">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4348,7 +4348,7 @@
         <v>3</v>
       </c>
       <c r="B194" s="5">
-        <v>46097</v>
+        <v>46252</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4359,7 +4359,7 @@
         <v>3</v>
       </c>
       <c r="B195" s="8">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4370,10 +4370,10 @@
         <v>3</v>
       </c>
       <c r="B196" s="5">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C196" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4381,10 +4381,10 @@
         <v>3</v>
       </c>
       <c r="B197" s="8">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C197" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4392,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="B198" s="5">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4403,7 +4403,7 @@
         <v>3</v>
       </c>
       <c r="B199" s="8">
-        <v>46120</v>
+        <v>46080</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4414,7 +4414,7 @@
         <v>3</v>
       </c>
       <c r="B200" s="5">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="C200" s="6">
         <v>1</v>
@@ -4425,7 +4425,7 @@
         <v>3</v>
       </c>
       <c r="B201" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C201" s="9">
         <v>1</v>
@@ -4436,7 +4436,7 @@
         <v>3</v>
       </c>
       <c r="B202" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C202" s="6">
         <v>1</v>
@@ -4447,7 +4447,7 @@
         <v>3</v>
       </c>
       <c r="B203" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C203" s="9">
         <v>1</v>
@@ -4458,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="B204" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C204" s="6">
         <v>1</v>
@@ -4469,7 +4469,7 @@
         <v>3</v>
       </c>
       <c r="B205" s="8">
-        <v>46295</v>
+        <v>46085</v>
       </c>
       <c r="C205" s="9">
         <v>1</v>
@@ -4480,7 +4480,7 @@
         <v>3</v>
       </c>
       <c r="B206" s="5">
-        <v>46148</v>
+        <v>46295</v>
       </c>
       <c r="C206" s="6">
         <v>1</v>
@@ -4491,10 +4491,10 @@
         <v>3</v>
       </c>
       <c r="B207" s="8">
-        <v>46126</v>
+        <v>46148</v>
       </c>
       <c r="C207" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4502,7 +4502,7 @@
         <v>3</v>
       </c>
       <c r="B208" s="5">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="C208" s="6">
         <v>2</v>
@@ -4513,10 +4513,10 @@
         <v>3</v>
       </c>
       <c r="B209" s="8">
-        <v>46258</v>
+        <v>46118</v>
       </c>
       <c r="C209" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4524,7 +4524,7 @@
         <v>3</v>
       </c>
       <c r="B210" s="5">
-        <v>46192</v>
+        <v>46258</v>
       </c>
       <c r="C210" s="6">
         <v>1</v>
@@ -4535,7 +4535,7 @@
         <v>3</v>
       </c>
       <c r="B211" s="8">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C211" s="9">
         <v>1</v>
@@ -4543,13 +4543,13 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B212" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C212" s="6">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4557,10 +4557,10 @@
         <v>15</v>
       </c>
       <c r="B213" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C213" s="9">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4568,10 +4568,10 @@
         <v>15</v>
       </c>
       <c r="B214" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C214" s="6">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4579,10 +4579,10 @@
         <v>15</v>
       </c>
       <c r="B215" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C215" s="9">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4590,10 +4590,10 @@
         <v>15</v>
       </c>
       <c r="B216" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C216" s="6">
-        <v>15</v>
+        <v>173</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4601,10 +4601,10 @@
         <v>15</v>
       </c>
       <c r="B217" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C217" s="9">
-        <v>168</v>
+        <v>15</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4612,10 +4612,10 @@
         <v>15</v>
       </c>
       <c r="B218" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C218" s="6">
-        <v>15</v>
+        <v>168</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4623,10 +4623,10 @@
         <v>15</v>
       </c>
       <c r="B219" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C219" s="9">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4634,10 +4634,10 @@
         <v>15</v>
       </c>
       <c r="B220" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C220" s="6">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4645,10 +4645,10 @@
         <v>15</v>
       </c>
       <c r="B221" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C221" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4656,10 +4656,10 @@
         <v>15</v>
       </c>
       <c r="B222" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C222" s="6">
-        <v>11</v>
+        <v>43</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4667,10 +4667,10 @@
         <v>15</v>
       </c>
       <c r="B223" s="8">
-        <v>46258</v>
+        <v>46013</v>
       </c>
       <c r="C223" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4678,10 +4678,10 @@
         <v>15</v>
       </c>
       <c r="B224" s="5">
-        <v>46080</v>
+        <v>46258</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4689,7 +4689,7 @@
         <v>15</v>
       </c>
       <c r="B225" s="8">
-        <v>46209</v>
+        <v>46080</v>
       </c>
       <c r="C225" s="9">
         <v>2</v>
@@ -4700,10 +4700,10 @@
         <v>15</v>
       </c>
       <c r="B226" s="5">
-        <v>46227</v>
+        <v>46209</v>
       </c>
       <c r="C226" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4711,10 +4711,10 @@
         <v>15</v>
       </c>
       <c r="B227" s="8">
-        <v>46192</v>
+        <v>46227</v>
       </c>
       <c r="C227" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>15</v>
       </c>
       <c r="B228" s="5">
-        <v>46079</v>
+        <v>46192</v>
       </c>
       <c r="C228" s="6">
         <v>4</v>
@@ -4733,10 +4733,10 @@
         <v>15</v>
       </c>
       <c r="B229" s="8">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C229" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4744,10 +4744,10 @@
         <v>15</v>
       </c>
       <c r="B230" s="5">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C230" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4755,10 +4755,10 @@
         <v>15</v>
       </c>
       <c r="B231" s="8">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C231" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4766,10 +4766,10 @@
         <v>15</v>
       </c>
       <c r="B232" s="5">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C232" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4777,10 +4777,10 @@
         <v>15</v>
       </c>
       <c r="B233" s="8">
-        <v>46265</v>
+        <v>46021</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4788,10 +4788,10 @@
         <v>15</v>
       </c>
       <c r="B234" s="5">
-        <v>46078</v>
+        <v>46265</v>
       </c>
       <c r="C234" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4799,10 +4799,10 @@
         <v>15</v>
       </c>
       <c r="B235" s="8">
-        <v>46260</v>
+        <v>46078</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4810,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="B236" s="5">
-        <v>46296</v>
+        <v>46260</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4821,10 +4821,10 @@
         <v>15</v>
       </c>
       <c r="B237" s="8">
-        <v>46128</v>
+        <v>46296</v>
       </c>
       <c r="C237" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4832,10 +4832,10 @@
         <v>15</v>
       </c>
       <c r="B238" s="5">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C238" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4843,10 +4843,10 @@
         <v>15</v>
       </c>
       <c r="B239" s="8">
-        <v>46322</v>
+        <v>46083</v>
       </c>
       <c r="C239" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4854,7 +4854,7 @@
         <v>15</v>
       </c>
       <c r="B240" s="5">
-        <v>46255</v>
+        <v>46322</v>
       </c>
       <c r="C240" s="6">
         <v>2</v>
@@ -4865,10 +4865,10 @@
         <v>15</v>
       </c>
       <c r="B241" s="8">
-        <v>46076</v>
+        <v>46255</v>
       </c>
       <c r="C241" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4876,10 +4876,10 @@
         <v>15</v>
       </c>
       <c r="B242" s="5">
-        <v>46294</v>
+        <v>46076</v>
       </c>
       <c r="C242" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -4887,10 +4887,10 @@
         <v>15</v>
       </c>
       <c r="B243" s="8">
-        <v>46262</v>
+        <v>46294</v>
       </c>
       <c r="C243" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4898,10 +4898,10 @@
         <v>15</v>
       </c>
       <c r="B244" s="5">
-        <v>46084</v>
+        <v>46262</v>
       </c>
       <c r="C244" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4909,10 +4909,10 @@
         <v>15</v>
       </c>
       <c r="B245" s="8">
-        <v>46090</v>
+        <v>46084</v>
       </c>
       <c r="C245" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4920,10 +4920,10 @@
         <v>15</v>
       </c>
       <c r="B246" s="5">
-        <v>46273</v>
+        <v>46090</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4931,10 +4931,10 @@
         <v>15</v>
       </c>
       <c r="B247" s="8">
-        <v>46099</v>
+        <v>46273</v>
       </c>
       <c r="C247" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4942,10 +4942,10 @@
         <v>15</v>
       </c>
       <c r="B248" s="5">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4953,7 +4953,7 @@
         <v>15</v>
       </c>
       <c r="B249" s="8">
-        <v>46226</v>
+        <v>46154</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -4964,7 +4964,7 @@
         <v>15</v>
       </c>
       <c r="B250" s="5">
-        <v>46092</v>
+        <v>46226</v>
       </c>
       <c r="C250" s="6">
         <v>1</v>
@@ -4975,7 +4975,7 @@
         <v>15</v>
       </c>
       <c r="B251" s="8">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -4986,10 +4986,10 @@
         <v>15</v>
       </c>
       <c r="B252" s="5">
-        <v>46120</v>
+        <v>46022</v>
       </c>
       <c r="C252" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -4997,10 +4997,10 @@
         <v>15</v>
       </c>
       <c r="B253" s="8">
-        <v>46237</v>
+        <v>46120</v>
       </c>
       <c r="C253" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5008,10 +5008,10 @@
         <v>15</v>
       </c>
       <c r="B254" s="5">
-        <v>46077</v>
+        <v>46237</v>
       </c>
       <c r="C254" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5019,10 +5019,10 @@
         <v>15</v>
       </c>
       <c r="B255" s="8">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C255" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5030,10 +5030,10 @@
         <v>15</v>
       </c>
       <c r="B256" s="5">
-        <v>46216</v>
+        <v>46114</v>
       </c>
       <c r="C256" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5041,10 +5041,10 @@
         <v>15</v>
       </c>
       <c r="B257" s="8">
-        <v>46037</v>
+        <v>46216</v>
       </c>
       <c r="C257" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -5052,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="B258" s="5">
-        <v>46289</v>
+        <v>46037</v>
       </c>
       <c r="C258" s="6">
         <v>1</v>
@@ -5063,7 +5063,7 @@
         <v>15</v>
       </c>
       <c r="B259" s="8">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="C259" s="9">
         <v>1</v>
@@ -5074,10 +5074,10 @@
         <v>15</v>
       </c>
       <c r="B260" s="5">
-        <v>46020</v>
+        <v>46276</v>
       </c>
       <c r="C260" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5085,10 +5085,10 @@
         <v>15</v>
       </c>
       <c r="B261" s="8">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C261" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5096,10 +5096,10 @@
         <v>15</v>
       </c>
       <c r="B262" s="5">
-        <v>46287</v>
+        <v>46106</v>
       </c>
       <c r="C262" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -5107,10 +5107,10 @@
         <v>15</v>
       </c>
       <c r="B263" s="8">
-        <v>46211</v>
+        <v>46287</v>
       </c>
       <c r="C263" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5118,7 +5118,7 @@
         <v>15</v>
       </c>
       <c r="B264" s="5">
-        <v>46239</v>
+        <v>46211</v>
       </c>
       <c r="C264" s="6">
         <v>1</v>
@@ -5129,7 +5129,7 @@
         <v>15</v>
       </c>
       <c r="B265" s="8">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="C265" s="9">
         <v>1</v>
@@ -5140,7 +5140,7 @@
         <v>15</v>
       </c>
       <c r="B266" s="5">
-        <v>46132</v>
+        <v>46155</v>
       </c>
       <c r="C266" s="6">
         <v>1</v>
@@ -5151,7 +5151,7 @@
         <v>15</v>
       </c>
       <c r="B267" s="8">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C267" s="9">
         <v>1</v>
@@ -5162,7 +5162,7 @@
         <v>15</v>
       </c>
       <c r="B268" s="5">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C268" s="6">
         <v>1</v>
@@ -5173,7 +5173,7 @@
         <v>15</v>
       </c>
       <c r="B269" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C269" s="9">
         <v>1</v>
@@ -5184,7 +5184,7 @@
         <v>15</v>
       </c>
       <c r="B270" s="5">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C270" s="6">
         <v>1</v>
@@ -5195,7 +5195,7 @@
         <v>15</v>
       </c>
       <c r="B271" s="8">
-        <v>46181</v>
+        <v>46035</v>
       </c>
       <c r="C271" s="9">
         <v>1</v>
@@ -5206,7 +5206,7 @@
         <v>15</v>
       </c>
       <c r="B272" s="5">
-        <v>46290</v>
+        <v>46181</v>
       </c>
       <c r="C272" s="6">
         <v>1</v>
@@ -5217,7 +5217,7 @@
         <v>15</v>
       </c>
       <c r="B273" s="8">
-        <v>46087</v>
+        <v>46290</v>
       </c>
       <c r="C273" s="9">
         <v>1</v>
@@ -5228,10 +5228,10 @@
         <v>15</v>
       </c>
       <c r="B274" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C274" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -5239,10 +5239,10 @@
         <v>15</v>
       </c>
       <c r="B275" s="8">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C275" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -5250,7 +5250,7 @@
         <v>15</v>
       </c>
       <c r="B276" s="5">
-        <v>46204</v>
+        <v>46031</v>
       </c>
       <c r="C276" s="6">
         <v>1</v>
@@ -5261,7 +5261,7 @@
         <v>15</v>
       </c>
       <c r="B277" s="8">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="C277" s="9">
         <v>1</v>
@@ -5272,7 +5272,7 @@
         <v>15</v>
       </c>
       <c r="B278" s="5">
-        <v>46286</v>
+        <v>46176</v>
       </c>
       <c r="C278" s="6">
         <v>1</v>
@@ -5283,7 +5283,7 @@
         <v>15</v>
       </c>
       <c r="B279" s="8">
-        <v>46101</v>
+        <v>46286</v>
       </c>
       <c r="C279" s="9">
         <v>1</v>
@@ -5294,7 +5294,7 @@
         <v>15</v>
       </c>
       <c r="B280" s="5">
-        <v>46213</v>
+        <v>46101</v>
       </c>
       <c r="C280" s="6">
         <v>1</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="B281" s="8">
-        <v>46142</v>
+        <v>46213</v>
       </c>
       <c r="C281" s="9">
         <v>1</v>
@@ -5313,13 +5313,13 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B282" s="5">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C282" s="6">
-        <v>150</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -5327,10 +5327,10 @@
         <v>21</v>
       </c>
       <c r="B283" s="8">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C283" s="9">
-        <v>37</v>
+        <v>150</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -5338,10 +5338,10 @@
         <v>21</v>
       </c>
       <c r="B284" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C284" s="6">
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -5349,10 +5349,10 @@
         <v>21</v>
       </c>
       <c r="B285" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C285" s="9">
-        <v>109</v>
+        <v>69</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -5360,10 +5360,10 @@
         <v>21</v>
       </c>
       <c r="B286" s="5">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C286" s="6">
-        <v>145</v>
+        <v>109</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -5371,10 +5371,10 @@
         <v>21</v>
       </c>
       <c r="B287" s="8">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C287" s="9">
-        <v>44</v>
+        <v>145</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -5382,10 +5382,10 @@
         <v>21</v>
       </c>
       <c r="B288" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C288" s="6">
-        <v>126</v>
+        <v>44</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -5393,10 +5393,10 @@
         <v>21</v>
       </c>
       <c r="B289" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C289" s="9">
-        <v>24</v>
+        <v>126</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -5404,10 +5404,10 @@
         <v>21</v>
       </c>
       <c r="B290" s="5">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C290" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -5415,10 +5415,10 @@
         <v>21</v>
       </c>
       <c r="B291" s="8">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C291" s="9">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -5426,10 +5426,10 @@
         <v>21</v>
       </c>
       <c r="B292" s="5">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C292" s="6">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -5437,10 +5437,10 @@
         <v>21</v>
       </c>
       <c r="B293" s="8">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C293" s="9">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -5448,10 +5448,10 @@
         <v>21</v>
       </c>
       <c r="B294" s="5">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="C294" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -5459,10 +5459,10 @@
         <v>21</v>
       </c>
       <c r="B295" s="8">
-        <v>46157</v>
+        <v>46014</v>
       </c>
       <c r="C295" s="9">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -5470,10 +5470,10 @@
         <v>21</v>
       </c>
       <c r="B296" s="5">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C296" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -5481,10 +5481,10 @@
         <v>21</v>
       </c>
       <c r="B297" s="8">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C297" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -5492,10 +5492,10 @@
         <v>21</v>
       </c>
       <c r="B298" s="5">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C298" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -5503,10 +5503,10 @@
         <v>21</v>
       </c>
       <c r="B299" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C299" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -5514,10 +5514,10 @@
         <v>21</v>
       </c>
       <c r="B300" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C300" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -5525,10 +5525,10 @@
         <v>21</v>
       </c>
       <c r="B301" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C301" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -5536,10 +5536,10 @@
         <v>21</v>
       </c>
       <c r="B302" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C302" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -5547,10 +5547,10 @@
         <v>21</v>
       </c>
       <c r="B303" s="8">
-        <v>46192</v>
+        <v>46094</v>
       </c>
       <c r="C303" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -5558,10 +5558,10 @@
         <v>21</v>
       </c>
       <c r="B304" s="5">
-        <v>46127</v>
+        <v>46192</v>
       </c>
       <c r="C304" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
@@ -5569,7 +5569,7 @@
         <v>21</v>
       </c>
       <c r="B305" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C305" s="9">
         <v>2</v>
@@ -5580,10 +5580,10 @@
         <v>21</v>
       </c>
       <c r="B306" s="5">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C306" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
@@ -5591,10 +5591,10 @@
         <v>21</v>
       </c>
       <c r="B307" s="8">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="C307" s="9">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
@@ -5602,10 +5602,10 @@
         <v>21</v>
       </c>
       <c r="B308" s="5">
-        <v>46020</v>
+        <v>46084</v>
       </c>
       <c r="C308" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
@@ -5613,10 +5613,10 @@
         <v>21</v>
       </c>
       <c r="B309" s="8">
-        <v>46080</v>
+        <v>46020</v>
       </c>
       <c r="C309" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
@@ -5624,7 +5624,7 @@
         <v>21</v>
       </c>
       <c r="B310" s="5">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C310" s="6">
         <v>6</v>
@@ -5635,10 +5635,10 @@
         <v>21</v>
       </c>
       <c r="B311" s="8">
-        <v>46217</v>
+        <v>46015</v>
       </c>
       <c r="C311" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -5646,10 +5646,10 @@
         <v>21</v>
       </c>
       <c r="B312" s="5">
-        <v>46078</v>
+        <v>46217</v>
       </c>
       <c r="C312" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -5657,10 +5657,10 @@
         <v>21</v>
       </c>
       <c r="B313" s="8">
-        <v>46209</v>
+        <v>46078</v>
       </c>
       <c r="C313" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -5668,10 +5668,10 @@
         <v>21</v>
       </c>
       <c r="B314" s="5">
-        <v>46237</v>
+        <v>46209</v>
       </c>
       <c r="C314" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -5679,10 +5679,10 @@
         <v>21</v>
       </c>
       <c r="B315" s="8">
-        <v>46148</v>
+        <v>46237</v>
       </c>
       <c r="C315" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -5690,7 +5690,7 @@
         <v>21</v>
       </c>
       <c r="B316" s="5">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C316" s="6">
         <v>2</v>
@@ -5701,10 +5701,10 @@
         <v>21</v>
       </c>
       <c r="B317" s="8">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C317" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -5712,7 +5712,7 @@
         <v>21</v>
       </c>
       <c r="B318" s="5">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C318" s="6">
         <v>3</v>
@@ -5723,10 +5723,10 @@
         <v>21</v>
       </c>
       <c r="B319" s="8">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C319" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -5734,10 +5734,10 @@
         <v>21</v>
       </c>
       <c r="B320" s="5">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C320" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -5745,10 +5745,10 @@
         <v>21</v>
       </c>
       <c r="B321" s="8">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C321" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
@@ -5756,7 +5756,7 @@
         <v>21</v>
       </c>
       <c r="B322" s="5">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C322" s="6">
         <v>3</v>
@@ -5767,10 +5767,10 @@
         <v>21</v>
       </c>
       <c r="B323" s="8">
-        <v>46316</v>
+        <v>46104</v>
       </c>
       <c r="C323" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
@@ -5778,7 +5778,7 @@
         <v>21</v>
       </c>
       <c r="B324" s="5">
-        <v>46118</v>
+        <v>46316</v>
       </c>
       <c r="C324" s="6">
         <v>1</v>
@@ -5789,7 +5789,7 @@
         <v>21</v>
       </c>
       <c r="B325" s="8">
-        <v>46231</v>
+        <v>46118</v>
       </c>
       <c r="C325" s="9">
         <v>1</v>
@@ -5800,10 +5800,10 @@
         <v>21</v>
       </c>
       <c r="B326" s="5">
-        <v>46076</v>
+        <v>46231</v>
       </c>
       <c r="C326" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
@@ -5811,10 +5811,10 @@
         <v>21</v>
       </c>
       <c r="B327" s="8">
-        <v>46322</v>
+        <v>46076</v>
       </c>
       <c r="C327" s="9">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
@@ -5822,10 +5822,10 @@
         <v>21</v>
       </c>
       <c r="B328" s="5">
-        <v>46182</v>
+        <v>46322</v>
       </c>
       <c r="C328" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
@@ -5833,7 +5833,7 @@
         <v>21</v>
       </c>
       <c r="B329" s="8">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="C329" s="9">
         <v>1</v>
@@ -5844,7 +5844,7 @@
         <v>21</v>
       </c>
       <c r="B330" s="5">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C330" s="6">
         <v>1</v>
@@ -5855,10 +5855,10 @@
         <v>21</v>
       </c>
       <c r="B331" s="8">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C331" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
@@ -5866,10 +5866,10 @@
         <v>21</v>
       </c>
       <c r="B332" s="5">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C332" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -5877,7 +5877,7 @@
         <v>21</v>
       </c>
       <c r="B333" s="8">
-        <v>46300</v>
+        <v>46122</v>
       </c>
       <c r="C333" s="9">
         <v>1</v>
@@ -5888,10 +5888,10 @@
         <v>21</v>
       </c>
       <c r="B334" s="5">
-        <v>46092</v>
+        <v>46300</v>
       </c>
       <c r="C334" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
@@ -5899,10 +5899,10 @@
         <v>21</v>
       </c>
       <c r="B335" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C335" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -5910,10 +5910,10 @@
         <v>21</v>
       </c>
       <c r="B336" s="5">
-        <v>46287</v>
+        <v>46156</v>
       </c>
       <c r="C336" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
@@ -5921,7 +5921,7 @@
         <v>21</v>
       </c>
       <c r="B337" s="8">
-        <v>46133</v>
+        <v>46287</v>
       </c>
       <c r="C337" s="9">
         <v>1</v>
@@ -5932,7 +5932,7 @@
         <v>21</v>
       </c>
       <c r="B338" s="5">
-        <v>46189</v>
+        <v>46133</v>
       </c>
       <c r="C338" s="6">
         <v>1</v>
@@ -5943,7 +5943,7 @@
         <v>21</v>
       </c>
       <c r="B339" s="8">
-        <v>46295</v>
+        <v>46189</v>
       </c>
       <c r="C339" s="9">
         <v>1</v>
@@ -5954,7 +5954,7 @@
         <v>21</v>
       </c>
       <c r="B340" s="5">
-        <v>46210</v>
+        <v>46295</v>
       </c>
       <c r="C340" s="6">
         <v>1</v>
@@ -5965,7 +5965,7 @@
         <v>21</v>
       </c>
       <c r="B341" s="8">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="C341" s="9">
         <v>1</v>
@@ -5976,7 +5976,7 @@
         <v>21</v>
       </c>
       <c r="B342" s="5">
-        <v>46126</v>
+        <v>46232</v>
       </c>
       <c r="C342" s="6">
         <v>1</v>
@@ -5987,7 +5987,7 @@
         <v>21</v>
       </c>
       <c r="B343" s="8">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C343" s="9">
         <v>1</v>
@@ -5998,7 +5998,7 @@
         <v>21</v>
       </c>
       <c r="B344" s="5">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C344" s="6">
         <v>1</v>
@@ -6009,10 +6009,10 @@
         <v>21</v>
       </c>
       <c r="B345" s="8">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C345" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -6020,7 +6020,7 @@
         <v>21</v>
       </c>
       <c r="B346" s="5">
-        <v>46077</v>
+        <v>46097</v>
       </c>
       <c r="C346" s="6">
         <v>3</v>
@@ -6031,10 +6031,10 @@
         <v>21</v>
       </c>
       <c r="B347" s="8">
-        <v>46108</v>
+        <v>46077</v>
       </c>
       <c r="C347" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
@@ -6042,7 +6042,7 @@
         <v>21</v>
       </c>
       <c r="B348" s="5">
-        <v>46233</v>
+        <v>46108</v>
       </c>
       <c r="C348" s="6">
         <v>1</v>
@@ -6053,7 +6053,7 @@
         <v>21</v>
       </c>
       <c r="B349" s="8">
-        <v>46100</v>
+        <v>46233</v>
       </c>
       <c r="C349" s="9">
         <v>1</v>
@@ -6064,10 +6064,10 @@
         <v>21</v>
       </c>
       <c r="B350" s="5">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="C350" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -6075,10 +6075,10 @@
         <v>21</v>
       </c>
       <c r="B351" s="8">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C351" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
@@ -6086,7 +6086,7 @@
         <v>21</v>
       </c>
       <c r="B352" s="5">
-        <v>46253</v>
+        <v>46113</v>
       </c>
       <c r="C352" s="6">
         <v>1</v>
@@ -6097,7 +6097,7 @@
         <v>21</v>
       </c>
       <c r="B353" s="8">
-        <v>46142</v>
+        <v>46253</v>
       </c>
       <c r="C353" s="9">
         <v>1</v>
@@ -6108,7 +6108,7 @@
         <v>21</v>
       </c>
       <c r="B354" s="5">
-        <v>46244</v>
+        <v>46142</v>
       </c>
       <c r="C354" s="6">
         <v>1</v>
@@ -6119,7 +6119,7 @@
         <v>21</v>
       </c>
       <c r="B355" s="8">
-        <v>46153</v>
+        <v>46244</v>
       </c>
       <c r="C355" s="9">
         <v>1</v>
@@ -6130,7 +6130,7 @@
         <v>21</v>
       </c>
       <c r="B356" s="5">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C356" s="6">
         <v>1</v>
@@ -6141,9 +6141,20 @@
         <v>21</v>
       </c>
       <c r="B357" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C357" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B358" s="5">
         <v>46155</v>
       </c>
-      <c r="C357" s="9">
+      <c r="C358" s="6">
         <v>1</v>
       </c>
     </row>
@@ -6366,7 +6377,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -6445,7 +6456,7 @@
         <v>12</v>
       </c>
       <c r="C17">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -6513,7 +6524,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -6706,7 +6717,7 @@
         <v>242</v>
       </c>
       <c r="E32">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -8944,7 +8955,7 @@
         <v>187</v>
       </c>
       <c r="C191">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -10764,7 +10775,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -10819,7 +10830,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -10957,7 +10968,7 @@
         <v>271</v>
       </c>
       <c r="C9">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -11133,7 +11144,7 @@
         <v>271</v>
       </c>
       <c r="C25">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
